--- a/research/traditional_assets/database/data/belgium/belgium_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_electronics_general.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtbr_bar" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0707</v>
+        <v>-0.0355</v>
+      </c>
+      <c r="E2">
+        <v>0.189</v>
       </c>
       <c r="G2">
-        <v>0.1874566072668364</v>
+        <v>0.1632010081915564</v>
       </c>
       <c r="H2">
-        <v>0.04940985882897477</v>
+        <v>0.04326822096198277</v>
       </c>
       <c r="I2">
-        <v>-0.003274704929414487</v>
+        <v>0.03633690401176223</v>
       </c>
       <c r="J2">
-        <v>-0.003274704929414487</v>
+        <v>0.03019824447844</v>
       </c>
       <c r="K2">
-        <v>-14.6</v>
+        <v>30.1</v>
       </c>
       <c r="L2">
-        <v>-0.01689423744503587</v>
+        <v>0.03161100609115732</v>
       </c>
       <c r="M2">
-        <v>24.4</v>
+        <v>26.67</v>
       </c>
       <c r="N2">
-        <v>0.0125805620005156</v>
+        <v>0.01212989493791786</v>
       </c>
       <c r="O2">
-        <v>-1.671232876712329</v>
+        <v>0.886046511627907</v>
       </c>
       <c r="P2">
-        <v>24.4</v>
+        <v>22</v>
       </c>
       <c r="Q2">
-        <v>0.0125805620005156</v>
+        <v>0.01000591258470915</v>
       </c>
       <c r="R2">
-        <v>-1.671232876712329</v>
+        <v>0.7308970099667774</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>4.670000000000002</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1751031121109862</v>
       </c>
       <c r="U2">
-        <v>312.3</v>
+        <v>294.4</v>
       </c>
       <c r="V2">
-        <v>0.1610208816705337</v>
+        <v>0.1338973029517442</v>
       </c>
       <c r="W2">
-        <v>-0.01940457203615098</v>
+        <v>0.03813022548771219</v>
       </c>
       <c r="X2">
-        <v>0.0767228916680654</v>
+        <v>0.1302434314723578</v>
       </c>
       <c r="Y2">
-        <v>-0.09612746370421638</v>
+        <v>-0.09211320598464559</v>
       </c>
       <c r="Z2">
-        <v>2.219311761684643</v>
+        <v>2.332680058794709</v>
       </c>
       <c r="AA2">
-        <v>-0.007267591165896251</v>
+        <v>0.07044284270546443</v>
       </c>
       <c r="AB2">
-        <v>0.07516133963362878</v>
+        <v>0.1282313938190113</v>
       </c>
       <c r="AC2">
-        <v>-0.08242893079952503</v>
+        <v>-0.0577885511135469</v>
       </c>
       <c r="AD2">
-        <v>56.3</v>
+        <v>50.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>56.3</v>
+        <v>50.7</v>
       </c>
       <c r="AG2">
-        <v>-256</v>
+        <v>-243.7</v>
       </c>
       <c r="AH2">
-        <v>0.02820923940274576</v>
+        <v>0.02253934382502001</v>
       </c>
       <c r="AI2">
-        <v>0.06312366857270994</v>
+        <v>0.06264673174348202</v>
       </c>
       <c r="AJ2">
-        <v>-0.1520641520641521</v>
+        <v>-0.1246547314578005</v>
       </c>
       <c r="AK2">
-        <v>-0.4416839199447895</v>
+        <v>-0.4732957855894347</v>
       </c>
       <c r="AL2">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AM2">
-        <v>1.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AN2">
-        <v>2.190661478599222</v>
+        <v>0.8817391304347827</v>
       </c>
       <c r="AO2">
-        <v>-1.635838150289017</v>
+        <v>16.63461538461538</v>
       </c>
       <c r="AP2">
-        <v>-9.961089494163424</v>
+        <v>-4.238260869565218</v>
       </c>
       <c r="AQ2">
-        <v>-1.635838150289017</v>
+        <v>42.71604938271605</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +724,8833 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0707</v>
+        <v>-0.0355</v>
+      </c>
+      <c r="E3">
+        <v>0.189</v>
       </c>
       <c r="G3">
-        <v>0.1874566072668364</v>
+        <v>0.1632010081915564</v>
       </c>
       <c r="H3">
-        <v>0.04940985882897477</v>
+        <v>0.04326822096198277</v>
       </c>
       <c r="I3">
-        <v>-0.003274704929414487</v>
+        <v>0.03633690401176223</v>
       </c>
       <c r="J3">
-        <v>-0.003274704929414487</v>
+        <v>0.03019824447844</v>
       </c>
       <c r="K3">
-        <v>-14.6</v>
+        <v>30.1</v>
       </c>
       <c r="L3">
-        <v>-0.01689423744503587</v>
+        <v>0.03161100609115732</v>
       </c>
       <c r="M3">
-        <v>24.4</v>
+        <v>26.67</v>
       </c>
       <c r="N3">
-        <v>0.0125805620005156</v>
+        <v>0.01212989493791786</v>
       </c>
       <c r="O3">
-        <v>-1.671232876712329</v>
+        <v>0.886046511627907</v>
       </c>
       <c r="P3">
-        <v>24.4</v>
+        <v>22</v>
       </c>
       <c r="Q3">
-        <v>0.0125805620005156</v>
+        <v>0.01000591258470915</v>
       </c>
       <c r="R3">
-        <v>-1.671232876712329</v>
+        <v>0.7308970099667774</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>4.670000000000002</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1751031121109862</v>
       </c>
       <c r="U3">
-        <v>312.3</v>
+        <v>294.4</v>
       </c>
       <c r="V3">
-        <v>0.1610208816705337</v>
+        <v>0.1338973029517442</v>
       </c>
       <c r="W3">
-        <v>-0.01940457203615098</v>
+        <v>0.03813022548771219</v>
       </c>
       <c r="X3">
-        <v>0.0767228916680654</v>
+        <v>0.1302434314723578</v>
       </c>
       <c r="Y3">
-        <v>-0.09612746370421638</v>
+        <v>-0.09211320598464559</v>
       </c>
       <c r="Z3">
-        <v>2.219311761684643</v>
+        <v>2.332680058794709</v>
       </c>
       <c r="AA3">
-        <v>-0.007267591165896251</v>
+        <v>0.07044284270546443</v>
       </c>
       <c r="AB3">
-        <v>0.07516133963362878</v>
+        <v>0.1282313938190113</v>
       </c>
       <c r="AC3">
-        <v>-0.08242893079952503</v>
+        <v>-0.0577885511135469</v>
       </c>
       <c r="AD3">
-        <v>56.3</v>
+        <v>50.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>56.3</v>
+        <v>50.7</v>
       </c>
       <c r="AG3">
-        <v>-256</v>
+        <v>-243.7</v>
       </c>
       <c r="AH3">
-        <v>0.02820923940274576</v>
+        <v>0.02253934382502001</v>
       </c>
       <c r="AI3">
-        <v>0.06312366857270994</v>
+        <v>0.06264673174348202</v>
       </c>
       <c r="AJ3">
-        <v>-0.1520641520641521</v>
+        <v>-0.1246547314578005</v>
       </c>
       <c r="AK3">
-        <v>-0.4416839199447895</v>
+        <v>-0.4732957855894347</v>
       </c>
       <c r="AL3">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AM3">
-        <v>1.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AN3">
-        <v>2.190661478599222</v>
+        <v>0.8817391304347827</v>
       </c>
       <c r="AO3">
-        <v>-1.635838150289017</v>
+        <v>16.63461538461538</v>
       </c>
       <c r="AP3">
-        <v>-9.961089494163424</v>
+        <v>-4.238260869565218</v>
       </c>
       <c r="AQ3">
-        <v>-1.635838150289017</v>
+        <v>42.71604938271605</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Barco NV (ENXTBR:BAR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTBR:BAR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electronics (General)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.02253934382502</v>
+      </c>
+      <c r="F2">
+        <v>0.06</v>
+      </c>
+      <c r="G2">
+        <v>2198.7</v>
+      </c>
+      <c r="H2">
+        <v>2130.83344305227</v>
+      </c>
+      <c r="I2">
+        <v>1955</v>
+      </c>
+      <c r="J2">
+        <v>1971.39744305227</v>
+      </c>
+      <c r="K2">
+        <v>50.7</v>
+      </c>
+      <c r="L2">
+        <v>134.964</v>
+      </c>
+      <c r="M2">
+        <v>0.128231393819011</v>
+      </c>
+      <c r="N2">
+        <v>0.127487532558361</v>
+      </c>
+      <c r="O2">
+        <v>0.040975630733945</v>
+      </c>
+      <c r="P2">
+        <v>0.04125</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.130243431472358</v>
+      </c>
+      <c r="T2">
+        <v>0.132992055913149</v>
+      </c>
+      <c r="U2">
+        <v>1.31595682724829</v>
+      </c>
+      <c r="V2">
+        <v>1.35551211339801</v>
+      </c>
+      <c r="W2">
+        <v>4.661175640103355</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>2198.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.06948816980840411</v>
+      </c>
+      <c r="AC2">
+        <v>0.0546341743119266</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>57.5</v>
+      </c>
+      <c r="AH2">
+        <v>22.9</v>
+      </c>
+      <c r="AI2">
+        <v>39.09999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>50.7</v>
+      </c>
+      <c r="AK2">
+        <v>50.7</v>
+      </c>
+      <c r="AL2">
+        <v>2.08</v>
+      </c>
+      <c r="AM2">
+        <v>50.7</v>
+      </c>
+      <c r="AN2">
+        <v>294.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1286888655414828</v>
+      </c>
+      <c r="C2">
+        <v>2239.450411560495</v>
+      </c>
+      <c r="D2">
+        <v>1945.050411560495</v>
+      </c>
+      <c r="E2">
+        <v>-50.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>294.4</v>
+      </c>
+      <c r="H2">
+        <v>2198.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>57.5</v>
+      </c>
+      <c r="K2">
+        <v>22.9</v>
+      </c>
+      <c r="L2">
+        <v>34.6</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>34.6</v>
+      </c>
+      <c r="O2">
+        <v>8.65</v>
+      </c>
+      <c r="P2">
+        <v>25.95</v>
+      </c>
+      <c r="Q2">
+        <v>48.85</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1286888655414828</v>
+      </c>
+      <c r="T2">
+        <v>1.293585164054952</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1284188933776291</v>
+      </c>
+      <c r="C3">
+        <v>2222.815772780242</v>
+      </c>
+      <c r="D3">
+        <v>1950.909772780242</v>
+      </c>
+      <c r="E3">
+        <v>-28.20600000000001</v>
+      </c>
+      <c r="F3">
+        <v>22.494</v>
+      </c>
+      <c r="G3">
+        <v>294.4</v>
+      </c>
+      <c r="H3">
+        <v>2198.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>57.5</v>
+      </c>
+      <c r="K3">
+        <v>22.9</v>
+      </c>
+      <c r="L3">
+        <v>34.6</v>
+      </c>
+      <c r="M3">
+        <v>1.0279758</v>
+      </c>
+      <c r="N3">
+        <v>33.5720242</v>
+      </c>
+      <c r="O3">
+        <v>8.39300605</v>
+      </c>
+      <c r="P3">
+        <v>25.17901815</v>
+      </c>
+      <c r="Q3">
+        <v>48.07901815</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1293698417955849</v>
+      </c>
+      <c r="T3">
+        <v>1.303385051661429</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>33.6583798957135</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1281489212137754</v>
+      </c>
+      <c r="C4">
+        <v>2206.216542696721</v>
+      </c>
+      <c r="D4">
+        <v>1956.804542696721</v>
+      </c>
+      <c r="E4">
+        <v>-5.71200000000001</v>
+      </c>
+      <c r="F4">
+        <v>44.98799999999999</v>
+      </c>
+      <c r="G4">
+        <v>294.4</v>
+      </c>
+      <c r="H4">
+        <v>2198.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>57.5</v>
+      </c>
+      <c r="K4">
+        <v>22.9</v>
+      </c>
+      <c r="L4">
+        <v>34.6</v>
+      </c>
+      <c r="M4">
+        <v>2.0559516</v>
+      </c>
+      <c r="N4">
+        <v>32.5440484</v>
+      </c>
+      <c r="O4">
+        <v>8.1360121</v>
+      </c>
+      <c r="P4">
+        <v>24.4080363</v>
+      </c>
+      <c r="Q4">
+        <v>47.3080363</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1300647155242606</v>
+      </c>
+      <c r="T4">
+        <v>1.313384936974161</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>16.82918994785675</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1279149490499217</v>
+      </c>
+      <c r="C5">
+        <v>2188.860152020125</v>
+      </c>
+      <c r="D5">
+        <v>1961.942152020125</v>
+      </c>
+      <c r="E5">
+        <v>16.78199999999998</v>
+      </c>
+      <c r="F5">
+        <v>67.48199999999999</v>
+      </c>
+      <c r="G5">
+        <v>294.4</v>
+      </c>
+      <c r="H5">
+        <v>2198.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>57.5</v>
+      </c>
+      <c r="K5">
+        <v>22.9</v>
+      </c>
+      <c r="L5">
+        <v>34.6</v>
+      </c>
+      <c r="M5">
+        <v>3.1918986</v>
+      </c>
+      <c r="N5">
+        <v>31.4081014</v>
+      </c>
+      <c r="O5">
+        <v>7.852025350000001</v>
+      </c>
+      <c r="P5">
+        <v>23.55607605</v>
+      </c>
+      <c r="Q5">
+        <v>46.45607605</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.130773916546311</v>
+      </c>
+      <c r="T5">
+        <v>1.323591005489216</v>
+      </c>
+      <c r="U5">
+        <v>0.0473</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.035475</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>10.83994334907757</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.127827976886068</v>
+      </c>
+      <c r="C6">
+        <v>2168.282789466973</v>
+      </c>
+      <c r="D6">
+        <v>1963.858789466973</v>
+      </c>
+      <c r="E6">
+        <v>39.27599999999998</v>
+      </c>
+      <c r="F6">
+        <v>89.97599999999998</v>
+      </c>
+      <c r="G6">
+        <v>294.4</v>
+      </c>
+      <c r="H6">
+        <v>2198.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>57.5</v>
+      </c>
+      <c r="K6">
+        <v>22.9</v>
+      </c>
+      <c r="L6">
+        <v>34.6</v>
+      </c>
+      <c r="M6">
+        <v>4.768727999999999</v>
+      </c>
+      <c r="N6">
+        <v>29.831272</v>
+      </c>
+      <c r="O6">
+        <v>7.457818000000001</v>
+      </c>
+      <c r="P6">
+        <v>22.373454</v>
+      </c>
+      <c r="Q6">
+        <v>45.273454</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1314978925896541</v>
+      </c>
+      <c r="T6">
+        <v>1.334009700431669</v>
+      </c>
+      <c r="U6">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>7.255603590726921</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1276877547222143</v>
+      </c>
+      <c r="C7">
+        <v>2148.886814946667</v>
+      </c>
+      <c r="D7">
+        <v>1966.956814946667</v>
+      </c>
+      <c r="E7">
+        <v>61.76999999999998</v>
+      </c>
+      <c r="F7">
+        <v>112.47</v>
+      </c>
+      <c r="G7">
+        <v>294.4</v>
+      </c>
+      <c r="H7">
+        <v>2198.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>57.5</v>
+      </c>
+      <c r="K7">
+        <v>22.9</v>
+      </c>
+      <c r="L7">
+        <v>34.6</v>
+      </c>
+      <c r="M7">
+        <v>6.185849999999999</v>
+      </c>
+      <c r="N7">
+        <v>28.41415</v>
+      </c>
+      <c r="O7">
+        <v>7.103537500000001</v>
+      </c>
+      <c r="P7">
+        <v>21.3106125</v>
+      </c>
+      <c r="Q7">
+        <v>44.2106125</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1322371102339098</v>
+      </c>
+      <c r="T7">
+        <v>1.344647736320279</v>
+      </c>
+      <c r="U7">
+        <v>0.055</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.04125</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>5.593410768124026</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1274875325583605</v>
+      </c>
+      <c r="C8">
+        <v>2130.833443052272</v>
+      </c>
+      <c r="D8">
+        <v>1971.397443052272</v>
+      </c>
+      <c r="E8">
+        <v>84.26399999999997</v>
+      </c>
+      <c r="F8">
+        <v>134.964</v>
+      </c>
+      <c r="G8">
+        <v>294.4</v>
+      </c>
+      <c r="H8">
+        <v>2198.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>57.5</v>
+      </c>
+      <c r="K8">
+        <v>22.9</v>
+      </c>
+      <c r="L8">
+        <v>34.6</v>
+      </c>
+      <c r="M8">
+        <v>7.423019999999998</v>
+      </c>
+      <c r="N8">
+        <v>27.17698</v>
+      </c>
+      <c r="O8">
+        <v>6.794245000000001</v>
+      </c>
+      <c r="P8">
+        <v>20.382735</v>
+      </c>
+      <c r="Q8">
+        <v>43.282735</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1329920559131495</v>
+      </c>
+      <c r="T8">
+        <v>1.355512113398008</v>
+      </c>
+      <c r="U8">
+        <v>0.055</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.04125</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>4.661175640103355</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1280800603945068</v>
+      </c>
+      <c r="C9">
+        <v>2095.255806505046</v>
+      </c>
+      <c r="D9">
+        <v>1958.313806505046</v>
+      </c>
+      <c r="E9">
+        <v>106.758</v>
+      </c>
+      <c r="F9">
+        <v>157.458</v>
+      </c>
+      <c r="G9">
+        <v>294.4</v>
+      </c>
+      <c r="H9">
+        <v>2198.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>57.5</v>
+      </c>
+      <c r="K9">
+        <v>22.9</v>
+      </c>
+      <c r="L9">
+        <v>34.6</v>
+      </c>
+      <c r="M9">
+        <v>11.0378058</v>
+      </c>
+      <c r="N9">
+        <v>23.5621942</v>
+      </c>
+      <c r="O9">
+        <v>5.89054855</v>
+      </c>
+      <c r="P9">
+        <v>17.67164565</v>
+      </c>
+      <c r="Q9">
+        <v>40.57164565</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1337632369833407</v>
+      </c>
+      <c r="T9">
+        <v>1.366610132993538</v>
+      </c>
+      <c r="U9">
+        <v>0.0701</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.052575</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>3.134680988861029</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1292710882306531</v>
+      </c>
+      <c r="C10">
+        <v>2046.981125614918</v>
+      </c>
+      <c r="D10">
+        <v>1932.533125614917</v>
+      </c>
+      <c r="E10">
+        <v>129.252</v>
+      </c>
+      <c r="F10">
+        <v>179.952</v>
+      </c>
+      <c r="G10">
+        <v>294.4</v>
+      </c>
+      <c r="H10">
+        <v>2198.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>57.5</v>
+      </c>
+      <c r="K10">
+        <v>22.9</v>
+      </c>
+      <c r="L10">
+        <v>34.6</v>
+      </c>
+      <c r="M10">
+        <v>16.4476128</v>
+      </c>
+      <c r="N10">
+        <v>18.1523872</v>
+      </c>
+      <c r="O10">
+        <v>4.538096800000001</v>
+      </c>
+      <c r="P10">
+        <v>13.6142904</v>
+      </c>
+      <c r="Q10">
+        <v>36.5142904</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1345511828594056</v>
+      </c>
+      <c r="T10">
+        <v>1.377949413884623</v>
+      </c>
+      <c r="U10">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.06855</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>2.103648743482094</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1307681160667994</v>
+      </c>
+      <c r="C11">
+        <v>1993.029964078424</v>
+      </c>
+      <c r="D11">
+        <v>1901.075964078424</v>
+      </c>
+      <c r="E11">
+        <v>151.746</v>
+      </c>
+      <c r="F11">
+        <v>202.446</v>
+      </c>
+      <c r="G11">
+        <v>294.4</v>
+      </c>
+      <c r="H11">
+        <v>2198.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>57.5</v>
+      </c>
+      <c r="K11">
+        <v>22.9</v>
+      </c>
+      <c r="L11">
+        <v>34.6</v>
+      </c>
+      <c r="M11">
+        <v>22.775175</v>
+      </c>
+      <c r="N11">
+        <v>11.824825</v>
+      </c>
+      <c r="O11">
+        <v>2.956206250000001</v>
+      </c>
+      <c r="P11">
+        <v>8.868618750000003</v>
+      </c>
+      <c r="Q11">
+        <v>31.76861875</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1353564462272521</v>
+      </c>
+      <c r="T11">
+        <v>1.389537909740347</v>
+      </c>
+      <c r="U11">
+        <v>0.1125</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>1.519197986404056</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1407266279720633</v>
+      </c>
+      <c r="C12">
+        <v>1784.795613418781</v>
+      </c>
+      <c r="D12">
+        <v>1715.335613418781</v>
+      </c>
+      <c r="E12">
+        <v>174.24</v>
+      </c>
+      <c r="F12">
+        <v>224.94</v>
+      </c>
+      <c r="G12">
+        <v>294.4</v>
+      </c>
+      <c r="H12">
+        <v>2198.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>57.5</v>
+      </c>
+      <c r="K12">
+        <v>22.9</v>
+      </c>
+      <c r="L12">
+        <v>34.6</v>
+      </c>
+      <c r="M12">
+        <v>48.09217199999999</v>
+      </c>
+      <c r="N12">
+        <v>-13.49217199999999</v>
+      </c>
+      <c r="O12">
+        <v>-3.373042999999997</v>
+      </c>
+      <c r="P12">
+        <v>-10.11912899999999</v>
+      </c>
+      <c r="Q12">
+        <v>12.78087100000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1368801087501651</v>
+      </c>
+      <c r="T12">
+        <v>1.411464843880562</v>
+      </c>
+      <c r="U12">
+        <v>0.2138</v>
+      </c>
+      <c r="V12">
+        <v>0.1798629515007141</v>
+      </c>
+      <c r="W12">
+        <v>0.1753453009691473</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.7194518060028565</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1424766279720633</v>
+      </c>
+      <c r="C13">
+        <v>1733.3477654571</v>
+      </c>
+      <c r="D13">
+        <v>1686.3817654571</v>
+      </c>
+      <c r="E13">
+        <v>196.734</v>
+      </c>
+      <c r="F13">
+        <v>247.434</v>
+      </c>
+      <c r="G13">
+        <v>294.4</v>
+      </c>
+      <c r="H13">
+        <v>2198.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>57.5</v>
+      </c>
+      <c r="K13">
+        <v>22.9</v>
+      </c>
+      <c r="L13">
+        <v>34.6</v>
+      </c>
+      <c r="M13">
+        <v>52.90138919999999</v>
+      </c>
+      <c r="N13">
+        <v>-18.30138919999999</v>
+      </c>
+      <c r="O13">
+        <v>-4.575347299999997</v>
+      </c>
+      <c r="P13">
+        <v>-13.72604189999999</v>
+      </c>
+      <c r="Q13">
+        <v>9.173958100000007</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1379821324439872</v>
+      </c>
+      <c r="T13">
+        <v>1.427323999429782</v>
+      </c>
+      <c r="U13">
+        <v>0.2138</v>
+      </c>
+      <c r="V13">
+        <v>0.1635117740915583</v>
+      </c>
+      <c r="W13">
+        <v>0.1788411826992248</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.6540470963662333</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1442266279720633</v>
+      </c>
+      <c r="C14">
+        <v>1682.86114019423</v>
+      </c>
+      <c r="D14">
+        <v>1658.38914019423</v>
+      </c>
+      <c r="E14">
+        <v>219.228</v>
+      </c>
+      <c r="F14">
+        <v>269.9279999999999</v>
+      </c>
+      <c r="G14">
+        <v>294.4</v>
+      </c>
+      <c r="H14">
+        <v>2198.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>57.5</v>
+      </c>
+      <c r="K14">
+        <v>22.9</v>
+      </c>
+      <c r="L14">
+        <v>34.6</v>
+      </c>
+      <c r="M14">
+        <v>57.71060639999998</v>
+      </c>
+      <c r="N14">
+        <v>-23.11060639999998</v>
+      </c>
+      <c r="O14">
+        <v>-5.777651599999995</v>
+      </c>
+      <c r="P14">
+        <v>-17.33295479999999</v>
+      </c>
+      <c r="Q14">
+        <v>5.567045200000013</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1391092021308507</v>
+      </c>
+      <c r="T14">
+        <v>1.443543590332393</v>
+      </c>
+      <c r="U14">
+        <v>0.2138</v>
+      </c>
+      <c r="V14">
+        <v>0.1498857929172618</v>
+      </c>
+      <c r="W14">
+        <v>0.1817544174742894</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.5995431716690471</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1459766279720633</v>
+      </c>
+      <c r="C15">
+        <v>1633.288652558881</v>
+      </c>
+      <c r="D15">
+        <v>1631.310652558882</v>
+      </c>
+      <c r="E15">
+        <v>241.722</v>
+      </c>
+      <c r="F15">
+        <v>292.422</v>
+      </c>
+      <c r="G15">
+        <v>294.4</v>
+      </c>
+      <c r="H15">
+        <v>2198.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>57.5</v>
+      </c>
+      <c r="K15">
+        <v>22.9</v>
+      </c>
+      <c r="L15">
+        <v>34.6</v>
+      </c>
+      <c r="M15">
+        <v>62.51982359999999</v>
+      </c>
+      <c r="N15">
+        <v>-27.91982359999999</v>
+      </c>
+      <c r="O15">
+        <v>-6.979955899999997</v>
+      </c>
+      <c r="P15">
+        <v>-20.93986769999999</v>
+      </c>
+      <c r="Q15">
+        <v>1.960132300000009</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.140262181465688</v>
+      </c>
+      <c r="T15">
+        <v>1.460136045393685</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1383561165390109</v>
+      </c>
+      <c r="W15">
+        <v>0.1842194622839595</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.5534244661560435</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1477266279720633</v>
+      </c>
+      <c r="C16">
+        <v>1584.586243328494</v>
+      </c>
+      <c r="D16">
+        <v>1605.102243328494</v>
+      </c>
+      <c r="E16">
+        <v>264.216</v>
+      </c>
+      <c r="F16">
+        <v>314.916</v>
+      </c>
+      <c r="G16">
+        <v>294.4</v>
+      </c>
+      <c r="H16">
+        <v>2198.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>57.5</v>
+      </c>
+      <c r="K16">
+        <v>22.9</v>
+      </c>
+      <c r="L16">
+        <v>34.6</v>
+      </c>
+      <c r="M16">
+        <v>67.3290408</v>
+      </c>
+      <c r="N16">
+        <v>-32.7290408</v>
+      </c>
+      <c r="O16">
+        <v>-8.1822602</v>
+      </c>
+      <c r="P16">
+        <v>-24.5467806</v>
+      </c>
+      <c r="Q16">
+        <v>-1.6467806</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1414419742734286</v>
+      </c>
+      <c r="T16">
+        <v>1.477114371502914</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.1284735367862244</v>
+      </c>
+      <c r="W16">
+        <v>0.1863323578351052</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.5138941471448975</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1533958875686226</v>
+      </c>
+      <c r="C17">
+        <v>1482.685019478513</v>
+      </c>
+      <c r="D17">
+        <v>1525.695019478513</v>
+      </c>
+      <c r="E17">
+        <v>286.7099999999999</v>
+      </c>
+      <c r="F17">
+        <v>337.4099999999999</v>
+      </c>
+      <c r="G17">
+        <v>294.4</v>
+      </c>
+      <c r="H17">
+        <v>2198.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>57.5</v>
+      </c>
+      <c r="K17">
+        <v>22.9</v>
+      </c>
+      <c r="L17">
+        <v>34.6</v>
+      </c>
+      <c r="M17">
+        <v>80.57350799999999</v>
+      </c>
+      <c r="N17">
+        <v>-45.97350799999999</v>
+      </c>
+      <c r="O17">
+        <v>-11.493377</v>
+      </c>
+      <c r="P17">
+        <v>-34.48013099999999</v>
+      </c>
+      <c r="Q17">
+        <v>-11.58013099999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1428486558490681</v>
+      </c>
+      <c r="T17">
+        <v>1.497357839988529</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.107355385345764</v>
+      </c>
+      <c r="W17">
+        <v>0.2131635339794316</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.4294215413830561</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1553958875686226</v>
+      </c>
+      <c r="C18">
+        <v>1434.020370559518</v>
+      </c>
+      <c r="D18">
+        <v>1499.524370559518</v>
+      </c>
+      <c r="E18">
+        <v>309.204</v>
+      </c>
+      <c r="F18">
+        <v>359.9039999999999</v>
+      </c>
+      <c r="G18">
+        <v>294.4</v>
+      </c>
+      <c r="H18">
+        <v>2198.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>57.5</v>
+      </c>
+      <c r="K18">
+        <v>22.9</v>
+      </c>
+      <c r="L18">
+        <v>34.6</v>
+      </c>
+      <c r="M18">
+        <v>85.94507519999999</v>
+      </c>
+      <c r="N18">
+        <v>-51.34507519999999</v>
+      </c>
+      <c r="O18">
+        <v>-12.8362688</v>
+      </c>
+      <c r="P18">
+        <v>-38.50880639999999</v>
+      </c>
+      <c r="Q18">
+        <v>-15.60880639999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1440873303234618</v>
+      </c>
+      <c r="T18">
+        <v>1.515183528559821</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.1006456737616538</v>
+      </c>
+      <c r="W18">
+        <v>0.2147658131057171</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.4025826950466151</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1573958875686226</v>
+      </c>
+      <c r="C19">
+        <v>1386.238404824755</v>
+      </c>
+      <c r="D19">
+        <v>1474.236404824755</v>
+      </c>
+      <c r="E19">
+        <v>331.698</v>
+      </c>
+      <c r="F19">
+        <v>382.398</v>
+      </c>
+      <c r="G19">
+        <v>294.4</v>
+      </c>
+      <c r="H19">
+        <v>2198.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>57.5</v>
+      </c>
+      <c r="K19">
+        <v>22.9</v>
+      </c>
+      <c r="L19">
+        <v>34.6</v>
+      </c>
+      <c r="M19">
+        <v>91.31664239999999</v>
+      </c>
+      <c r="N19">
+        <v>-56.71664239999999</v>
+      </c>
+      <c r="O19">
+        <v>-14.1791606</v>
+      </c>
+      <c r="P19">
+        <v>-42.53748179999999</v>
+      </c>
+      <c r="Q19">
+        <v>-19.6374818</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1453558523755517</v>
+      </c>
+      <c r="T19">
+        <v>1.533438751795482</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.09472534001096826</v>
+      </c>
+      <c r="W19">
+        <v>0.2161795888053808</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.3789013600438731</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1593958875686226</v>
+      </c>
+      <c r="C20">
+        <v>1339.295206190418</v>
+      </c>
+      <c r="D20">
+        <v>1449.787206190418</v>
+      </c>
+      <c r="E20">
+        <v>354.192</v>
+      </c>
+      <c r="F20">
+        <v>404.8919999999999</v>
+      </c>
+      <c r="G20">
+        <v>294.4</v>
+      </c>
+      <c r="H20">
+        <v>2198.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>57.5</v>
+      </c>
+      <c r="K20">
+        <v>22.9</v>
+      </c>
+      <c r="L20">
+        <v>34.6</v>
+      </c>
+      <c r="M20">
+        <v>96.68820959999999</v>
+      </c>
+      <c r="N20">
+        <v>-62.08820959999999</v>
+      </c>
+      <c r="O20">
+        <v>-15.5220524</v>
+      </c>
+      <c r="P20">
+        <v>-46.56615719999999</v>
+      </c>
+      <c r="Q20">
+        <v>-23.66615719999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1466553139898876</v>
+      </c>
+      <c r="T20">
+        <v>1.552139224378353</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.08946282112147003</v>
+      </c>
+      <c r="W20">
+        <v>0.2174362783161929</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.3578512844858801</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1613958875686226</v>
+      </c>
+      <c r="C21">
+        <v>1293.149724318664</v>
+      </c>
+      <c r="D21">
+        <v>1426.135724318664</v>
+      </c>
+      <c r="E21">
+        <v>376.6859999999999</v>
+      </c>
+      <c r="F21">
+        <v>427.3859999999999</v>
+      </c>
+      <c r="G21">
+        <v>294.4</v>
+      </c>
+      <c r="H21">
+        <v>2198.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>57.5</v>
+      </c>
+      <c r="K21">
+        <v>22.9</v>
+      </c>
+      <c r="L21">
+        <v>34.6</v>
+      </c>
+      <c r="M21">
+        <v>102.0597768</v>
+      </c>
+      <c r="N21">
+        <v>-67.45977679999999</v>
+      </c>
+      <c r="O21">
+        <v>-16.8649442</v>
+      </c>
+      <c r="P21">
+        <v>-50.59483259999999</v>
+      </c>
+      <c r="Q21">
+        <v>-27.69483259999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1479868610761826</v>
+      </c>
+      <c r="T21">
+        <v>1.571301437025</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.08475425158876108</v>
+      </c>
+      <c r="W21">
+        <v>0.2185606847206039</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.3390170063550443</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1633958875686226</v>
+      </c>
+      <c r="C22">
+        <v>1247.763544614367</v>
+      </c>
+      <c r="D22">
+        <v>1403.243544614367</v>
+      </c>
+      <c r="E22">
+        <v>399.1799999999999</v>
+      </c>
+      <c r="F22">
+        <v>449.8799999999999</v>
+      </c>
+      <c r="G22">
+        <v>294.4</v>
+      </c>
+      <c r="H22">
+        <v>2198.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>57.5</v>
+      </c>
+      <c r="K22">
+        <v>22.9</v>
+      </c>
+      <c r="L22">
+        <v>34.6</v>
+      </c>
+      <c r="M22">
+        <v>107.431344</v>
+      </c>
+      <c r="N22">
+        <v>-72.831344</v>
+      </c>
+      <c r="O22">
+        <v>-18.207836</v>
+      </c>
+      <c r="P22">
+        <v>-54.623508</v>
+      </c>
+      <c r="Q22">
+        <v>-31.723508</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1493516968396348</v>
+      </c>
+      <c r="T22">
+        <v>1.590942704987812</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.08051653900932303</v>
+      </c>
+      <c r="W22">
+        <v>0.2195726504845737</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.3220661560372921</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1653958875686226</v>
+      </c>
+      <c r="C23">
+        <v>1203.100680023821</v>
+      </c>
+      <c r="D23">
+        <v>1381.074680023821</v>
+      </c>
+      <c r="E23">
+        <v>421.6739999999999</v>
+      </c>
+      <c r="F23">
+        <v>472.3739999999999</v>
+      </c>
+      <c r="G23">
+        <v>294.4</v>
+      </c>
+      <c r="H23">
+        <v>2198.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>57.5</v>
+      </c>
+      <c r="K23">
+        <v>22.9</v>
+      </c>
+      <c r="L23">
+        <v>34.6</v>
+      </c>
+      <c r="M23">
+        <v>112.8029112</v>
+      </c>
+      <c r="N23">
+        <v>-78.20291119999999</v>
+      </c>
+      <c r="O23">
+        <v>-19.5507278</v>
+      </c>
+      <c r="P23">
+        <v>-58.65218339999999</v>
+      </c>
+      <c r="Q23">
+        <v>-35.75218339999999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1507510854072252</v>
+      </c>
+      <c r="T23">
+        <v>1.611081220240822</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.07668241810411718</v>
+      </c>
+      <c r="W23">
+        <v>0.2204882385567368</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3067296724164686</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1673958875686226</v>
+      </c>
+      <c r="C24">
+        <v>1159.127382261879</v>
+      </c>
+      <c r="D24">
+        <v>1359.595382261879</v>
+      </c>
+      <c r="E24">
+        <v>444.1679999999999</v>
+      </c>
+      <c r="F24">
+        <v>494.8679999999999</v>
+      </c>
+      <c r="G24">
+        <v>294.4</v>
+      </c>
+      <c r="H24">
+        <v>2198.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>57.5</v>
+      </c>
+      <c r="K24">
+        <v>22.9</v>
+      </c>
+      <c r="L24">
+        <v>34.6</v>
+      </c>
+      <c r="M24">
+        <v>118.1744784</v>
+      </c>
+      <c r="N24">
+        <v>-83.5744784</v>
+      </c>
+      <c r="O24">
+        <v>-20.8936196</v>
+      </c>
+      <c r="P24">
+        <v>-62.6808588</v>
+      </c>
+      <c r="Q24">
+        <v>-39.7808588</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1521863557329588</v>
+      </c>
+      <c r="T24">
+        <v>1.631736107679807</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.0731968536448391</v>
+      </c>
+      <c r="W24">
+        <v>0.2213205913496124</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.2927874145793564</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1693958875686226</v>
+      </c>
+      <c r="C25">
+        <v>1115.811970384764</v>
+      </c>
+      <c r="D25">
+        <v>1338.773970384764</v>
+      </c>
+      <c r="E25">
+        <v>466.662</v>
+      </c>
+      <c r="F25">
+        <v>517.362</v>
+      </c>
+      <c r="G25">
+        <v>294.4</v>
+      </c>
+      <c r="H25">
+        <v>2198.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>57.5</v>
+      </c>
+      <c r="K25">
+        <v>22.9</v>
+      </c>
+      <c r="L25">
+        <v>34.6</v>
+      </c>
+      <c r="M25">
+        <v>123.5460456</v>
+      </c>
+      <c r="N25">
+        <v>-88.94604559999999</v>
+      </c>
+      <c r="O25">
+        <v>-22.2365114</v>
+      </c>
+      <c r="P25">
+        <v>-66.70953419999999</v>
+      </c>
+      <c r="Q25">
+        <v>-43.80953419999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1536589058074128</v>
+      </c>
+      <c r="T25">
+        <v>1.652927485701623</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.07001438174723741</v>
+      </c>
+      <c r="W25">
+        <v>0.2220805656387597</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.2800575269889497</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1713958875686226</v>
+      </c>
+      <c r="C26">
+        <v>1073.124674877135</v>
+      </c>
+      <c r="D26">
+        <v>1318.580674877135</v>
+      </c>
+      <c r="E26">
+        <v>489.1559999999999</v>
+      </c>
+      <c r="F26">
+        <v>539.8559999999999</v>
+      </c>
+      <c r="G26">
+        <v>294.4</v>
+      </c>
+      <c r="H26">
+        <v>2198.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>57.5</v>
+      </c>
+      <c r="K26">
+        <v>22.9</v>
+      </c>
+      <c r="L26">
+        <v>34.6</v>
+      </c>
+      <c r="M26">
+        <v>128.9176128</v>
+      </c>
+      <c r="N26">
+        <v>-94.31761279999998</v>
+      </c>
+      <c r="O26">
+        <v>-23.57940319999999</v>
+      </c>
+      <c r="P26">
+        <v>-70.73820959999998</v>
+      </c>
+      <c r="Q26">
+        <v>-47.83820959999998</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1551702071996156</v>
+      </c>
+      <c r="T26">
+        <v>1.674676531566118</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.06709711584110253</v>
+      </c>
+      <c r="W26">
+        <v>0.2227772087371447</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.26838846336441</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1733958875686226</v>
+      </c>
+      <c r="C27">
+        <v>1031.037495639695</v>
+      </c>
+      <c r="D27">
+        <v>1298.987495639695</v>
+      </c>
+      <c r="E27">
+        <v>511.6499999999999</v>
+      </c>
+      <c r="F27">
+        <v>562.3499999999999</v>
+      </c>
+      <c r="G27">
+        <v>294.4</v>
+      </c>
+      <c r="H27">
+        <v>2198.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>57.5</v>
+      </c>
+      <c r="K27">
+        <v>22.9</v>
+      </c>
+      <c r="L27">
+        <v>34.6</v>
+      </c>
+      <c r="M27">
+        <v>134.28918</v>
+      </c>
+      <c r="N27">
+        <v>-99.68917999999999</v>
+      </c>
+      <c r="O27">
+        <v>-24.922295</v>
+      </c>
+      <c r="P27">
+        <v>-74.766885</v>
+      </c>
+      <c r="Q27">
+        <v>-51.866885</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1567218099622772</v>
+      </c>
+      <c r="T27">
+        <v>1.697005551987</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.06441323120745843</v>
+      </c>
+      <c r="W27">
+        <v>0.2234181203876589</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.2576529248298336</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1753958875686226</v>
+      </c>
+      <c r="C28">
+        <v>989.5240724526376</v>
+      </c>
+      <c r="D28">
+        <v>1279.968072452638</v>
+      </c>
+      <c r="E28">
+        <v>534.1439999999999</v>
+      </c>
+      <c r="F28">
+        <v>584.8439999999999</v>
+      </c>
+      <c r="G28">
+        <v>294.4</v>
+      </c>
+      <c r="H28">
+        <v>2198.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>57.5</v>
+      </c>
+      <c r="K28">
+        <v>22.9</v>
+      </c>
+      <c r="L28">
+        <v>34.6</v>
+      </c>
+      <c r="M28">
+        <v>139.6607472</v>
+      </c>
+      <c r="N28">
+        <v>-105.0607472</v>
+      </c>
+      <c r="O28">
+        <v>-26.2651868</v>
+      </c>
+      <c r="P28">
+        <v>-78.7955604</v>
+      </c>
+      <c r="Q28">
+        <v>-55.8955604</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1583153479347404</v>
+      </c>
+      <c r="T28">
+        <v>1.719938059446283</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.06193579923794078</v>
+      </c>
+      <c r="W28">
+        <v>0.2240097311419798</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.2477431969517631</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1773958875686226</v>
+      </c>
+      <c r="C29">
+        <v>948.559566654709</v>
+      </c>
+      <c r="D29">
+        <v>1261.497566654709</v>
+      </c>
+      <c r="E29">
+        <v>556.6379999999999</v>
+      </c>
+      <c r="F29">
+        <v>607.338</v>
+      </c>
+      <c r="G29">
+        <v>294.4</v>
+      </c>
+      <c r="H29">
+        <v>2198.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>57.5</v>
+      </c>
+      <c r="K29">
+        <v>22.9</v>
+      </c>
+      <c r="L29">
+        <v>34.6</v>
+      </c>
+      <c r="M29">
+        <v>145.0323144</v>
+      </c>
+      <c r="N29">
+        <v>-110.4323144</v>
+      </c>
+      <c r="O29">
+        <v>-27.6080786</v>
+      </c>
+      <c r="P29">
+        <v>-82.8242358</v>
+      </c>
+      <c r="Q29">
+        <v>-59.9242358</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1599525444817916</v>
+      </c>
+      <c r="T29">
+        <v>1.743498854781164</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.05964188074764668</v>
+      </c>
+      <c r="W29">
+        <v>0.224557518877462</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2385675229905867</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1793958875686226</v>
+      </c>
+      <c r="C30">
+        <v>908.1205529210891</v>
+      </c>
+      <c r="D30">
+        <v>1243.552552921089</v>
+      </c>
+      <c r="E30">
+        <v>579.1319999999999</v>
+      </c>
+      <c r="F30">
+        <v>629.832</v>
+      </c>
+      <c r="G30">
+        <v>294.4</v>
+      </c>
+      <c r="H30">
+        <v>2198.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>57.5</v>
+      </c>
+      <c r="K30">
+        <v>22.9</v>
+      </c>
+      <c r="L30">
+        <v>34.6</v>
+      </c>
+      <c r="M30">
+        <v>150.4038816</v>
+      </c>
+      <c r="N30">
+        <v>-115.8038816</v>
+      </c>
+      <c r="O30">
+        <v>-28.9509704</v>
+      </c>
+      <c r="P30">
+        <v>-86.85291120000001</v>
+      </c>
+      <c r="Q30">
+        <v>-63.95291120000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1616352187107054</v>
+      </c>
+      <c r="T30">
+        <v>1.767714116653125</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.05751181357808787</v>
+      </c>
+      <c r="W30">
+        <v>0.2250661789175526</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2300472543123514</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1813958875686226</v>
+      </c>
+      <c r="C31">
+        <v>868.1849201485786</v>
+      </c>
+      <c r="D31">
+        <v>1226.110920148578</v>
+      </c>
+      <c r="E31">
+        <v>601.6259999999997</v>
+      </c>
+      <c r="F31">
+        <v>652.3259999999998</v>
+      </c>
+      <c r="G31">
+        <v>294.4</v>
+      </c>
+      <c r="H31">
+        <v>2198.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>57.5</v>
+      </c>
+      <c r="K31">
+        <v>22.9</v>
+      </c>
+      <c r="L31">
+        <v>34.6</v>
+      </c>
+      <c r="M31">
+        <v>155.7754488</v>
+      </c>
+      <c r="N31">
+        <v>-121.1754488</v>
+      </c>
+      <c r="O31">
+        <v>-30.29386219999999</v>
+      </c>
+      <c r="P31">
+        <v>-90.88158659999998</v>
+      </c>
+      <c r="Q31">
+        <v>-67.98158659999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1633652922136731</v>
+      </c>
+      <c r="T31">
+        <v>1.792611498577816</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.05552864759263658</v>
+      </c>
+      <c r="W31">
+        <v>0.2255397589548784</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2221145903705463</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1833958875686226</v>
+      </c>
+      <c r="C32">
+        <v>828.7317805663178</v>
+      </c>
+      <c r="D32">
+        <v>1209.151780566317</v>
+      </c>
+      <c r="E32">
+        <v>624.1199999999998</v>
+      </c>
+      <c r="F32">
+        <v>674.8199999999998</v>
+      </c>
+      <c r="G32">
+        <v>294.4</v>
+      </c>
+      <c r="H32">
+        <v>2198.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>57.5</v>
+      </c>
+      <c r="K32">
+        <v>22.9</v>
+      </c>
+      <c r="L32">
+        <v>34.6</v>
+      </c>
+      <c r="M32">
+        <v>161.147016</v>
+      </c>
+      <c r="N32">
+        <v>-126.547016</v>
+      </c>
+      <c r="O32">
+        <v>-31.636754</v>
+      </c>
+      <c r="P32">
+        <v>-94.91026199999999</v>
+      </c>
+      <c r="Q32">
+        <v>-72.01026199999998</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1651447963881541</v>
+      </c>
+      <c r="T32">
+        <v>1.818220234271785</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05367769267288202</v>
+      </c>
+      <c r="W32">
+        <v>0.2259817669897158</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.214710770691528</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1853958875686226</v>
+      </c>
+      <c r="C33">
+        <v>789.7413862864946</v>
+      </c>
+      <c r="D33">
+        <v>1192.655386286495</v>
+      </c>
+      <c r="E33">
+        <v>646.6139999999998</v>
+      </c>
+      <c r="F33">
+        <v>697.3139999999999</v>
+      </c>
+      <c r="G33">
+        <v>294.4</v>
+      </c>
+      <c r="H33">
+        <v>2198.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>57.5</v>
+      </c>
+      <c r="K33">
+        <v>22.9</v>
+      </c>
+      <c r="L33">
+        <v>34.6</v>
+      </c>
+      <c r="M33">
+        <v>166.5185832</v>
+      </c>
+      <c r="N33">
+        <v>-131.9185832</v>
+      </c>
+      <c r="O33">
+        <v>-32.97964579999999</v>
+      </c>
+      <c r="P33">
+        <v>-98.93893739999999</v>
+      </c>
+      <c r="Q33">
+        <v>-76.03893739999998</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1669758803937795</v>
+      </c>
+      <c r="T33">
+        <v>1.844571252159782</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.05194615419956325</v>
+      </c>
+      <c r="W33">
+        <v>0.2263952583771443</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.207784616798253</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1873958875686226</v>
+      </c>
+      <c r="C34">
+        <v>751.1950525940734</v>
+      </c>
+      <c r="D34">
+        <v>1176.603052594073</v>
+      </c>
+      <c r="E34">
+        <v>669.1079999999998</v>
+      </c>
+      <c r="F34">
+        <v>719.8079999999999</v>
+      </c>
+      <c r="G34">
+        <v>294.4</v>
+      </c>
+      <c r="H34">
+        <v>2198.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>57.5</v>
+      </c>
+      <c r="K34">
+        <v>22.9</v>
+      </c>
+      <c r="L34">
+        <v>34.6</v>
+      </c>
+      <c r="M34">
+        <v>171.8901504</v>
+      </c>
+      <c r="N34">
+        <v>-137.2901504</v>
+      </c>
+      <c r="O34">
+        <v>-34.3225376</v>
+      </c>
+      <c r="P34">
+        <v>-102.9676128</v>
+      </c>
+      <c r="Q34">
+        <v>-80.06761279999998</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1688608198113351</v>
+      </c>
+      <c r="T34">
+        <v>1.871697299985661</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05032283688082689</v>
+      </c>
+      <c r="W34">
+        <v>0.2267829065528586</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2012913475233076</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1893958875686226</v>
+      </c>
+      <c r="C35">
+        <v>713.0750873490676</v>
+      </c>
+      <c r="D35">
+        <v>1160.977087349068</v>
+      </c>
+      <c r="E35">
+        <v>691.6019999999999</v>
+      </c>
+      <c r="F35">
+        <v>742.3019999999999</v>
+      </c>
+      <c r="G35">
+        <v>294.4</v>
+      </c>
+      <c r="H35">
+        <v>2198.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>57.5</v>
+      </c>
+      <c r="K35">
+        <v>22.9</v>
+      </c>
+      <c r="L35">
+        <v>34.6</v>
+      </c>
+      <c r="M35">
+        <v>177.2617176</v>
+      </c>
+      <c r="N35">
+        <v>-142.6617176</v>
+      </c>
+      <c r="O35">
+        <v>-35.6654294</v>
+      </c>
+      <c r="P35">
+        <v>-106.9962882</v>
+      </c>
+      <c r="Q35">
+        <v>-84.0962882</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1708020260771759</v>
+      </c>
+      <c r="T35">
+        <v>1.899633080582462</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.04879790242989274</v>
+      </c>
+      <c r="W35">
+        <v>0.2271470608997416</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1951916097195709</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1913958875686226</v>
+      </c>
+      <c r="C36">
+        <v>675.3647259405469</v>
+      </c>
+      <c r="D36">
+        <v>1145.760725940547</v>
+      </c>
+      <c r="E36">
+        <v>714.0959999999999</v>
+      </c>
+      <c r="F36">
+        <v>764.7959999999999</v>
+      </c>
+      <c r="G36">
+        <v>294.4</v>
+      </c>
+      <c r="H36">
+        <v>2198.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>57.5</v>
+      </c>
+      <c r="K36">
+        <v>22.9</v>
+      </c>
+      <c r="L36">
+        <v>34.6</v>
+      </c>
+      <c r="M36">
+        <v>182.6332848</v>
+      </c>
+      <c r="N36">
+        <v>-148.0332848</v>
+      </c>
+      <c r="O36">
+        <v>-37.0083212</v>
+      </c>
+      <c r="P36">
+        <v>-111.0249636</v>
+      </c>
+      <c r="Q36">
+        <v>-88.1249636</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.172802056775315</v>
+      </c>
+      <c r="T36">
+        <v>1.928415399985227</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.04736267000548413</v>
+      </c>
+      <c r="W36">
+        <v>0.2274897944026904</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.1894506800219364</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1933958875686226</v>
+      </c>
+      <c r="C37">
+        <v>638.0480712896338</v>
+      </c>
+      <c r="D37">
+        <v>1130.938071289634</v>
+      </c>
+      <c r="E37">
+        <v>736.5899999999999</v>
+      </c>
+      <c r="F37">
+        <v>787.29</v>
+      </c>
+      <c r="G37">
+        <v>294.4</v>
+      </c>
+      <c r="H37">
+        <v>2198.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>57.5</v>
+      </c>
+      <c r="K37">
+        <v>22.9</v>
+      </c>
+      <c r="L37">
+        <v>34.6</v>
+      </c>
+      <c r="M37">
+        <v>188.004852</v>
+      </c>
+      <c r="N37">
+        <v>-153.404852</v>
+      </c>
+      <c r="O37">
+        <v>-38.351213</v>
+      </c>
+      <c r="P37">
+        <v>-115.053639</v>
+      </c>
+      <c r="Q37">
+        <v>-92.153639</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1748636268795506</v>
+      </c>
+      <c r="T37">
+        <v>1.958083329215769</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.0460094508624703</v>
+      </c>
+      <c r="W37">
+        <v>0.2278129431340421</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1840378034498812</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1953958875686226</v>
+      </c>
+      <c r="C38">
+        <v>601.1100384500867</v>
+      </c>
+      <c r="D38">
+        <v>1116.494038450086</v>
+      </c>
+      <c r="E38">
+        <v>759.0839999999998</v>
+      </c>
+      <c r="F38">
+        <v>809.7839999999999</v>
+      </c>
+      <c r="G38">
+        <v>294.4</v>
+      </c>
+      <c r="H38">
+        <v>2198.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>57.5</v>
+      </c>
+      <c r="K38">
+        <v>22.9</v>
+      </c>
+      <c r="L38">
+        <v>34.6</v>
+      </c>
+      <c r="M38">
+        <v>193.3764192</v>
+      </c>
+      <c r="N38">
+        <v>-158.7764192</v>
+      </c>
+      <c r="O38">
+        <v>-39.6941048</v>
+      </c>
+      <c r="P38">
+        <v>-119.0823144</v>
+      </c>
+      <c r="Q38">
+        <v>-96.1823144</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1769896210495435</v>
+      </c>
+      <c r="T38">
+        <v>1.988678381234765</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04473141056073501</v>
+      </c>
+      <c r="W38">
+        <v>0.2281181391580965</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1789256422429401</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1973958875686226</v>
+      </c>
+      <c r="C39">
+        <v>564.5363034006258</v>
+      </c>
+      <c r="D39">
+        <v>1102.414303400626</v>
+      </c>
+      <c r="E39">
+        <v>781.5779999999999</v>
+      </c>
+      <c r="F39">
+        <v>832.2779999999999</v>
+      </c>
+      <c r="G39">
+        <v>294.4</v>
+      </c>
+      <c r="H39">
+        <v>2198.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>57.5</v>
+      </c>
+      <c r="K39">
+        <v>22.9</v>
+      </c>
+      <c r="L39">
+        <v>34.6</v>
+      </c>
+      <c r="M39">
+        <v>198.7479864</v>
+      </c>
+      <c r="N39">
+        <v>-164.1479864</v>
+      </c>
+      <c r="O39">
+        <v>-41.03699659999999</v>
+      </c>
+      <c r="P39">
+        <v>-123.1109898</v>
+      </c>
+      <c r="Q39">
+        <v>-100.2109898</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.179183107097949</v>
+      </c>
+      <c r="T39">
+        <v>2.020244704746428</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04352245351855299</v>
+      </c>
+      <c r="W39">
+        <v>0.2284068380997696</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1740898140742119</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1993958875686226</v>
+      </c>
+      <c r="C40">
+        <v>528.3132556635902</v>
+      </c>
+      <c r="D40">
+        <v>1088.68525566359</v>
+      </c>
+      <c r="E40">
+        <v>804.0719999999998</v>
+      </c>
+      <c r="F40">
+        <v>854.7719999999998</v>
+      </c>
+      <c r="G40">
+        <v>294.4</v>
+      </c>
+      <c r="H40">
+        <v>2198.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>57.5</v>
+      </c>
+      <c r="K40">
+        <v>22.9</v>
+      </c>
+      <c r="L40">
+        <v>34.6</v>
+      </c>
+      <c r="M40">
+        <v>204.1195536</v>
+      </c>
+      <c r="N40">
+        <v>-169.5195536</v>
+      </c>
+      <c r="O40">
+        <v>-42.37988839999999</v>
+      </c>
+      <c r="P40">
+        <v>-127.1396652</v>
+      </c>
+      <c r="Q40">
+        <v>-104.2396652</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1814473507608192</v>
+      </c>
+      <c r="T40">
+        <v>2.052829296758467</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.04237712579438054</v>
+      </c>
+      <c r="W40">
+        <v>0.2286803423603019</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1695085031775222</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2013958875686226</v>
+      </c>
+      <c r="C41">
+        <v>492.4279544204503</v>
+      </c>
+      <c r="D41">
+        <v>1075.29395442045</v>
+      </c>
+      <c r="E41">
+        <v>826.5659999999998</v>
+      </c>
+      <c r="F41">
+        <v>877.2659999999998</v>
+      </c>
+      <c r="G41">
+        <v>294.4</v>
+      </c>
+      <c r="H41">
+        <v>2198.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>57.5</v>
+      </c>
+      <c r="K41">
+        <v>22.9</v>
+      </c>
+      <c r="L41">
+        <v>34.6</v>
+      </c>
+      <c r="M41">
+        <v>209.4911208</v>
+      </c>
+      <c r="N41">
+        <v>-174.8911208</v>
+      </c>
+      <c r="O41">
+        <v>-43.7227802</v>
+      </c>
+      <c r="P41">
+        <v>-131.1683406</v>
+      </c>
+      <c r="Q41">
+        <v>-108.2683406</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1837858319208326</v>
+      </c>
+      <c r="T41">
+        <v>2.086482236049589</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04129053282529386</v>
+      </c>
+      <c r="W41">
+        <v>0.2289398207613199</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1651621313011754</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2033958875686226</v>
+      </c>
+      <c r="C42">
+        <v>456.8680878267645</v>
+      </c>
+      <c r="D42">
+        <v>1062.228087826764</v>
+      </c>
+      <c r="E42">
+        <v>849.0599999999998</v>
+      </c>
+      <c r="F42">
+        <v>899.7599999999999</v>
+      </c>
+      <c r="G42">
+        <v>294.4</v>
+      </c>
+      <c r="H42">
+        <v>2198.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>57.5</v>
+      </c>
+      <c r="K42">
+        <v>22.9</v>
+      </c>
+      <c r="L42">
+        <v>34.6</v>
+      </c>
+      <c r="M42">
+        <v>214.862688</v>
+      </c>
+      <c r="N42">
+        <v>-180.262688</v>
+      </c>
+      <c r="O42">
+        <v>-45.065672</v>
+      </c>
+      <c r="P42">
+        <v>-135.197016</v>
+      </c>
+      <c r="Q42">
+        <v>-112.297016</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1862022624528465</v>
+      </c>
+      <c r="T42">
+        <v>2.12125693998375</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04025826950466151</v>
+      </c>
+      <c r="W42">
+        <v>0.2291863252422869</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.161033078018646</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2053958875686226</v>
+      </c>
+      <c r="C43">
+        <v>421.6219352577018</v>
+      </c>
+      <c r="D43">
+        <v>1049.475935257702</v>
+      </c>
+      <c r="E43">
+        <v>871.5539999999999</v>
+      </c>
+      <c r="F43">
+        <v>922.2539999999999</v>
+      </c>
+      <c r="G43">
+        <v>294.4</v>
+      </c>
+      <c r="H43">
+        <v>2198.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>57.5</v>
+      </c>
+      <c r="K43">
+        <v>22.9</v>
+      </c>
+      <c r="L43">
+        <v>34.6</v>
+      </c>
+      <c r="M43">
+        <v>220.2342552</v>
+      </c>
+      <c r="N43">
+        <v>-185.6342552</v>
+      </c>
+      <c r="O43">
+        <v>-46.4085638</v>
+      </c>
+      <c r="P43">
+        <v>-139.2256914</v>
+      </c>
+      <c r="Q43">
+        <v>-116.3256914</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1887006058842506</v>
+      </c>
+      <c r="T43">
+        <v>2.157210447441101</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.0392763604923527</v>
+      </c>
+      <c r="W43">
+        <v>0.2294208051144262</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1571054419694108</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2073958875686226</v>
+      </c>
+      <c r="C44">
+        <v>386.6783322407771</v>
+      </c>
+      <c r="D44">
+        <v>1037.026332240777</v>
+      </c>
+      <c r="E44">
+        <v>894.0479999999998</v>
+      </c>
+      <c r="F44">
+        <v>944.7479999999998</v>
+      </c>
+      <c r="G44">
+        <v>294.4</v>
+      </c>
+      <c r="H44">
+        <v>2198.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>57.5</v>
+      </c>
+      <c r="K44">
+        <v>22.9</v>
+      </c>
+      <c r="L44">
+        <v>34.6</v>
+      </c>
+      <c r="M44">
+        <v>225.6058224</v>
+      </c>
+      <c r="N44">
+        <v>-191.0058224</v>
+      </c>
+      <c r="O44">
+        <v>-47.75145559999999</v>
+      </c>
+      <c r="P44">
+        <v>-143.2543668</v>
+      </c>
+      <c r="Q44">
+        <v>-120.3543668</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1912850990891515</v>
+      </c>
+      <c r="T44">
+        <v>2.194403731017672</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.03834120905205859</v>
+      </c>
+      <c r="W44">
+        <v>0.2296441192783684</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1533648362082343</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2093958875686226</v>
+      </c>
+      <c r="C45">
+        <v>352.0266378552823</v>
+      </c>
+      <c r="D45">
+        <v>1024.868637855282</v>
+      </c>
+      <c r="E45">
+        <v>916.5419999999998</v>
+      </c>
+      <c r="F45">
+        <v>967.2419999999998</v>
+      </c>
+      <c r="G45">
+        <v>294.4</v>
+      </c>
+      <c r="H45">
+        <v>2198.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>57.5</v>
+      </c>
+      <c r="K45">
+        <v>22.9</v>
+      </c>
+      <c r="L45">
+        <v>34.6</v>
+      </c>
+      <c r="M45">
+        <v>230.9773896</v>
+      </c>
+      <c r="N45">
+        <v>-196.3773896</v>
+      </c>
+      <c r="O45">
+        <v>-49.0943474</v>
+      </c>
+      <c r="P45">
+        <v>-147.2830422</v>
+      </c>
+      <c r="Q45">
+        <v>-124.3830422</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1939602762661542</v>
+      </c>
+      <c r="T45">
+        <v>2.232902042088157</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03744955302759211</v>
+      </c>
+      <c r="W45">
+        <v>0.229857046737011</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1497982121103684</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2113958875686227</v>
+      </c>
+      <c r="C46">
+        <v>317.6567043983182</v>
+      </c>
+      <c r="D46">
+        <v>1012.992704398318</v>
+      </c>
+      <c r="E46">
+        <v>939.0359999999998</v>
+      </c>
+      <c r="F46">
+        <v>989.7359999999999</v>
+      </c>
+      <c r="G46">
+        <v>294.4</v>
+      </c>
+      <c r="H46">
+        <v>2198.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>57.5</v>
+      </c>
+      <c r="K46">
+        <v>22.9</v>
+      </c>
+      <c r="L46">
+        <v>34.6</v>
+      </c>
+      <c r="M46">
+        <v>236.3489568</v>
+      </c>
+      <c r="N46">
+        <v>-201.7489568</v>
+      </c>
+      <c r="O46">
+        <v>-50.4372392</v>
+      </c>
+      <c r="P46">
+        <v>-151.3117176</v>
+      </c>
+      <c r="Q46">
+        <v>-128.4117176</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1967309954851927</v>
+      </c>
+      <c r="T46">
+        <v>2.272775292839732</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03659842682241955</v>
+      </c>
+      <c r="W46">
+        <v>0.2300602956748062</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1463937072896782</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2133958875686226</v>
+      </c>
+      <c r="C47">
+        <v>283.5588491356888</v>
+      </c>
+      <c r="D47">
+        <v>1001.388849135689</v>
+      </c>
+      <c r="E47">
+        <v>961.5299999999999</v>
+      </c>
+      <c r="F47">
+        <v>1012.23</v>
+      </c>
+      <c r="G47">
+        <v>294.4</v>
+      </c>
+      <c r="H47">
+        <v>2198.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>57.5</v>
+      </c>
+      <c r="K47">
+        <v>22.9</v>
+      </c>
+      <c r="L47">
+        <v>34.6</v>
+      </c>
+      <c r="M47">
+        <v>241.720524</v>
+      </c>
+      <c r="N47">
+        <v>-207.120524</v>
+      </c>
+      <c r="O47">
+        <v>-51.780131</v>
+      </c>
+      <c r="P47">
+        <v>-155.340393</v>
+      </c>
+      <c r="Q47">
+        <v>-132.440393</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.199602468130378</v>
+      </c>
+      <c r="T47">
+        <v>2.314098479982272</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03578512844858801</v>
+      </c>
+      <c r="W47">
+        <v>0.2302545113264772</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.143140513794352</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2153958875686226</v>
+      </c>
+      <c r="C48">
+        <v>249.723827972367</v>
+      </c>
+      <c r="D48">
+        <v>990.0478279723669</v>
+      </c>
+      <c r="E48">
+        <v>984.0239999999999</v>
+      </c>
+      <c r="F48">
+        <v>1034.724</v>
+      </c>
+      <c r="G48">
+        <v>294.4</v>
+      </c>
+      <c r="H48">
+        <v>2198.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>57.5</v>
+      </c>
+      <c r="K48">
+        <v>22.9</v>
+      </c>
+      <c r="L48">
+        <v>34.6</v>
+      </c>
+      <c r="M48">
+        <v>247.0920912</v>
+      </c>
+      <c r="N48">
+        <v>-212.4920912</v>
+      </c>
+      <c r="O48">
+        <v>-53.1230228</v>
+      </c>
+      <c r="P48">
+        <v>-159.3690684</v>
+      </c>
+      <c r="Q48">
+        <v>-136.4690684</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2025802916142738</v>
+      </c>
+      <c r="T48">
+        <v>2.356952155537499</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03500719087361871</v>
+      </c>
+      <c r="W48">
+        <v>0.2304402828193799</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1400287634944748</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2173958875686226</v>
+      </c>
+      <c r="C49">
+        <v>216.1428108920666</v>
+      </c>
+      <c r="D49">
+        <v>978.9608108920664</v>
+      </c>
+      <c r="E49">
+        <v>1006.518</v>
+      </c>
+      <c r="F49">
+        <v>1057.218</v>
+      </c>
+      <c r="G49">
+        <v>294.4</v>
+      </c>
+      <c r="H49">
+        <v>2198.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>57.5</v>
+      </c>
+      <c r="K49">
+        <v>22.9</v>
+      </c>
+      <c r="L49">
+        <v>34.6</v>
+      </c>
+      <c r="M49">
+        <v>252.4636584</v>
+      </c>
+      <c r="N49">
+        <v>-217.8636584</v>
+      </c>
+      <c r="O49">
+        <v>-54.4659146</v>
+      </c>
+      <c r="P49">
+        <v>-163.3977438</v>
+      </c>
+      <c r="Q49">
+        <v>-140.4977438</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2056704857956752</v>
+      </c>
+      <c r="T49">
+        <v>2.401422950924999</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03426235702524384</v>
+      </c>
+      <c r="W49">
+        <v>0.2306181491423718</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1370494281009753</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2193958875686226</v>
+      </c>
+      <c r="C50">
+        <v>182.8073590287725</v>
+      </c>
+      <c r="D50">
+        <v>968.1193590287721</v>
+      </c>
+      <c r="E50">
+        <v>1029.012</v>
+      </c>
+      <c r="F50">
+        <v>1079.712</v>
+      </c>
+      <c r="G50">
+        <v>294.4</v>
+      </c>
+      <c r="H50">
+        <v>2198.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>57.5</v>
+      </c>
+      <c r="K50">
+        <v>22.9</v>
+      </c>
+      <c r="L50">
+        <v>34.6</v>
+      </c>
+      <c r="M50">
+        <v>257.8352255999999</v>
+      </c>
+      <c r="N50">
+        <v>-223.2352255999999</v>
+      </c>
+      <c r="O50">
+        <v>-55.80880639999999</v>
+      </c>
+      <c r="P50">
+        <v>-167.4264192</v>
+      </c>
+      <c r="Q50">
+        <v>-144.5264192</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2088795335994382</v>
+      </c>
+      <c r="T50">
+        <v>2.447604161519711</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03354855792055127</v>
+      </c>
+      <c r="W50">
+        <v>0.2307886043685724</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.134194231682205</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2213958875686226</v>
+      </c>
+      <c r="C51">
+        <v>149.7094032451027</v>
+      </c>
+      <c r="D51">
+        <v>957.5154032451027</v>
+      </c>
+      <c r="E51">
+        <v>1051.506</v>
+      </c>
+      <c r="F51">
+        <v>1102.206</v>
+      </c>
+      <c r="G51">
+        <v>294.4</v>
+      </c>
+      <c r="H51">
+        <v>2198.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>57.5</v>
+      </c>
+      <c r="K51">
+        <v>22.9</v>
+      </c>
+      <c r="L51">
+        <v>34.6</v>
+      </c>
+      <c r="M51">
+        <v>263.2067928</v>
+      </c>
+      <c r="N51">
+        <v>-228.6067928</v>
+      </c>
+      <c r="O51">
+        <v>-57.15169820000001</v>
+      </c>
+      <c r="P51">
+        <v>-171.4550946</v>
+      </c>
+      <c r="Q51">
+        <v>-148.5550946</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2122144264151135</v>
+      </c>
+      <c r="T51">
+        <v>2.495596399980882</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03286389347319307</v>
+      </c>
+      <c r="W51">
+        <v>0.2309521022386015</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1314555738927723</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2233958875686226</v>
+      </c>
+      <c r="C52">
+        <v>116.8412241032283</v>
+      </c>
+      <c r="D52">
+        <v>947.1412241032282</v>
+      </c>
+      <c r="E52">
+        <v>1074</v>
+      </c>
+      <c r="F52">
+        <v>1124.7</v>
+      </c>
+      <c r="G52">
+        <v>294.4</v>
+      </c>
+      <c r="H52">
+        <v>2198.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>57.5</v>
+      </c>
+      <c r="K52">
+        <v>22.9</v>
+      </c>
+      <c r="L52">
+        <v>34.6</v>
+      </c>
+      <c r="M52">
+        <v>268.57836</v>
+      </c>
+      <c r="N52">
+        <v>-233.97836</v>
+      </c>
+      <c r="O52">
+        <v>-58.49459</v>
+      </c>
+      <c r="P52">
+        <v>-175.48377</v>
+      </c>
+      <c r="Q52">
+        <v>-152.58377</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2156827149434157</v>
+      </c>
+      <c r="T52">
+        <v>2.545508327980499</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03220661560372921</v>
+      </c>
+      <c r="W52">
+        <v>0.2311090601938295</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1288264624149168</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2253958875686226</v>
+      </c>
+      <c r="C53">
+        <v>84.19543312385963</v>
+      </c>
+      <c r="D53">
+        <v>936.9894331238594</v>
+      </c>
+      <c r="E53">
+        <v>1096.494</v>
+      </c>
+      <c r="F53">
+        <v>1147.194</v>
+      </c>
+      <c r="G53">
+        <v>294.4</v>
+      </c>
+      <c r="H53">
+        <v>2198.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>57.5</v>
+      </c>
+      <c r="K53">
+        <v>22.9</v>
+      </c>
+      <c r="L53">
+        <v>34.6</v>
+      </c>
+      <c r="M53">
+        <v>273.9499271999999</v>
+      </c>
+      <c r="N53">
+        <v>-239.3499271999999</v>
+      </c>
+      <c r="O53">
+        <v>-59.83748179999998</v>
+      </c>
+      <c r="P53">
+        <v>-179.5124454</v>
+      </c>
+      <c r="Q53">
+        <v>-156.6124454</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2192925662687916</v>
+      </c>
+      <c r="T53">
+        <v>2.597457477531122</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03157511333698942</v>
+      </c>
+      <c r="W53">
+        <v>0.2312598629351269</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1263004533479577</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2273958875686226</v>
+      </c>
+      <c r="C54">
+        <v>51.76495523769222</v>
+      </c>
+      <c r="D54">
+        <v>927.0529552376921</v>
+      </c>
+      <c r="E54">
+        <v>1118.988</v>
+      </c>
+      <c r="F54">
+        <v>1169.688</v>
+      </c>
+      <c r="G54">
+        <v>294.4</v>
+      </c>
+      <c r="H54">
+        <v>2198.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>57.5</v>
+      </c>
+      <c r="K54">
+        <v>22.9</v>
+      </c>
+      <c r="L54">
+        <v>34.6</v>
+      </c>
+      <c r="M54">
+        <v>279.3214944</v>
+      </c>
+      <c r="N54">
+        <v>-244.7214944</v>
+      </c>
+      <c r="O54">
+        <v>-61.1803736</v>
+      </c>
+      <c r="P54">
+        <v>-183.5411208</v>
+      </c>
+      <c r="Q54">
+        <v>-160.6411208</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2230528280660581</v>
+      </c>
+      <c r="T54">
+        <v>2.651571174979687</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03096789961897039</v>
+      </c>
+      <c r="W54">
+        <v>0.2314048655709899</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1238715984758816</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2293958875686226</v>
+      </c>
+      <c r="C55">
+        <v>19.54301234171635</v>
+      </c>
+      <c r="D55">
+        <v>917.3250123417163</v>
+      </c>
+      <c r="E55">
+        <v>1141.482</v>
+      </c>
+      <c r="F55">
+        <v>1192.182</v>
+      </c>
+      <c r="G55">
+        <v>294.4</v>
+      </c>
+      <c r="H55">
+        <v>2198.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>57.5</v>
+      </c>
+      <c r="K55">
+        <v>22.9</v>
+      </c>
+      <c r="L55">
+        <v>34.6</v>
+      </c>
+      <c r="M55">
+        <v>284.6930616</v>
+      </c>
+      <c r="N55">
+        <v>-250.0930616</v>
+      </c>
+      <c r="O55">
+        <v>-62.52326539999999</v>
+      </c>
+      <c r="P55">
+        <v>-187.5697962</v>
+      </c>
+      <c r="Q55">
+        <v>-164.6697962</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2269731010036338</v>
+      </c>
+      <c r="T55">
+        <v>2.707987582957978</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03038359962615963</v>
+      </c>
+      <c r="W55">
+        <v>0.2315443964092731</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1215343985046385</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2313958875686226</v>
+      </c>
+      <c r="C56">
+        <v>-12.4768921199236</v>
+      </c>
+      <c r="D56">
+        <v>907.7991078800763</v>
+      </c>
+      <c r="E56">
+        <v>1163.976</v>
+      </c>
+      <c r="F56">
+        <v>1214.676</v>
+      </c>
+      <c r="G56">
+        <v>294.4</v>
+      </c>
+      <c r="H56">
+        <v>2198.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>57.5</v>
+      </c>
+      <c r="K56">
+        <v>22.9</v>
+      </c>
+      <c r="L56">
+        <v>34.6</v>
+      </c>
+      <c r="M56">
+        <v>290.0646288</v>
+      </c>
+      <c r="N56">
+        <v>-255.4646288</v>
+      </c>
+      <c r="O56">
+        <v>-63.8661572</v>
+      </c>
+      <c r="P56">
+        <v>-191.5984716</v>
+      </c>
+      <c r="Q56">
+        <v>-168.6984716</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2310638205906693</v>
+      </c>
+      <c r="T56">
+        <v>2.766856878239673</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.02982094037382334</v>
+      </c>
+      <c r="W56">
+        <v>0.231678759438731</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1192837614952933</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2333958875686226</v>
+      </c>
+      <c r="C57">
+        <v>-44.3009876242279</v>
+      </c>
+      <c r="D57">
+        <v>898.4690123757719</v>
+      </c>
+      <c r="E57">
+        <v>1186.47</v>
+      </c>
+      <c r="F57">
+        <v>1237.17</v>
+      </c>
+      <c r="G57">
+        <v>294.4</v>
+      </c>
+      <c r="H57">
+        <v>2198.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>57.5</v>
+      </c>
+      <c r="K57">
+        <v>22.9</v>
+      </c>
+      <c r="L57">
+        <v>34.6</v>
+      </c>
+      <c r="M57">
+        <v>295.436196</v>
+      </c>
+      <c r="N57">
+        <v>-260.836196</v>
+      </c>
+      <c r="O57">
+        <v>-65.20904899999999</v>
+      </c>
+      <c r="P57">
+        <v>-195.627147</v>
+      </c>
+      <c r="Q57">
+        <v>-172.727147</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2353363499371287</v>
+      </c>
+      <c r="T57">
+        <v>2.828342586645</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.02927874145793564</v>
+      </c>
+      <c r="W57">
+        <v>0.231808236539845</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1171149658317426</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2353958875686226</v>
+      </c>
+      <c r="C58">
+        <v>-75.93525015451269</v>
+      </c>
+      <c r="D58">
+        <v>889.3287498454873</v>
+      </c>
+      <c r="E58">
+        <v>1208.964</v>
+      </c>
+      <c r="F58">
+        <v>1259.664</v>
+      </c>
+      <c r="G58">
+        <v>294.4</v>
+      </c>
+      <c r="H58">
+        <v>2198.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>57.5</v>
+      </c>
+      <c r="K58">
+        <v>22.9</v>
+      </c>
+      <c r="L58">
+        <v>34.6</v>
+      </c>
+      <c r="M58">
+        <v>300.8077632</v>
+      </c>
+      <c r="N58">
+        <v>-266.2077632</v>
+      </c>
+      <c r="O58">
+        <v>-66.5519408</v>
+      </c>
+      <c r="P58">
+        <v>-199.6558224</v>
+      </c>
+      <c r="Q58">
+        <v>-176.7558224</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2398030851629725</v>
+      </c>
+      <c r="T58">
+        <v>2.892623099977841</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02875590678904394</v>
+      </c>
+      <c r="W58">
+        <v>0.2319330894587763</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1150236271561758</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2373958875686226</v>
+      </c>
+      <c r="C59">
+        <v>-107.3854149647048</v>
+      </c>
+      <c r="D59">
+        <v>880.3725850352952</v>
+      </c>
+      <c r="E59">
+        <v>1231.458</v>
+      </c>
+      <c r="F59">
+        <v>1282.158</v>
+      </c>
+      <c r="G59">
+        <v>294.4</v>
+      </c>
+      <c r="H59">
+        <v>2198.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>57.5</v>
+      </c>
+      <c r="K59">
+        <v>22.9</v>
+      </c>
+      <c r="L59">
+        <v>34.6</v>
+      </c>
+      <c r="M59">
+        <v>306.1793304</v>
+      </c>
+      <c r="N59">
+        <v>-271.5793303999999</v>
+      </c>
+      <c r="O59">
+        <v>-67.89483259999999</v>
+      </c>
+      <c r="P59">
+        <v>-203.6844978</v>
+      </c>
+      <c r="Q59">
+        <v>-180.7844978</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2444775755155998</v>
+      </c>
+      <c r="T59">
+        <v>2.959893404628488</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02825141719625369</v>
+      </c>
+      <c r="W59">
+        <v>0.2320535615735346</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1130056687850148</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2393958875686226</v>
+      </c>
+      <c r="C60">
+        <v>-138.6569885800573</v>
+      </c>
+      <c r="D60">
+        <v>871.5950114199424</v>
+      </c>
+      <c r="E60">
+        <v>1253.952</v>
+      </c>
+      <c r="F60">
+        <v>1304.652</v>
+      </c>
+      <c r="G60">
+        <v>294.4</v>
+      </c>
+      <c r="H60">
+        <v>2198.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>57.5</v>
+      </c>
+      <c r="K60">
+        <v>22.9</v>
+      </c>
+      <c r="L60">
+        <v>34.6</v>
+      </c>
+      <c r="M60">
+        <v>311.5508975999999</v>
+      </c>
+      <c r="N60">
+        <v>-276.9508975999999</v>
+      </c>
+      <c r="O60">
+        <v>-69.23772439999998</v>
+      </c>
+      <c r="P60">
+        <v>-207.7131731999999</v>
+      </c>
+      <c r="Q60">
+        <v>-184.8131731999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2493746606469235</v>
+      </c>
+      <c r="T60">
+        <v>3.030367057119642</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02776432379631829</v>
+      </c>
+      <c r="W60">
+        <v>0.2321698794774392</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1110572951852732</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2413958875686226</v>
+      </c>
+      <c r="C61">
+        <v>-169.7552600870467</v>
+      </c>
+      <c r="D61">
+        <v>862.9907399129531</v>
+      </c>
+      <c r="E61">
+        <v>1276.446</v>
+      </c>
+      <c r="F61">
+        <v>1327.146</v>
+      </c>
+      <c r="G61">
+        <v>294.4</v>
+      </c>
+      <c r="H61">
+        <v>2198.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>57.5</v>
+      </c>
+      <c r="K61">
+        <v>22.9</v>
+      </c>
+      <c r="L61">
+        <v>34.6</v>
+      </c>
+      <c r="M61">
+        <v>316.9224647999999</v>
+      </c>
+      <c r="N61">
+        <v>-282.3224647999999</v>
+      </c>
+      <c r="O61">
+        <v>-70.58061619999998</v>
+      </c>
+      <c r="P61">
+        <v>-211.7418485999999</v>
+      </c>
+      <c r="Q61">
+        <v>-188.8418485999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2545106279797753</v>
+      </c>
+      <c r="T61">
+        <v>3.104278448756706</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02729374203705865</v>
+      </c>
+      <c r="W61">
+        <v>0.2322822544015504</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1091749681482347</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2433958875686226</v>
+      </c>
+      <c r="C62">
+        <v>-200.685311761091</v>
+      </c>
+      <c r="D62">
+        <v>854.5546882389087</v>
+      </c>
+      <c r="E62">
+        <v>1298.94</v>
+      </c>
+      <c r="F62">
+        <v>1349.64</v>
+      </c>
+      <c r="G62">
+        <v>294.4</v>
+      </c>
+      <c r="H62">
+        <v>2198.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>57.5</v>
+      </c>
+      <c r="K62">
+        <v>22.9</v>
+      </c>
+      <c r="L62">
+        <v>34.6</v>
+      </c>
+      <c r="M62">
+        <v>322.294032</v>
+      </c>
+      <c r="N62">
+        <v>-287.6940319999999</v>
+      </c>
+      <c r="O62">
+        <v>-71.92350799999998</v>
+      </c>
+      <c r="P62">
+        <v>-215.770524</v>
+      </c>
+      <c r="Q62">
+        <v>-192.870524</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2599033936792696</v>
+      </c>
+      <c r="T62">
+        <v>3.181885409975624</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02683884633644101</v>
+      </c>
+      <c r="W62">
+        <v>0.2323908834948579</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1073553853457641</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2453958875686226</v>
+      </c>
+      <c r="C63">
+        <v>-231.4520290769676</v>
+      </c>
+      <c r="D63">
+        <v>846.2819709230321</v>
+      </c>
+      <c r="E63">
+        <v>1321.434</v>
+      </c>
+      <c r="F63">
+        <v>1372.134</v>
+      </c>
+      <c r="G63">
+        <v>294.4</v>
+      </c>
+      <c r="H63">
+        <v>2198.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>57.5</v>
+      </c>
+      <c r="K63">
+        <v>22.9</v>
+      </c>
+      <c r="L63">
+        <v>34.6</v>
+      </c>
+      <c r="M63">
+        <v>327.6655992</v>
+      </c>
+      <c r="N63">
+        <v>-293.0655992</v>
+      </c>
+      <c r="O63">
+        <v>-73.26639979999999</v>
+      </c>
+      <c r="P63">
+        <v>-219.7991994</v>
+      </c>
+      <c r="Q63">
+        <v>-196.8991994</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2655727114659177</v>
+      </c>
+      <c r="T63">
+        <v>3.263472215359614</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02639886524895837</v>
+      </c>
+      <c r="W63">
+        <v>0.2324959509785487</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1055954609958335</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2473958875686226</v>
+      </c>
+      <c r="C64">
+        <v>-262.0601101433513</v>
+      </c>
+      <c r="D64">
+        <v>838.1678898566485</v>
+      </c>
+      <c r="E64">
+        <v>1343.928</v>
+      </c>
+      <c r="F64">
+        <v>1394.628</v>
+      </c>
+      <c r="G64">
+        <v>294.4</v>
+      </c>
+      <c r="H64">
+        <v>2198.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>57.5</v>
+      </c>
+      <c r="K64">
+        <v>22.9</v>
+      </c>
+      <c r="L64">
+        <v>34.6</v>
+      </c>
+      <c r="M64">
+        <v>333.0371663999999</v>
+      </c>
+      <c r="N64">
+        <v>-298.4371663999999</v>
+      </c>
+      <c r="O64">
+        <v>-74.60929159999998</v>
+      </c>
+      <c r="P64">
+        <v>-223.8278747999999</v>
+      </c>
+      <c r="Q64">
+        <v>-200.9278747999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2715404143992313</v>
+      </c>
+      <c r="T64">
+        <v>3.349353063132236</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02597307709978162</v>
+      </c>
+      <c r="W64">
+        <v>0.2325976291885722</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1038923083991266</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2493958875686226</v>
+      </c>
+      <c r="C65">
+        <v>-292.514074599766</v>
+      </c>
+      <c r="D65">
+        <v>830.2079254002338</v>
+      </c>
+      <c r="E65">
+        <v>1366.422</v>
+      </c>
+      <c r="F65">
+        <v>1417.122</v>
+      </c>
+      <c r="G65">
+        <v>294.4</v>
+      </c>
+      <c r="H65">
+        <v>2198.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>57.5</v>
+      </c>
+      <c r="K65">
+        <v>22.9</v>
+      </c>
+      <c r="L65">
+        <v>34.6</v>
+      </c>
+      <c r="M65">
+        <v>338.4087336</v>
+      </c>
+      <c r="N65">
+        <v>-303.8087336</v>
+      </c>
+      <c r="O65">
+        <v>-75.9521834</v>
+      </c>
+      <c r="P65">
+        <v>-227.8565502</v>
+      </c>
+      <c r="Q65">
+        <v>-204.9565502</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2778306958694808</v>
+      </c>
+      <c r="T65">
+        <v>3.439876118892567</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02556080603470572</v>
+      </c>
+      <c r="W65">
+        <v>0.2326960795189123</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1022432241388229</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2513958875686226</v>
+      </c>
+      <c r="C66">
+        <v>-322.8182720113434</v>
+      </c>
+      <c r="D66">
+        <v>822.3977279886565</v>
+      </c>
+      <c r="E66">
+        <v>1388.916</v>
+      </c>
+      <c r="F66">
+        <v>1439.616</v>
+      </c>
+      <c r="G66">
+        <v>294.4</v>
+      </c>
+      <c r="H66">
+        <v>2198.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>57.5</v>
+      </c>
+      <c r="K66">
+        <v>22.9</v>
+      </c>
+      <c r="L66">
+        <v>34.6</v>
+      </c>
+      <c r="M66">
+        <v>343.7803008</v>
+      </c>
+      <c r="N66">
+        <v>-309.1803007999999</v>
+      </c>
+      <c r="O66">
+        <v>-77.29507519999999</v>
+      </c>
+      <c r="P66">
+        <v>-231.8852256</v>
+      </c>
+      <c r="Q66">
+        <v>-208.9852255999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2844704374214108</v>
+      </c>
+      <c r="T66">
+        <v>3.535428233306249</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02516141844041345</v>
+      </c>
+      <c r="W66">
+        <v>0.2327914532764293</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1006456737616539</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2533958875686226</v>
+      </c>
+      <c r="C67">
+        <v>-352.9768897941578</v>
+      </c>
+      <c r="D67">
+        <v>814.733110205842</v>
+      </c>
+      <c r="E67">
+        <v>1411.41</v>
+      </c>
+      <c r="F67">
+        <v>1462.11</v>
+      </c>
+      <c r="G67">
+        <v>294.4</v>
+      </c>
+      <c r="H67">
+        <v>2198.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>57.5</v>
+      </c>
+      <c r="K67">
+        <v>22.9</v>
+      </c>
+      <c r="L67">
+        <v>34.6</v>
+      </c>
+      <c r="M67">
+        <v>349.151868</v>
+      </c>
+      <c r="N67">
+        <v>-314.551868</v>
+      </c>
+      <c r="O67">
+        <v>-78.63796699999999</v>
+      </c>
+      <c r="P67">
+        <v>-235.913901</v>
+      </c>
+      <c r="Q67">
+        <v>-213.0139009999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2914895927763083</v>
+      </c>
+      <c r="T67">
+        <v>3.636440468543571</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02477431969517632</v>
+      </c>
+      <c r="W67">
+        <v>0.2328838924567919</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.09909727878070529</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2553958875686226</v>
+      </c>
+      <c r="C68">
+        <v>-382.9939607014735</v>
+      </c>
+      <c r="D68">
+        <v>807.2100392985265</v>
+      </c>
+      <c r="E68">
+        <v>1433.904</v>
+      </c>
+      <c r="F68">
+        <v>1484.604</v>
+      </c>
+      <c r="G68">
+        <v>294.4</v>
+      </c>
+      <c r="H68">
+        <v>2198.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>57.5</v>
+      </c>
+      <c r="K68">
+        <v>22.9</v>
+      </c>
+      <c r="L68">
+        <v>34.6</v>
+      </c>
+      <c r="M68">
+        <v>354.5234352</v>
+      </c>
+      <c r="N68">
+        <v>-319.9234352</v>
+      </c>
+      <c r="O68">
+        <v>-79.98085879999999</v>
+      </c>
+      <c r="P68">
+        <v>-239.9425764</v>
+      </c>
+      <c r="Q68">
+        <v>-217.0425764</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2989216396226703</v>
+      </c>
+      <c r="T68">
+        <v>3.743394599971323</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02439895121494637</v>
+      </c>
+      <c r="W68">
+        <v>0.2329735304498708</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.09759580485978558</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2573958875686226</v>
+      </c>
+      <c r="C69">
+        <v>-412.8733698990286</v>
+      </c>
+      <c r="D69">
+        <v>799.8246301009714</v>
+      </c>
+      <c r="E69">
+        <v>1456.398</v>
+      </c>
+      <c r="F69">
+        <v>1507.098</v>
+      </c>
+      <c r="G69">
+        <v>294.4</v>
+      </c>
+      <c r="H69">
+        <v>2198.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>57.5</v>
+      </c>
+      <c r="K69">
+        <v>22.9</v>
+      </c>
+      <c r="L69">
+        <v>34.6</v>
+      </c>
+      <c r="M69">
+        <v>359.8950024</v>
+      </c>
+      <c r="N69">
+        <v>-325.2950024</v>
+      </c>
+      <c r="O69">
+        <v>-81.3237506</v>
+      </c>
+      <c r="P69">
+        <v>-243.9712518</v>
+      </c>
+      <c r="Q69">
+        <v>-221.0712518</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.30680411355063</v>
+      </c>
+      <c r="T69">
+        <v>3.856830799970454</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02403478776397702</v>
+      </c>
+      <c r="W69">
+        <v>0.2330604926819623</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.09613915105590809</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2593958875686226</v>
+      </c>
+      <c r="C70">
+        <v>-442.6188616554391</v>
+      </c>
+      <c r="D70">
+        <v>792.5731383445608</v>
+      </c>
+      <c r="E70">
+        <v>1478.892</v>
+      </c>
+      <c r="F70">
+        <v>1529.592</v>
+      </c>
+      <c r="G70">
+        <v>294.4</v>
+      </c>
+      <c r="H70">
+        <v>2198.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>57.5</v>
+      </c>
+      <c r="K70">
+        <v>22.9</v>
+      </c>
+      <c r="L70">
+        <v>34.6</v>
+      </c>
+      <c r="M70">
+        <v>365.2665696</v>
+      </c>
+      <c r="N70">
+        <v>-330.6665695999999</v>
+      </c>
+      <c r="O70">
+        <v>-82.66664239999999</v>
+      </c>
+      <c r="P70">
+        <v>-247.9999271999999</v>
+      </c>
+      <c r="Q70">
+        <v>-225.0999271999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3151792420990872</v>
+      </c>
+      <c r="T70">
+        <v>3.977356762469531</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02368133500274206</v>
+      </c>
+      <c r="W70">
+        <v>0.2331448972013452</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.09472534001096833</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2613958875686226</v>
+      </c>
+      <c r="C71">
+        <v>-472.2340456719248</v>
+      </c>
+      <c r="D71">
+        <v>785.4519543280751</v>
+      </c>
+      <c r="E71">
+        <v>1501.386</v>
+      </c>
+      <c r="F71">
+        <v>1552.086</v>
+      </c>
+      <c r="G71">
+        <v>294.4</v>
+      </c>
+      <c r="H71">
+        <v>2198.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>57.5</v>
+      </c>
+      <c r="K71">
+        <v>22.9</v>
+      </c>
+      <c r="L71">
+        <v>34.6</v>
+      </c>
+      <c r="M71">
+        <v>370.6381368</v>
+      </c>
+      <c r="N71">
+        <v>-336.0381368</v>
+      </c>
+      <c r="O71">
+        <v>-84.00953419999999</v>
+      </c>
+      <c r="P71">
+        <v>-252.0286026</v>
+      </c>
+      <c r="Q71">
+        <v>-229.1286026</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3240947015216384</v>
+      </c>
+      <c r="T71">
+        <v>4.105658593516935</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02333812724907914</v>
+      </c>
+      <c r="W71">
+        <v>0.2332268552129199</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.09335250899631664</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2633958875686226</v>
+      </c>
+      <c r="C72">
+        <v>-501.7224030738439</v>
+      </c>
+      <c r="D72">
+        <v>778.457596926156</v>
+      </c>
+      <c r="E72">
+        <v>1523.88</v>
+      </c>
+      <c r="F72">
+        <v>1574.58</v>
+      </c>
+      <c r="G72">
+        <v>294.4</v>
+      </c>
+      <c r="H72">
+        <v>2198.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>57.5</v>
+      </c>
+      <c r="K72">
+        <v>22.9</v>
+      </c>
+      <c r="L72">
+        <v>34.6</v>
+      </c>
+      <c r="M72">
+        <v>376.009704</v>
+      </c>
+      <c r="N72">
+        <v>-341.409704</v>
+      </c>
+      <c r="O72">
+        <v>-85.35242599999999</v>
+      </c>
+      <c r="P72">
+        <v>-256.057278</v>
+      </c>
+      <c r="Q72">
+        <v>-233.157278</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.333604524905693</v>
+      </c>
+      <c r="T72">
+        <v>4.2425138799675</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02300472543123515</v>
+      </c>
+      <c r="W72">
+        <v>0.2333064715670211</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.09201890172494065</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2653958875686226</v>
+      </c>
+      <c r="C73">
+        <v>-531.0872920849285</v>
+      </c>
+      <c r="D73">
+        <v>771.5867079150711</v>
+      </c>
+      <c r="E73">
+        <v>1546.374</v>
+      </c>
+      <c r="F73">
+        <v>1597.074</v>
+      </c>
+      <c r="G73">
+        <v>294.4</v>
+      </c>
+      <c r="H73">
+        <v>2198.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>57.5</v>
+      </c>
+      <c r="K73">
+        <v>22.9</v>
+      </c>
+      <c r="L73">
+        <v>34.6</v>
+      </c>
+      <c r="M73">
+        <v>381.3812711999999</v>
+      </c>
+      <c r="N73">
+        <v>-346.7812711999999</v>
+      </c>
+      <c r="O73">
+        <v>-86.69531779999997</v>
+      </c>
+      <c r="P73">
+        <v>-260.0859533999999</v>
+      </c>
+      <c r="Q73">
+        <v>-237.1859533999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.343770198178303</v>
+      </c>
+      <c r="T73">
+        <v>4.388807462035343</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02268071521389381</v>
+      </c>
+      <c r="W73">
+        <v>0.2333838452069222</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.09072286085557535</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2673958875686226</v>
+      </c>
+      <c r="C74">
+        <v>-560.3319534036582</v>
+      </c>
+      <c r="D74">
+        <v>764.8360465963415</v>
+      </c>
+      <c r="E74">
+        <v>1568.868</v>
+      </c>
+      <c r="F74">
+        <v>1619.568</v>
+      </c>
+      <c r="G74">
+        <v>294.4</v>
+      </c>
+      <c r="H74">
+        <v>2198.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>57.5</v>
+      </c>
+      <c r="K74">
+        <v>22.9</v>
+      </c>
+      <c r="L74">
+        <v>34.6</v>
+      </c>
+      <c r="M74">
+        <v>386.7528384</v>
+      </c>
+      <c r="N74">
+        <v>-352.1528384</v>
+      </c>
+      <c r="O74">
+        <v>-88.03820959999999</v>
+      </c>
+      <c r="P74">
+        <v>-264.1146288</v>
+      </c>
+      <c r="Q74">
+        <v>-241.2146288</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3546619909703853</v>
+      </c>
+      <c r="T74">
+        <v>4.545550585679463</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02236570528036751</v>
+      </c>
+      <c r="W74">
+        <v>0.2334590695790482</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.08946282112147008</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2693958875686226</v>
+      </c>
+      <c r="C75">
+        <v>-589.4595152998452</v>
+      </c>
+      <c r="D75">
+        <v>758.2024847001544</v>
+      </c>
+      <c r="E75">
+        <v>1591.362</v>
+      </c>
+      <c r="F75">
+        <v>1642.062</v>
+      </c>
+      <c r="G75">
+        <v>294.4</v>
+      </c>
+      <c r="H75">
+        <v>2198.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>57.5</v>
+      </c>
+      <c r="K75">
+        <v>22.9</v>
+      </c>
+      <c r="L75">
+        <v>34.6</v>
+      </c>
+      <c r="M75">
+        <v>392.1244055999999</v>
+      </c>
+      <c r="N75">
+        <v>-357.5244055999999</v>
+      </c>
+      <c r="O75">
+        <v>-89.38110139999998</v>
+      </c>
+      <c r="P75">
+        <v>-268.1433041999999</v>
+      </c>
+      <c r="Q75">
+        <v>-245.2433041999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3663605832285476</v>
+      </c>
+      <c r="T75">
+        <v>4.713904311074998</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02205932575597891</v>
+      </c>
+      <c r="W75">
+        <v>0.2335322330094723</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.08823730302391575</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2713958875686226</v>
+      </c>
+      <c r="C76">
+        <v>-618.4729984482863</v>
+      </c>
+      <c r="D76">
+        <v>751.6830015517136</v>
+      </c>
+      <c r="E76">
+        <v>1613.856</v>
+      </c>
+      <c r="F76">
+        <v>1664.556</v>
+      </c>
+      <c r="G76">
+        <v>294.4</v>
+      </c>
+      <c r="H76">
+        <v>2198.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>57.5</v>
+      </c>
+      <c r="K76">
+        <v>22.9</v>
+      </c>
+      <c r="L76">
+        <v>34.6</v>
+      </c>
+      <c r="M76">
+        <v>397.4959727999999</v>
+      </c>
+      <c r="N76">
+        <v>-362.8959727999999</v>
+      </c>
+      <c r="O76">
+        <v>-90.72399319999998</v>
+      </c>
+      <c r="P76">
+        <v>-272.1719795999999</v>
+      </c>
+      <c r="Q76">
+        <v>-249.2719795999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3789590671988764</v>
+      </c>
+      <c r="T76">
+        <v>4.895208323039421</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02176122675927649</v>
+      </c>
+      <c r="W76">
+        <v>0.2336034190498848</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.08704490703710599</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2733958875686226</v>
+      </c>
+      <c r="C77">
+        <v>-647.3753205151581</v>
+      </c>
+      <c r="D77">
+        <v>745.2746794848416</v>
+      </c>
+      <c r="E77">
+        <v>1636.35</v>
+      </c>
+      <c r="F77">
+        <v>1687.05</v>
+      </c>
+      <c r="G77">
+        <v>294.4</v>
+      </c>
+      <c r="H77">
+        <v>2198.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>57.5</v>
+      </c>
+      <c r="K77">
+        <v>22.9</v>
+      </c>
+      <c r="L77">
+        <v>34.6</v>
+      </c>
+      <c r="M77">
+        <v>402.86754</v>
+      </c>
+      <c r="N77">
+        <v>-368.2675399999999</v>
+      </c>
+      <c r="O77">
+        <v>-92.06688499999998</v>
+      </c>
+      <c r="P77">
+        <v>-276.200655</v>
+      </c>
+      <c r="Q77">
+        <v>-253.300655</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3925654298868315</v>
+      </c>
+      <c r="T77">
+        <v>5.091016655960998</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02147107706915281</v>
+      </c>
+      <c r="W77">
+        <v>0.2336727067958863</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.08588430827661131</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2753958875686227</v>
+      </c>
+      <c r="C78">
+        <v>-676.1693005117986</v>
+      </c>
+      <c r="D78">
+        <v>738.9746994882011</v>
+      </c>
+      <c r="E78">
+        <v>1658.844</v>
+      </c>
+      <c r="F78">
+        <v>1709.544</v>
+      </c>
+      <c r="G78">
+        <v>294.4</v>
+      </c>
+      <c r="H78">
+        <v>2198.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>57.5</v>
+      </c>
+      <c r="K78">
+        <v>22.9</v>
+      </c>
+      <c r="L78">
+        <v>34.6</v>
+      </c>
+      <c r="M78">
+        <v>408.2391071999999</v>
+      </c>
+      <c r="N78">
+        <v>-373.6391071999999</v>
+      </c>
+      <c r="O78">
+        <v>-93.40977679999997</v>
+      </c>
+      <c r="P78">
+        <v>-280.2293303999999</v>
+      </c>
+      <c r="Q78">
+        <v>-257.3293303999999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4073056561321162</v>
+      </c>
+      <c r="T78">
+        <v>5.303142349959374</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02118856289719027</v>
+      </c>
+      <c r="W78">
+        <v>0.233740171180151</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.08475425158876115</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2773958875686226</v>
+      </c>
+      <c r="C79">
+        <v>-704.8576629295137</v>
+      </c>
+      <c r="D79">
+        <v>732.7803370704862</v>
+      </c>
+      <c r="E79">
+        <v>1681.338</v>
+      </c>
+      <c r="F79">
+        <v>1732.038</v>
+      </c>
+      <c r="G79">
+        <v>294.4</v>
+      </c>
+      <c r="H79">
+        <v>2198.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>57.5</v>
+      </c>
+      <c r="K79">
+        <v>22.9</v>
+      </c>
+      <c r="L79">
+        <v>34.6</v>
+      </c>
+      <c r="M79">
+        <v>413.6106744</v>
+      </c>
+      <c r="N79">
+        <v>-379.0106744</v>
+      </c>
+      <c r="O79">
+        <v>-94.75266859999999</v>
+      </c>
+      <c r="P79">
+        <v>-284.2580058</v>
+      </c>
+      <c r="Q79">
+        <v>-261.3580058</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4233276411813386</v>
+      </c>
+      <c r="T79">
+        <v>5.533713756479346</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02091338675566832</v>
+      </c>
+      <c r="W79">
+        <v>0.2338058832427464</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.08365354702267336</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2793958875686226</v>
+      </c>
+      <c r="C80">
+        <v>-733.4430416681587</v>
+      </c>
+      <c r="D80">
+        <v>726.688958331841</v>
+      </c>
+      <c r="E80">
+        <v>1703.832</v>
+      </c>
+      <c r="F80">
+        <v>1754.532</v>
+      </c>
+      <c r="G80">
+        <v>294.4</v>
+      </c>
+      <c r="H80">
+        <v>2198.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>57.5</v>
+      </c>
+      <c r="K80">
+        <v>22.9</v>
+      </c>
+      <c r="L80">
+        <v>34.6</v>
+      </c>
+      <c r="M80">
+        <v>418.9822416</v>
+      </c>
+      <c r="N80">
+        <v>-384.3822415999999</v>
+      </c>
+      <c r="O80">
+        <v>-96.09556039999998</v>
+      </c>
+      <c r="P80">
+        <v>-288.2866812</v>
+      </c>
+      <c r="Q80">
+        <v>-265.3866812</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.440806170325945</v>
+      </c>
+      <c r="T80">
+        <v>5.785246199955681</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02064526641264693</v>
+      </c>
+      <c r="W80">
+        <v>0.2338699103806599</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.08258106565058776</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2813958875686226</v>
+      </c>
+      <c r="C81">
+        <v>-761.9279837703929</v>
+      </c>
+      <c r="D81">
+        <v>720.698016229607</v>
+      </c>
+      <c r="E81">
+        <v>1726.326</v>
+      </c>
+      <c r="F81">
+        <v>1777.026</v>
+      </c>
+      <c r="G81">
+        <v>294.4</v>
+      </c>
+      <c r="H81">
+        <v>2198.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>57.5</v>
+      </c>
+      <c r="K81">
+        <v>22.9</v>
+      </c>
+      <c r="L81">
+        <v>34.6</v>
+      </c>
+      <c r="M81">
+        <v>424.3538088</v>
+      </c>
+      <c r="N81">
+        <v>-389.7538087999999</v>
+      </c>
+      <c r="O81">
+        <v>-97.43845219999999</v>
+      </c>
+      <c r="P81">
+        <v>-292.3153566</v>
+      </c>
+      <c r="Q81">
+        <v>-269.4153566</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4599493212938471</v>
+      </c>
+      <c r="T81">
+        <v>6.060734114239285</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02038393392641089</v>
+      </c>
+      <c r="W81">
+        <v>0.2339323165783731</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.08153573570564365</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2833958875686227</v>
+      </c>
+      <c r="C82">
+        <v>-790.3149529727259</v>
+      </c>
+      <c r="D82">
+        <v>714.8050470272739</v>
+      </c>
+      <c r="E82">
+        <v>1748.82</v>
+      </c>
+      <c r="F82">
+        <v>1799.52</v>
+      </c>
+      <c r="G82">
+        <v>294.4</v>
+      </c>
+      <c r="H82">
+        <v>2198.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>57.5</v>
+      </c>
+      <c r="K82">
+        <v>22.9</v>
+      </c>
+      <c r="L82">
+        <v>34.6</v>
+      </c>
+      <c r="M82">
+        <v>429.725376</v>
+      </c>
+      <c r="N82">
+        <v>-395.125376</v>
+      </c>
+      <c r="O82">
+        <v>-98.78134399999999</v>
+      </c>
+      <c r="P82">
+        <v>-296.344032</v>
+      </c>
+      <c r="Q82">
+        <v>-273.444032</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4810067873585395</v>
+      </c>
+      <c r="T82">
+        <v>6.36377081995125</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02012913475233076</v>
+      </c>
+      <c r="W82">
+        <v>0.2339931626211434</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.0805165390093231</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2853958875686227</v>
+      </c>
+      <c r="C83">
+        <v>-818.6063330837659</v>
+      </c>
+      <c r="D83">
+        <v>709.007666916234</v>
+      </c>
+      <c r="E83">
+        <v>1771.314</v>
+      </c>
+      <c r="F83">
+        <v>1822.014</v>
+      </c>
+      <c r="G83">
+        <v>294.4</v>
+      </c>
+      <c r="H83">
+        <v>2198.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>57.5</v>
+      </c>
+      <c r="K83">
+        <v>22.9</v>
+      </c>
+      <c r="L83">
+        <v>34.6</v>
+      </c>
+      <c r="M83">
+        <v>435.0969432</v>
+      </c>
+      <c r="N83">
+        <v>-400.4969432</v>
+      </c>
+      <c r="O83">
+        <v>-100.1242358</v>
+      </c>
+      <c r="P83">
+        <v>-300.3727074</v>
+      </c>
+      <c r="Q83">
+        <v>-277.4727074</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5042808287984627</v>
+      </c>
+      <c r="T83">
+        <v>6.698706126264474</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.01988062691588223</v>
+      </c>
+      <c r="W83">
+        <v>0.2340525062924873</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.07952250766352897</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2873958875686226</v>
+      </c>
+      <c r="C84">
+        <v>-846.8044311993913</v>
+      </c>
+      <c r="D84">
+        <v>703.3035688006086</v>
+      </c>
+      <c r="E84">
+        <v>1793.808</v>
+      </c>
+      <c r="F84">
+        <v>1844.508</v>
+      </c>
+      <c r="G84">
+        <v>294.4</v>
+      </c>
+      <c r="H84">
+        <v>2198.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>57.5</v>
+      </c>
+      <c r="K84">
+        <v>22.9</v>
+      </c>
+      <c r="L84">
+        <v>34.6</v>
+      </c>
+      <c r="M84">
+        <v>440.4685104</v>
+      </c>
+      <c r="N84">
+        <v>-405.8685103999999</v>
+      </c>
+      <c r="O84">
+        <v>-101.4671276</v>
+      </c>
+      <c r="P84">
+        <v>-304.4013828</v>
+      </c>
+      <c r="Q84">
+        <v>-281.5013828</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5301408748428217</v>
+      </c>
+      <c r="T84">
+        <v>7.0708564666125</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01963818024617635</v>
+      </c>
+      <c r="W84">
+        <v>0.2341104025572131</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.07855272098470545</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2893958875686226</v>
+      </c>
+      <c r="C85">
+        <v>-874.911480763966</v>
+      </c>
+      <c r="D85">
+        <v>697.690519236034</v>
+      </c>
+      <c r="E85">
+        <v>1816.302</v>
+      </c>
+      <c r="F85">
+        <v>1867.002</v>
+      </c>
+      <c r="G85">
+        <v>294.4</v>
+      </c>
+      <c r="H85">
+        <v>2198.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>57.5</v>
+      </c>
+      <c r="K85">
+        <v>22.9</v>
+      </c>
+      <c r="L85">
+        <v>34.6</v>
+      </c>
+      <c r="M85">
+        <v>445.8400776</v>
+      </c>
+      <c r="N85">
+        <v>-411.2400776</v>
+      </c>
+      <c r="O85">
+        <v>-102.8100194</v>
+      </c>
+      <c r="P85">
+        <v>-308.4300582</v>
+      </c>
+      <c r="Q85">
+        <v>-285.5300582</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5590432792453406</v>
+      </c>
+      <c r="T85">
+        <v>7.486789199942648</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01940157566489711</v>
+      </c>
+      <c r="W85">
+        <v>0.2341669037312226</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.07760630265958846</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2913958875686226</v>
+      </c>
+      <c r="C86">
+        <v>-902.9296444861204</v>
+      </c>
+      <c r="D86">
+        <v>692.1663555138792</v>
+      </c>
+      <c r="E86">
+        <v>1838.796</v>
+      </c>
+      <c r="F86">
+        <v>1889.496</v>
+      </c>
+      <c r="G86">
+        <v>294.4</v>
+      </c>
+      <c r="H86">
+        <v>2198.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>57.5</v>
+      </c>
+      <c r="K86">
+        <v>22.9</v>
+      </c>
+      <c r="L86">
+        <v>34.6</v>
+      </c>
+      <c r="M86">
+        <v>451.2116447999999</v>
+      </c>
+      <c r="N86">
+        <v>-416.6116447999999</v>
+      </c>
+      <c r="O86">
+        <v>-104.1529112</v>
+      </c>
+      <c r="P86">
+        <v>-312.4587336</v>
+      </c>
+      <c r="Q86">
+        <v>-289.5587336</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5915584841981743</v>
+      </c>
+      <c r="T86">
+        <v>7.954713524939059</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01917060452602929</v>
+      </c>
+      <c r="W86">
+        <v>0.2342220596391842</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.07668241810411724</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2933958875686226</v>
+      </c>
+      <c r="C87">
+        <v>-930.8610171171084</v>
+      </c>
+      <c r="D87">
+        <v>686.7289828828912</v>
+      </c>
+      <c r="E87">
+        <v>1861.29</v>
+      </c>
+      <c r="F87">
+        <v>1911.99</v>
+      </c>
+      <c r="G87">
+        <v>294.4</v>
+      </c>
+      <c r="H87">
+        <v>2198.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>57.5</v>
+      </c>
+      <c r="K87">
+        <v>22.9</v>
+      </c>
+      <c r="L87">
+        <v>34.6</v>
+      </c>
+      <c r="M87">
+        <v>456.5832119999999</v>
+      </c>
+      <c r="N87">
+        <v>-421.9832119999999</v>
+      </c>
+      <c r="O87">
+        <v>-105.495803</v>
+      </c>
+      <c r="P87">
+        <v>-316.4874089999999</v>
+      </c>
+      <c r="Q87">
+        <v>-293.5874089999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6284090498113859</v>
+      </c>
+      <c r="T87">
+        <v>8.485027759934997</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01894506800219366</v>
+      </c>
+      <c r="W87">
+        <v>0.2342759177610762</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.07578027200877469</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2953958875686226</v>
+      </c>
+      <c r="C88">
+        <v>-958.7076280992252</v>
+      </c>
+      <c r="D88">
+        <v>681.3763719007745</v>
+      </c>
+      <c r="E88">
+        <v>1883.784</v>
+      </c>
+      <c r="F88">
+        <v>1934.484</v>
+      </c>
+      <c r="G88">
+        <v>294.4</v>
+      </c>
+      <c r="H88">
+        <v>2198.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>57.5</v>
+      </c>
+      <c r="K88">
+        <v>22.9</v>
+      </c>
+      <c r="L88">
+        <v>34.6</v>
+      </c>
+      <c r="M88">
+        <v>461.9547792</v>
+      </c>
+      <c r="N88">
+        <v>-427.3547791999999</v>
+      </c>
+      <c r="O88">
+        <v>-106.8386948</v>
+      </c>
+      <c r="P88">
+        <v>-320.5160844</v>
+      </c>
+      <c r="Q88">
+        <v>-297.6160844</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6705239819407705</v>
+      </c>
+      <c r="T88">
+        <v>9.091101171358925</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01872477651379605</v>
+      </c>
+      <c r="W88">
+        <v>0.2343285233685055</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.07489910605518424</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2973958875686226</v>
+      </c>
+      <c r="C89">
+        <v>-986.4714440913295</v>
+      </c>
+      <c r="D89">
+        <v>676.1065559086701</v>
+      </c>
+      <c r="E89">
+        <v>1906.278</v>
+      </c>
+      <c r="F89">
+        <v>1956.978</v>
+      </c>
+      <c r="G89">
+        <v>294.4</v>
+      </c>
+      <c r="H89">
+        <v>2198.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>57.5</v>
+      </c>
+      <c r="K89">
+        <v>22.9</v>
+      </c>
+      <c r="L89">
+        <v>34.6</v>
+      </c>
+      <c r="M89">
+        <v>467.3263463999999</v>
+      </c>
+      <c r="N89">
+        <v>-432.7263463999999</v>
+      </c>
+      <c r="O89">
+        <v>-108.1815866</v>
+      </c>
+      <c r="P89">
+        <v>-324.5447598</v>
+      </c>
+      <c r="Q89">
+        <v>-301.6447598</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7191181343977529</v>
+      </c>
+      <c r="T89">
+        <v>9.790416646078842</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01850954919754553</v>
+      </c>
+      <c r="W89">
+        <v>0.2343799196516261</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.0740381967901822</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2993958875686226</v>
+      </c>
+      <c r="C90">
+        <v>-1014.154371378071</v>
+      </c>
+      <c r="D90">
+        <v>670.917628621929</v>
+      </c>
+      <c r="E90">
+        <v>1928.772</v>
+      </c>
+      <c r="F90">
+        <v>1979.472</v>
+      </c>
+      <c r="G90">
+        <v>294.4</v>
+      </c>
+      <c r="H90">
+        <v>2198.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>57.5</v>
+      </c>
+      <c r="K90">
+        <v>22.9</v>
+      </c>
+      <c r="L90">
+        <v>34.6</v>
+      </c>
+      <c r="M90">
+        <v>472.6979136</v>
+      </c>
+      <c r="N90">
+        <v>-438.0979136</v>
+      </c>
+      <c r="O90">
+        <v>-109.5244784</v>
+      </c>
+      <c r="P90">
+        <v>-328.5734351999999</v>
+      </c>
+      <c r="Q90">
+        <v>-305.6734352</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7758113122642323</v>
+      </c>
+      <c r="T90">
+        <v>10.60628469991875</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01829921341120978</v>
+      </c>
+      <c r="W90">
+        <v>0.2344301478374031</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.07319685364483919</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3013958875686227</v>
+      </c>
+      <c r="C91">
+        <v>-1041.758258169018</v>
+      </c>
+      <c r="D91">
+        <v>665.8077418309821</v>
+      </c>
+      <c r="E91">
+        <v>1951.266</v>
+      </c>
+      <c r="F91">
+        <v>2001.966</v>
+      </c>
+      <c r="G91">
+        <v>294.4</v>
+      </c>
+      <c r="H91">
+        <v>2198.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>57.5</v>
+      </c>
+      <c r="K91">
+        <v>22.9</v>
+      </c>
+      <c r="L91">
+        <v>34.6</v>
+      </c>
+      <c r="M91">
+        <v>478.0694808</v>
+      </c>
+      <c r="N91">
+        <v>-443.4694807999999</v>
+      </c>
+      <c r="O91">
+        <v>-110.8673702</v>
+      </c>
+      <c r="P91">
+        <v>-332.6021105999999</v>
+      </c>
+      <c r="Q91">
+        <v>-309.7021106</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8428123406518899</v>
+      </c>
+      <c r="T91">
+        <v>11.57049239991136</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01809360427175798</v>
+      </c>
+      <c r="W91">
+        <v>0.2344792472999042</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.07237441708703196</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3033958875686227</v>
+      </c>
+      <c r="C92">
+        <v>-1069.284896793519</v>
+      </c>
+      <c r="D92">
+        <v>660.7751032064812</v>
+      </c>
+      <c r="E92">
+        <v>1973.76</v>
+      </c>
+      <c r="F92">
+        <v>2024.46</v>
+      </c>
+      <c r="G92">
+        <v>294.4</v>
+      </c>
+      <c r="H92">
+        <v>2198.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>57.5</v>
+      </c>
+      <c r="K92">
+        <v>22.9</v>
+      </c>
+      <c r="L92">
+        <v>34.6</v>
+      </c>
+      <c r="M92">
+        <v>483.441048</v>
+      </c>
+      <c r="N92">
+        <v>-448.8410479999999</v>
+      </c>
+      <c r="O92">
+        <v>-112.210262</v>
+      </c>
+      <c r="P92">
+        <v>-336.6307859999999</v>
+      </c>
+      <c r="Q92">
+        <v>-313.730786</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9232135747170791</v>
+      </c>
+      <c r="T92">
+        <v>12.7275416399025</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01789256422429401</v>
+      </c>
+      <c r="W92">
+        <v>0.2345272556632386</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.07157025689717611</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3053958875686226</v>
+      </c>
+      <c r="C93">
+        <v>-1096.736025796766</v>
+      </c>
+      <c r="D93">
+        <v>655.8179742032336</v>
+      </c>
+      <c r="E93">
+        <v>1996.254</v>
+      </c>
+      <c r="F93">
+        <v>2046.954</v>
+      </c>
+      <c r="G93">
+        <v>294.4</v>
+      </c>
+      <c r="H93">
+        <v>2198.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>57.5</v>
+      </c>
+      <c r="K93">
+        <v>22.9</v>
+      </c>
+      <c r="L93">
+        <v>34.6</v>
+      </c>
+      <c r="M93">
+        <v>488.8126152</v>
+      </c>
+      <c r="N93">
+        <v>-454.2126152</v>
+      </c>
+      <c r="O93">
+        <v>-113.5531538</v>
+      </c>
+      <c r="P93">
+        <v>-340.6594613999999</v>
+      </c>
+      <c r="Q93">
+        <v>-317.7594614</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.021481749685643</v>
+      </c>
+      <c r="T93">
+        <v>14.141712933225</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01769594263941165</v>
+      </c>
+      <c r="W93">
+        <v>0.2345742088977085</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.07078377055764662</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3073958875686226</v>
+      </c>
+      <c r="C94">
+        <v>-1124.113331942217</v>
+      </c>
+      <c r="D94">
+        <v>650.9346680577835</v>
+      </c>
+      <c r="E94">
+        <v>2018.748</v>
+      </c>
+      <c r="F94">
+        <v>2069.448</v>
+      </c>
+      <c r="G94">
+        <v>294.4</v>
+      </c>
+      <c r="H94">
+        <v>2198.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>57.5</v>
+      </c>
+      <c r="K94">
+        <v>22.9</v>
+      </c>
+      <c r="L94">
+        <v>34.6</v>
+      </c>
+      <c r="M94">
+        <v>494.1841824</v>
+      </c>
+      <c r="N94">
+        <v>-459.5841824</v>
+      </c>
+      <c r="O94">
+        <v>-114.8960456</v>
+      </c>
+      <c r="P94">
+        <v>-344.6881368</v>
+      </c>
+      <c r="Q94">
+        <v>-321.7881368</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.144316968396349</v>
+      </c>
+      <c r="T94">
+        <v>15.90942704987813</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01750359543680935</v>
+      </c>
+      <c r="W94">
+        <v>0.23462014140969</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.0700143817472374</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3093958875686226</v>
+      </c>
+      <c r="C95">
+        <v>-1151.418452125206</v>
+      </c>
+      <c r="D95">
+        <v>646.1235478747933</v>
+      </c>
+      <c r="E95">
+        <v>2041.242</v>
+      </c>
+      <c r="F95">
+        <v>2091.942</v>
+      </c>
+      <c r="G95">
+        <v>294.4</v>
+      </c>
+      <c r="H95">
+        <v>2198.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>57.5</v>
+      </c>
+      <c r="K95">
+        <v>22.9</v>
+      </c>
+      <c r="L95">
+        <v>34.6</v>
+      </c>
+      <c r="M95">
+        <v>499.5557495999999</v>
+      </c>
+      <c r="N95">
+        <v>-464.9557495999999</v>
+      </c>
+      <c r="O95">
+        <v>-116.2389374</v>
+      </c>
+      <c r="P95">
+        <v>-348.7168121999999</v>
+      </c>
+      <c r="Q95">
+        <v>-325.8168122</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.302247963881542</v>
+      </c>
+      <c r="T95">
+        <v>18.18220234271786</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01731538473318775</v>
+      </c>
+      <c r="W95">
+        <v>0.2346650861257148</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.069261538932751</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3113958875686226</v>
+      </c>
+      <c r="C96">
+        <v>-1178.652975202336</v>
+      </c>
+      <c r="D96">
+        <v>641.383024797664</v>
+      </c>
+      <c r="E96">
+        <v>2063.736</v>
+      </c>
+      <c r="F96">
+        <v>2114.436</v>
+      </c>
+      <c r="G96">
+        <v>294.4</v>
+      </c>
+      <c r="H96">
+        <v>2198.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>57.5</v>
+      </c>
+      <c r="K96">
+        <v>22.9</v>
+      </c>
+      <c r="L96">
+        <v>34.6</v>
+      </c>
+      <c r="M96">
+        <v>504.9273168</v>
+      </c>
+      <c r="N96">
+        <v>-470.3273167999999</v>
+      </c>
+      <c r="O96">
+        <v>-117.5818292</v>
+      </c>
+      <c r="P96">
+        <v>-352.7454875999999</v>
+      </c>
+      <c r="Q96">
+        <v>-329.8454876</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.512822624528466</v>
+      </c>
+      <c r="T96">
+        <v>21.21256939983751</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01713117851262192</v>
+      </c>
+      <c r="W96">
+        <v>0.2347090745711859</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.06852471405048777</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3133958875686226</v>
+      </c>
+      <c r="C97">
+        <v>-1205.818443740898</v>
+      </c>
+      <c r="D97">
+        <v>636.7115562591019</v>
+      </c>
+      <c r="E97">
+        <v>2086.23</v>
+      </c>
+      <c r="F97">
+        <v>2136.93</v>
+      </c>
+      <c r="G97">
+        <v>294.4</v>
+      </c>
+      <c r="H97">
+        <v>2198.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>57.5</v>
+      </c>
+      <c r="K97">
+        <v>22.9</v>
+      </c>
+      <c r="L97">
+        <v>34.6</v>
+      </c>
+      <c r="M97">
+        <v>510.298884</v>
+      </c>
+      <c r="N97">
+        <v>-475.698884</v>
+      </c>
+      <c r="O97">
+        <v>-118.924721</v>
+      </c>
+      <c r="P97">
+        <v>-356.774163</v>
+      </c>
+      <c r="Q97">
+        <v>-333.874163</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.80762714943416</v>
+      </c>
+      <c r="T97">
+        <v>25.45508327980503</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01695085031775221</v>
+      </c>
+      <c r="W97">
+        <v>0.2347521369441208</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.06780340127100892</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3153958875686226</v>
+      </c>
+      <c r="C98">
+        <v>-1232.916355692417</v>
+      </c>
+      <c r="D98">
+        <v>632.107644307583</v>
+      </c>
+      <c r="E98">
+        <v>2108.724</v>
+      </c>
+      <c r="F98">
+        <v>2159.424</v>
+      </c>
+      <c r="G98">
+        <v>294.4</v>
+      </c>
+      <c r="H98">
+        <v>2198.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>57.5</v>
+      </c>
+      <c r="K98">
+        <v>22.9</v>
+      </c>
+      <c r="L98">
+        <v>34.6</v>
+      </c>
+      <c r="M98">
+        <v>515.6704511999999</v>
+      </c>
+      <c r="N98">
+        <v>-481.0704511999999</v>
+      </c>
+      <c r="O98">
+        <v>-120.2676128</v>
+      </c>
+      <c r="P98">
+        <v>-360.8028383999999</v>
+      </c>
+      <c r="Q98">
+        <v>-337.9028384</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.249833936792695</v>
+      </c>
+      <c r="T98">
+        <v>31.81885409975621</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01677427896027563</v>
+      </c>
+      <c r="W98">
+        <v>0.2347943021842862</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.06709711584110256</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3173958875686226</v>
+      </c>
+      <c r="C99">
+        <v>-1259.948165994099</v>
+      </c>
+      <c r="D99">
+        <v>627.5698340059009</v>
+      </c>
+      <c r="E99">
+        <v>2131.218</v>
+      </c>
+      <c r="F99">
+        <v>2181.918</v>
+      </c>
+      <c r="G99">
+        <v>294.4</v>
+      </c>
+      <c r="H99">
+        <v>2198.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>57.5</v>
+      </c>
+      <c r="K99">
+        <v>22.9</v>
+      </c>
+      <c r="L99">
+        <v>34.6</v>
+      </c>
+      <c r="M99">
+        <v>521.0420184</v>
+      </c>
+      <c r="N99">
+        <v>-486.4420183999999</v>
+      </c>
+      <c r="O99">
+        <v>-121.6105046</v>
+      </c>
+      <c r="P99">
+        <v>-364.8315137999999</v>
+      </c>
+      <c r="Q99">
+        <v>-341.9315137999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.986845249056927</v>
+      </c>
+      <c r="T99">
+        <v>42.42513879967495</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01660134824934495</v>
+      </c>
+      <c r="W99">
+        <v>0.2348355980380564</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.06640539299737991</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3193958875686226</v>
+      </c>
+      <c r="C100">
+        <v>-1286.915288101795</v>
+      </c>
+      <c r="D100">
+        <v>623.0967118982047</v>
+      </c>
+      <c r="E100">
+        <v>2153.712</v>
+      </c>
+      <c r="F100">
+        <v>2204.412</v>
+      </c>
+      <c r="G100">
+        <v>294.4</v>
+      </c>
+      <c r="H100">
+        <v>2198.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>57.5</v>
+      </c>
+      <c r="K100">
+        <v>22.9</v>
+      </c>
+      <c r="L100">
+        <v>34.6</v>
+      </c>
+      <c r="M100">
+        <v>526.4135856</v>
+      </c>
+      <c r="N100">
+        <v>-491.8135856</v>
+      </c>
+      <c r="O100">
+        <v>-122.9533964</v>
+      </c>
+      <c r="P100">
+        <v>-368.8601892</v>
+      </c>
+      <c r="Q100">
+        <v>-345.9601892000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.46086787358539</v>
+      </c>
+      <c r="T100">
+        <v>63.63770819951242</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01643194673659653</v>
+      </c>
+      <c r="W100">
+        <v>0.2348760511193008</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.06572778694638615</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3213958875686226</v>
+      </c>
+      <c r="C101">
+        <v>-1313.819095457869</v>
+      </c>
+      <c r="D101">
+        <v>618.6869045421305</v>
+      </c>
+      <c r="E101">
+        <v>2176.206</v>
+      </c>
+      <c r="F101">
+        <v>2226.905999999999</v>
+      </c>
+      <c r="G101">
+        <v>294.4</v>
+      </c>
+      <c r="H101">
+        <v>2198.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>57.5</v>
+      </c>
+      <c r="K101">
+        <v>22.9</v>
+      </c>
+      <c r="L101">
+        <v>34.6</v>
+      </c>
+      <c r="M101">
+        <v>531.7851527999999</v>
+      </c>
+      <c r="N101">
+        <v>-497.1851527999999</v>
+      </c>
+      <c r="O101">
+        <v>-124.2962882</v>
+      </c>
+      <c r="P101">
+        <v>-372.8888645999999</v>
+      </c>
+      <c r="Q101">
+        <v>-349.9888645999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.88293574717078</v>
+      </c>
+      <c r="T101">
+        <v>127.2754163990248</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01626596747663092</v>
+      </c>
+      <c r="W101">
+        <v>0.2349156869665806</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.06506386990652369</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_electronics_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1112967576199604</v>
+        <v>0.1110522657259105</v>
       </c>
       <c r="C2">
-        <v>1024.486062443636</v>
+        <v>1016.965739564425</v>
       </c>
       <c r="D2">
-        <v>765.8860624436362</v>
+        <v>768.7557395644247</v>
       </c>
       <c r="E2">
-        <v>-77.90000000000001</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.39</v>
       </c>
       <c r="G2">
         <v>258.6</v>
@@ -1451,28 +1451,28 @@
         <v>67</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.522617</v>
       </c>
       <c r="N2">
-        <v>67</v>
+        <v>66.477383</v>
       </c>
       <c r="O2">
-        <v>16.75</v>
+        <v>16.61934575</v>
       </c>
       <c r="P2">
-        <v>50.25</v>
+        <v>49.85803725</v>
       </c>
       <c r="Q2">
-        <v>78.65000000000001</v>
+        <v>78.25803725</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1112967576199604</v>
+        <v>0.1117929451776873</v>
       </c>
       <c r="T2">
-        <v>1.276653715063877</v>
+        <v>1.286325334117391</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>128.2009578716345</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1110522657259105</v>
+        <v>0.1108077738318606</v>
       </c>
       <c r="C3">
-        <v>1016.965739564425</v>
+        <v>1009.46700218963</v>
       </c>
       <c r="D3">
-        <v>768.7557395644247</v>
+        <v>771.6470021896298</v>
       </c>
       <c r="E3">
-        <v>-67.51000000000001</v>
+        <v>-57.12</v>
       </c>
       <c r="F3">
-        <v>10.39</v>
+        <v>20.78</v>
       </c>
       <c r="G3">
         <v>258.6</v>
@@ -1533,28 +1533,28 @@
         <v>67</v>
       </c>
       <c r="M3">
-        <v>0.522617</v>
+        <v>1.045234</v>
       </c>
       <c r="N3">
-        <v>66.477383</v>
+        <v>65.95476600000001</v>
       </c>
       <c r="O3">
-        <v>16.61934575</v>
+        <v>16.4886915</v>
       </c>
       <c r="P3">
-        <v>49.85803725</v>
+        <v>49.4660745</v>
       </c>
       <c r="Q3">
-        <v>78.25803725</v>
+        <v>77.86607450000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1117929451776873</v>
+        <v>0.1122992590121026</v>
       </c>
       <c r="T3">
-        <v>1.286325334117391</v>
+        <v>1.29619433315159</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>128.2009578716345</v>
+        <v>64.10047893581725</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1108077738318606</v>
+        <v>0.1105632819378106</v>
       </c>
       <c r="C4">
-        <v>1009.46700218963</v>
+        <v>1001.990094785593</v>
       </c>
       <c r="D4">
-        <v>771.6470021896298</v>
+        <v>774.5600947855925</v>
       </c>
       <c r="E4">
-        <v>-57.12</v>
+        <v>-46.73</v>
       </c>
       <c r="F4">
-        <v>20.78</v>
+        <v>31.17</v>
       </c>
       <c r="G4">
         <v>258.6</v>
@@ -1615,28 +1615,28 @@
         <v>67</v>
       </c>
       <c r="M4">
-        <v>1.045234</v>
+        <v>1.567851</v>
       </c>
       <c r="N4">
-        <v>65.95476600000001</v>
+        <v>65.432149</v>
       </c>
       <c r="O4">
-        <v>16.4886915</v>
+        <v>16.35803725</v>
       </c>
       <c r="P4">
-        <v>49.4660745</v>
+        <v>49.07411175</v>
       </c>
       <c r="Q4">
-        <v>77.86607450000001</v>
+        <v>77.47411175000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1122992590121026</v>
+        <v>0.1128160123070213</v>
       </c>
       <c r="T4">
-        <v>1.29619433315159</v>
+        <v>1.306266816701957</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.10047893581725</v>
+        <v>42.73365262387816</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1105632819378106</v>
+        <v>0.1103187900437608</v>
       </c>
       <c r="C5">
-        <v>1001.990094785593</v>
+        <v>994.5352655242432</v>
       </c>
       <c r="D5">
-        <v>774.5600947855925</v>
+        <v>777.4952655242431</v>
       </c>
       <c r="E5">
-        <v>-46.73</v>
+        <v>-36.34</v>
       </c>
       <c r="F5">
-        <v>31.17</v>
+        <v>41.56</v>
       </c>
       <c r="G5">
         <v>258.6</v>
@@ -1697,28 +1697,28 @@
         <v>67</v>
       </c>
       <c r="M5">
-        <v>1.567851</v>
+        <v>2.090468</v>
       </c>
       <c r="N5">
-        <v>65.432149</v>
+        <v>64.909532</v>
       </c>
       <c r="O5">
-        <v>16.35803725</v>
+        <v>16.227383</v>
       </c>
       <c r="P5">
-        <v>49.07411175</v>
+        <v>48.682149</v>
       </c>
       <c r="Q5">
-        <v>77.47411175000001</v>
+        <v>77.082149</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1128160123070213</v>
+        <v>0.1133435312955841</v>
       </c>
       <c r="T5">
-        <v>1.306266816701957</v>
+        <v>1.316549143659623</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.73365262387816</v>
+        <v>32.05023946790863</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1103187900437608</v>
+        <v>0.1100742981497109</v>
       </c>
       <c r="C6">
-        <v>994.5352655242432</v>
+        <v>987.1027663535804</v>
       </c>
       <c r="D6">
-        <v>777.4952655242431</v>
+        <v>780.4527663535804</v>
       </c>
       <c r="E6">
-        <v>-36.34</v>
+        <v>-25.95</v>
       </c>
       <c r="F6">
-        <v>41.56</v>
+        <v>51.95</v>
       </c>
       <c r="G6">
         <v>258.6</v>
@@ -1779,28 +1779,28 @@
         <v>67</v>
       </c>
       <c r="M6">
-        <v>2.090468</v>
+        <v>2.613085</v>
       </c>
       <c r="N6">
-        <v>64.909532</v>
+        <v>64.386915</v>
       </c>
       <c r="O6">
-        <v>16.227383</v>
+        <v>16.09672875</v>
       </c>
       <c r="P6">
-        <v>48.682149</v>
+        <v>48.29018625</v>
       </c>
       <c r="Q6">
-        <v>77.082149</v>
+        <v>76.69018625000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1133435312955841</v>
+        <v>0.1138821559470641</v>
       </c>
       <c r="T6">
-        <v>1.316549143659623</v>
+        <v>1.327047940658504</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.05023946790863</v>
+        <v>25.6401915743269</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1100742981497109</v>
+        <v>0.109829806255661</v>
       </c>
       <c r="C7">
-        <v>987.1027663535804</v>
+        <v>979.6928530697638</v>
       </c>
       <c r="D7">
-        <v>780.4527663535804</v>
+        <v>783.4328530697637</v>
       </c>
       <c r="E7">
-        <v>-25.95</v>
+        <v>-15.56</v>
       </c>
       <c r="F7">
-        <v>51.95</v>
+        <v>62.34</v>
       </c>
       <c r="G7">
         <v>258.6</v>
@@ -1861,28 +1861,28 @@
         <v>67</v>
       </c>
       <c r="M7">
-        <v>2.613085</v>
+        <v>3.135702</v>
       </c>
       <c r="N7">
-        <v>64.386915</v>
+        <v>63.864298</v>
       </c>
       <c r="O7">
-        <v>16.09672875</v>
+        <v>15.9660745</v>
       </c>
       <c r="P7">
-        <v>48.29018625</v>
+        <v>47.8982235</v>
       </c>
       <c r="Q7">
-        <v>76.69018625000001</v>
+        <v>76.29822350000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1138821559470641</v>
+        <v>0.1144322406975117</v>
       </c>
       <c r="T7">
-        <v>1.327047940658504</v>
+        <v>1.337770116316935</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.6401915743269</v>
+        <v>21.36682631193908</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.109829806255661</v>
+        <v>0.1095853143616111</v>
       </c>
       <c r="C8">
-        <v>979.6928530697638</v>
+        <v>972.3057853908626</v>
       </c>
       <c r="D8">
-        <v>783.4328530697637</v>
+        <v>786.4357853908626</v>
       </c>
       <c r="E8">
-        <v>-15.56000000000001</v>
+        <v>-5.170000000000016</v>
       </c>
       <c r="F8">
-        <v>62.34</v>
+        <v>72.72999999999999</v>
       </c>
       <c r="G8">
         <v>258.6</v>
@@ -1943,28 +1943,28 @@
         <v>67</v>
       </c>
       <c r="M8">
-        <v>3.135702</v>
+        <v>3.658318999999999</v>
       </c>
       <c r="N8">
-        <v>63.864298</v>
+        <v>63.341681</v>
       </c>
       <c r="O8">
-        <v>15.9660745</v>
+        <v>15.83542025</v>
       </c>
       <c r="P8">
-        <v>47.8982235</v>
+        <v>47.50626075</v>
       </c>
       <c r="Q8">
-        <v>76.29822350000001</v>
+        <v>75.90626075</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1144322406975117</v>
+        <v>0.1149941552275388</v>
       </c>
       <c r="T8">
-        <v>1.337770116316935</v>
+        <v>1.348722876398128</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.36682631193908</v>
+        <v>18.31442255309064</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.109585314361611</v>
+        <v>0.1093408224675612</v>
       </c>
       <c r="C9">
-        <v>972.3057853908626</v>
+        <v>964.941827032313</v>
       </c>
       <c r="D9">
-        <v>786.4357853908627</v>
+        <v>789.4618270323128</v>
       </c>
       <c r="E9">
-        <v>-5.170000000000002</v>
+        <v>5.219999999999999</v>
       </c>
       <c r="F9">
-        <v>72.73</v>
+        <v>83.12</v>
       </c>
       <c r="G9">
         <v>258.6</v>
@@ -2025,28 +2025,28 @@
         <v>67</v>
       </c>
       <c r="M9">
-        <v>3.658319</v>
+        <v>4.180936</v>
       </c>
       <c r="N9">
-        <v>63.341681</v>
+        <v>62.819064</v>
       </c>
       <c r="O9">
-        <v>15.83542025</v>
+        <v>15.704766</v>
       </c>
       <c r="P9">
-        <v>47.50626075</v>
+        <v>47.114298</v>
       </c>
       <c r="Q9">
-        <v>75.90626075</v>
+        <v>75.514298</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1149941552275388</v>
+        <v>0.1155682852908274</v>
       </c>
       <c r="T9">
-        <v>1.348722876398128</v>
+        <v>1.359913739959348</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.31442255309064</v>
+        <v>16.02511973395431</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1093408224675612</v>
+        <v>0.1090963305735113</v>
       </c>
       <c r="C10">
-        <v>964.941827032313</v>
+        <v>957.6012457841164</v>
       </c>
       <c r="D10">
-        <v>789.4618270323128</v>
+        <v>792.5112457841165</v>
       </c>
       <c r="E10">
-        <v>5.219999999999999</v>
+        <v>15.60999999999999</v>
       </c>
       <c r="F10">
-        <v>83.12</v>
+        <v>93.50999999999999</v>
       </c>
       <c r="G10">
         <v>258.6</v>
@@ -2107,28 +2107,28 @@
         <v>67</v>
       </c>
       <c r="M10">
-        <v>4.180936</v>
+        <v>4.703552999999999</v>
       </c>
       <c r="N10">
-        <v>62.819064</v>
+        <v>62.296447</v>
       </c>
       <c r="O10">
-        <v>15.704766</v>
+        <v>15.57411175</v>
       </c>
       <c r="P10">
-        <v>47.114298</v>
+        <v>46.72233525</v>
       </c>
       <c r="Q10">
-        <v>75.514298</v>
+        <v>75.12233525000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1155682852908274</v>
+        <v>0.1161550335972651</v>
       </c>
       <c r="T10">
-        <v>1.359913739959348</v>
+        <v>1.371350556565868</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.02511973395431</v>
+        <v>14.24455087462606</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1090963305735113</v>
+        <v>0.1089643386794613</v>
       </c>
       <c r="C11">
-        <v>957.6012457841164</v>
+        <v>948.8673236054602</v>
       </c>
       <c r="D11">
-        <v>792.5112457841165</v>
+        <v>794.1673236054603</v>
       </c>
       <c r="E11">
-        <v>15.60999999999999</v>
+        <v>25.99999999999999</v>
       </c>
       <c r="F11">
-        <v>93.50999999999999</v>
+        <v>103.9</v>
       </c>
       <c r="G11">
         <v>258.6</v>
@@ -2189,45 +2189,45 @@
         <v>67</v>
       </c>
       <c r="M11">
-        <v>4.703552999999999</v>
+        <v>5.38202</v>
       </c>
       <c r="N11">
-        <v>62.296447</v>
+        <v>61.61798</v>
       </c>
       <c r="O11">
-        <v>15.57411175</v>
+        <v>15.404495</v>
       </c>
       <c r="P11">
-        <v>46.72233525</v>
+        <v>46.21348500000001</v>
       </c>
       <c r="Q11">
-        <v>75.12233525000001</v>
+        <v>74.61348500000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1161550335972651</v>
+        <v>0.1167548207549571</v>
       </c>
       <c r="T11">
-        <v>1.371350556565868</v>
+        <v>1.383041524652534</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>14.24455087462606</v>
+        <v>12.44885749216837</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1089643386794613</v>
+        <v>0.1087310967854115</v>
       </c>
       <c r="C12">
-        <v>948.8673236054602</v>
+        <v>941.4207506266339</v>
       </c>
       <c r="D12">
-        <v>794.1673236054603</v>
+        <v>797.1107506266338</v>
       </c>
       <c r="E12">
-        <v>26</v>
+        <v>36.39</v>
       </c>
       <c r="F12">
-        <v>103.9</v>
+        <v>114.29</v>
       </c>
       <c r="G12">
         <v>258.6</v>
@@ -2271,28 +2271,28 @@
         <v>67</v>
       </c>
       <c r="M12">
-        <v>5.38202</v>
+        <v>5.920222</v>
       </c>
       <c r="N12">
-        <v>61.61798</v>
+        <v>61.079778</v>
       </c>
       <c r="O12">
-        <v>15.404495</v>
+        <v>15.2699445</v>
       </c>
       <c r="P12">
-        <v>46.21348500000001</v>
+        <v>45.8098335</v>
       </c>
       <c r="Q12">
-        <v>74.61348500000001</v>
+        <v>74.2098335</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1167548207549571</v>
+        <v>0.1173680862757432</v>
       </c>
       <c r="T12">
-        <v>1.383041524652534</v>
+        <v>1.394995211123169</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.44885749216837</v>
+        <v>11.31714317469852</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1087310967854115</v>
+        <v>0.1084978548913616</v>
       </c>
       <c r="C13">
-        <v>941.4207506266339</v>
+        <v>933.9960772963553</v>
       </c>
       <c r="D13">
-        <v>797.1107506266338</v>
+        <v>800.0760772963554</v>
       </c>
       <c r="E13">
-        <v>36.39</v>
+        <v>46.77999999999999</v>
       </c>
       <c r="F13">
-        <v>114.29</v>
+        <v>124.68</v>
       </c>
       <c r="G13">
         <v>258.6</v>
@@ -2353,28 +2353,28 @@
         <v>67</v>
       </c>
       <c r="M13">
-        <v>5.920222</v>
+        <v>6.458423999999999</v>
       </c>
       <c r="N13">
-        <v>61.079778</v>
+        <v>60.541576</v>
       </c>
       <c r="O13">
-        <v>15.2699445</v>
+        <v>15.135394</v>
       </c>
       <c r="P13">
-        <v>45.8098335</v>
+        <v>45.406182</v>
       </c>
       <c r="Q13">
-        <v>74.2098335</v>
+        <v>73.80618200000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1173680862757432</v>
+        <v>0.1179952896492745</v>
       </c>
       <c r="T13">
-        <v>1.394995211123169</v>
+        <v>1.407220572286319</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.31714317469852</v>
+        <v>10.37404791014031</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1084978548913616</v>
+        <v>0.1084303629973117</v>
       </c>
       <c r="C14">
-        <v>933.9960772963553</v>
+        <v>924.4682573517873</v>
       </c>
       <c r="D14">
-        <v>800.0760772963554</v>
+        <v>800.9382573517873</v>
       </c>
       <c r="E14">
-        <v>46.77999999999999</v>
+        <v>57.16999999999999</v>
       </c>
       <c r="F14">
-        <v>124.68</v>
+        <v>135.07</v>
       </c>
       <c r="G14">
         <v>258.6</v>
@@ -2435,45 +2435,45 @@
         <v>67</v>
       </c>
       <c r="M14">
-        <v>6.458423999999999</v>
+        <v>7.226245</v>
       </c>
       <c r="N14">
-        <v>60.541576</v>
+        <v>59.773755</v>
       </c>
       <c r="O14">
-        <v>15.135394</v>
+        <v>14.94343875</v>
       </c>
       <c r="P14">
-        <v>45.406182</v>
+        <v>44.83031625</v>
       </c>
       <c r="Q14">
-        <v>73.80618200000001</v>
+        <v>73.23031625000002</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1179952896492745</v>
+        <v>0.1186369114911628</v>
       </c>
       <c r="T14">
-        <v>1.407220572286319</v>
+        <v>1.419726976234829</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.37404791014031</v>
+        <v>9.271758707323098</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1084303629973117</v>
+        <v>0.1082098711032617</v>
       </c>
       <c r="C15">
-        <v>924.4682573517873</v>
+        <v>916.9079442307802</v>
       </c>
       <c r="D15">
-        <v>800.9382573517873</v>
+        <v>803.7679442307801</v>
       </c>
       <c r="E15">
-        <v>57.16999999999999</v>
+        <v>67.56</v>
       </c>
       <c r="F15">
-        <v>135.07</v>
+        <v>145.46</v>
       </c>
       <c r="G15">
         <v>258.6</v>
@@ -2517,28 +2517,28 @@
         <v>67</v>
       </c>
       <c r="M15">
-        <v>7.226245</v>
+        <v>7.78211</v>
       </c>
       <c r="N15">
-        <v>59.773755</v>
+        <v>59.21789</v>
       </c>
       <c r="O15">
-        <v>14.94343875</v>
+        <v>14.8044725</v>
       </c>
       <c r="P15">
-        <v>44.83031625</v>
+        <v>44.41341749999999</v>
       </c>
       <c r="Q15">
-        <v>73.23031625000002</v>
+        <v>72.8134175</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1186369114911628</v>
+        <v>0.1192934547712346</v>
       </c>
       <c r="T15">
-        <v>1.419726976234829</v>
+        <v>1.432524226786793</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.271758707323098</v>
+        <v>8.609490228228591</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1082098711032617</v>
+        <v>0.1079893792092119</v>
       </c>
       <c r="C16">
-        <v>916.9079442307802</v>
+        <v>909.3676963693864</v>
       </c>
       <c r="D16">
-        <v>803.7679442307801</v>
+        <v>806.6176963693863</v>
       </c>
       <c r="E16">
-        <v>67.56</v>
+        <v>77.95000000000002</v>
       </c>
       <c r="F16">
-        <v>145.46</v>
+        <v>155.85</v>
       </c>
       <c r="G16">
         <v>258.6</v>
@@ -2599,28 +2599,28 @@
         <v>67</v>
       </c>
       <c r="M16">
-        <v>7.78211</v>
+        <v>8.337975000000002</v>
       </c>
       <c r="N16">
-        <v>59.21789</v>
+        <v>58.662025</v>
       </c>
       <c r="O16">
-        <v>14.8044725</v>
+        <v>14.66550625</v>
       </c>
       <c r="P16">
-        <v>44.41341749999999</v>
+        <v>43.99651875</v>
       </c>
       <c r="Q16">
-        <v>72.8134175</v>
+        <v>72.39651875000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1192934547712346</v>
+        <v>0.1199654461284845</v>
       </c>
       <c r="T16">
-        <v>1.432524226786793</v>
+        <v>1.445622589116449</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.609490228228591</v>
+        <v>8.03552421301335</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1079893792092119</v>
+        <v>0.1078648873151619</v>
       </c>
       <c r="C17">
-        <v>909.3676963693864</v>
+        <v>900.5956379969168</v>
       </c>
       <c r="D17">
-        <v>806.6176963693863</v>
+        <v>808.2356379969168</v>
       </c>
       <c r="E17">
-        <v>77.94999999999999</v>
+        <v>88.34</v>
       </c>
       <c r="F17">
-        <v>155.85</v>
+        <v>166.24</v>
       </c>
       <c r="G17">
         <v>258.6</v>
@@ -2681,45 +2681,45 @@
         <v>67</v>
       </c>
       <c r="M17">
-        <v>8.337975</v>
+        <v>9.026832000000001</v>
       </c>
       <c r="N17">
-        <v>58.662025</v>
+        <v>57.973168</v>
       </c>
       <c r="O17">
-        <v>14.66550625</v>
+        <v>14.493292</v>
       </c>
       <c r="P17">
-        <v>43.99651875</v>
+        <v>43.479876</v>
       </c>
       <c r="Q17">
-        <v>72.39651875000001</v>
+        <v>71.87987600000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1199654461284845</v>
+        <v>0.1206534372799547</v>
       </c>
       <c r="T17">
-        <v>1.445622589116449</v>
+        <v>1.45903281721586</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>8.035524213013352</v>
+        <v>7.422316046205357</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1078648873151619</v>
+        <v>0.1076503954211121</v>
       </c>
       <c r="C18">
-        <v>900.5956379969168</v>
+        <v>893.0085302282802</v>
       </c>
       <c r="D18">
-        <v>808.2356379969168</v>
+        <v>811.03853022828</v>
       </c>
       <c r="E18">
-        <v>88.34</v>
+        <v>98.73000000000002</v>
       </c>
       <c r="F18">
-        <v>166.24</v>
+        <v>176.63</v>
       </c>
       <c r="G18">
         <v>258.6</v>
@@ -2763,28 +2763,28 @@
         <v>67</v>
       </c>
       <c r="M18">
-        <v>9.026832000000001</v>
+        <v>9.591009000000001</v>
       </c>
       <c r="N18">
-        <v>57.973168</v>
+        <v>57.408991</v>
       </c>
       <c r="O18">
-        <v>14.493292</v>
+        <v>14.35224775</v>
       </c>
       <c r="P18">
-        <v>43.479876</v>
+        <v>43.05674325</v>
       </c>
       <c r="Q18">
-        <v>71.87987600000001</v>
+        <v>71.45674325</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1206534372799547</v>
+        <v>0.1213580065314603</v>
       </c>
       <c r="T18">
-        <v>1.45903281721586</v>
+        <v>1.472766183341762</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.422316046205357</v>
+        <v>6.985709219957982</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1076503954211121</v>
+        <v>0.1074359035270622</v>
       </c>
       <c r="C19">
-        <v>893.0085302282802</v>
+        <v>885.4409304940559</v>
       </c>
       <c r="D19">
-        <v>811.03853022828</v>
+        <v>813.8609304940559</v>
       </c>
       <c r="E19">
-        <v>98.73000000000002</v>
+        <v>109.12</v>
       </c>
       <c r="F19">
-        <v>176.63</v>
+        <v>187.02</v>
       </c>
       <c r="G19">
         <v>258.6</v>
@@ -2845,28 +2845,28 @@
         <v>67</v>
       </c>
       <c r="M19">
-        <v>9.591009000000001</v>
+        <v>10.155186</v>
       </c>
       <c r="N19">
-        <v>57.408991</v>
+        <v>56.844814</v>
       </c>
       <c r="O19">
-        <v>14.35224775</v>
+        <v>14.2112035</v>
       </c>
       <c r="P19">
-        <v>43.05674325</v>
+        <v>42.6336105</v>
       </c>
       <c r="Q19">
-        <v>71.45674325</v>
+        <v>71.03361050000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1213580065314603</v>
+        <v>0.1220797603988563</v>
       </c>
       <c r="T19">
-        <v>1.472766183341762</v>
+        <v>1.486834509617077</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.985709219957982</v>
+        <v>6.597614263293651</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1074359035270622</v>
+        <v>0.1072214116330123</v>
       </c>
       <c r="C20">
-        <v>885.4409304940559</v>
+        <v>877.8930431683447</v>
       </c>
       <c r="D20">
-        <v>813.8609304940558</v>
+        <v>816.7030431683446</v>
       </c>
       <c r="E20">
-        <v>109.12</v>
+        <v>119.51</v>
       </c>
       <c r="F20">
-        <v>187.02</v>
+        <v>197.41</v>
       </c>
       <c r="G20">
         <v>258.6</v>
@@ -2927,28 +2927,28 @@
         <v>67</v>
       </c>
       <c r="M20">
-        <v>10.155186</v>
+        <v>10.719363</v>
       </c>
       <c r="N20">
-        <v>56.844814</v>
+        <v>56.280637</v>
       </c>
       <c r="O20">
-        <v>14.2112035</v>
+        <v>14.07015925</v>
       </c>
       <c r="P20">
-        <v>42.6336105</v>
+        <v>42.21047775</v>
       </c>
       <c r="Q20">
-        <v>71.03361050000001</v>
+        <v>70.61047775</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1220797603988563</v>
+        <v>0.1228193353493978</v>
       </c>
       <c r="T20">
-        <v>1.486834509617077</v>
+        <v>1.501250201973263</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.597614263293652</v>
+        <v>6.250371407330827</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1072214116330123</v>
+        <v>0.1071569197389624</v>
       </c>
       <c r="C21">
-        <v>877.8930431683447</v>
+        <v>868.3614748880973</v>
       </c>
       <c r="D21">
-        <v>816.7030431683446</v>
+        <v>817.5614748880972</v>
       </c>
       <c r="E21">
-        <v>119.51</v>
+        <v>129.9</v>
       </c>
       <c r="F21">
-        <v>197.41</v>
+        <v>207.8</v>
       </c>
       <c r="G21">
         <v>258.6</v>
@@ -3009,45 +3009,45 @@
         <v>67</v>
       </c>
       <c r="M21">
-        <v>10.719363</v>
+        <v>11.49134</v>
       </c>
       <c r="N21">
-        <v>56.280637</v>
+        <v>55.50866</v>
       </c>
       <c r="O21">
-        <v>14.07015925</v>
+        <v>13.877165</v>
       </c>
       <c r="P21">
-        <v>42.21047775</v>
+        <v>41.631495</v>
       </c>
       <c r="Q21">
-        <v>70.61047775</v>
+        <v>70.03149500000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1228193353493978</v>
+        <v>0.1235773996737029</v>
       </c>
       <c r="T21">
-        <v>1.501250201973263</v>
+        <v>1.516026286638354</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.250371407330827</v>
+        <v>5.83047755962316</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1071569197389624</v>
+        <v>0.1069499278449124</v>
       </c>
       <c r="C22">
-        <v>868.3614748880973</v>
+        <v>860.7389123022267</v>
       </c>
       <c r="D22">
-        <v>817.5614748880972</v>
+        <v>820.3289123022266</v>
       </c>
       <c r="E22">
-        <v>129.9</v>
+        <v>140.29</v>
       </c>
       <c r="F22">
-        <v>207.8</v>
+        <v>218.19</v>
       </c>
       <c r="G22">
         <v>258.6</v>
@@ -3091,28 +3091,28 @@
         <v>67</v>
       </c>
       <c r="M22">
-        <v>11.49134</v>
+        <v>12.065907</v>
       </c>
       <c r="N22">
-        <v>55.50866</v>
+        <v>54.934093</v>
       </c>
       <c r="O22">
-        <v>13.877165</v>
+        <v>13.73352325</v>
       </c>
       <c r="P22">
-        <v>41.631495</v>
+        <v>41.20056975</v>
       </c>
       <c r="Q22">
-        <v>70.03149500000001</v>
+        <v>69.60056975000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1235773996737029</v>
+        <v>0.1243546554998892</v>
       </c>
       <c r="T22">
-        <v>1.516026286638354</v>
+        <v>1.531176449396233</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.83047755962316</v>
+        <v>5.552835771069676</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1069499278449124</v>
+        <v>0.1067429359508625</v>
       </c>
       <c r="C23">
-        <v>860.7389123022267</v>
+        <v>853.1351488471518</v>
       </c>
       <c r="D23">
-        <v>820.3289123022266</v>
+        <v>823.1151488471519</v>
       </c>
       <c r="E23">
-        <v>140.29</v>
+        <v>150.68</v>
       </c>
       <c r="F23">
-        <v>218.19</v>
+        <v>228.58</v>
       </c>
       <c r="G23">
         <v>258.6</v>
@@ -3173,28 +3173,28 @@
         <v>67</v>
       </c>
       <c r="M23">
-        <v>12.065907</v>
+        <v>12.640474</v>
       </c>
       <c r="N23">
-        <v>54.934093</v>
+        <v>54.359526</v>
       </c>
       <c r="O23">
-        <v>13.73352325</v>
+        <v>13.5898815</v>
       </c>
       <c r="P23">
-        <v>41.20056975</v>
+        <v>40.7696445</v>
       </c>
       <c r="Q23">
-        <v>69.60056975000001</v>
+        <v>69.1696445</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1243546554998892</v>
+        <v>0.1251518409626443</v>
       </c>
       <c r="T23">
-        <v>1.531176449396233</v>
+        <v>1.546715077865851</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.552835771069676</v>
+        <v>5.300434145111963</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1067429359508625</v>
+        <v>0.1065359440568127</v>
       </c>
       <c r="C24">
-        <v>853.1351488471518</v>
+        <v>845.5503767287116</v>
       </c>
       <c r="D24">
-        <v>823.1151488471519</v>
+        <v>825.9203767287116</v>
       </c>
       <c r="E24">
-        <v>150.68</v>
+        <v>161.07</v>
       </c>
       <c r="F24">
-        <v>228.58</v>
+        <v>238.97</v>
       </c>
       <c r="G24">
         <v>258.6</v>
@@ -3255,28 +3255,28 @@
         <v>67</v>
       </c>
       <c r="M24">
-        <v>12.640474</v>
+        <v>13.215041</v>
       </c>
       <c r="N24">
-        <v>54.359526</v>
+        <v>53.784959</v>
       </c>
       <c r="O24">
-        <v>13.5898815</v>
+        <v>13.44623975</v>
       </c>
       <c r="P24">
-        <v>40.7696445</v>
+        <v>40.33871925</v>
       </c>
       <c r="Q24">
-        <v>69.1696445</v>
+        <v>68.73871925</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1251518409626443</v>
+        <v>0.1259697325413151</v>
       </c>
       <c r="T24">
-        <v>1.546715077865851</v>
+        <v>1.562657307074941</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.300434145111963</v>
+        <v>5.069980486628834</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1065359440568127</v>
+        <v>0.1063289521627627</v>
       </c>
       <c r="C25">
-        <v>845.5503767287116</v>
+        <v>837.9847907819036</v>
       </c>
       <c r="D25">
-        <v>825.9203767287116</v>
+        <v>828.7447907819037</v>
       </c>
       <c r="E25">
-        <v>161.07</v>
+        <v>171.46</v>
       </c>
       <c r="F25">
-        <v>238.97</v>
+        <v>249.36</v>
       </c>
       <c r="G25">
         <v>258.6</v>
@@ -3337,28 +3337,28 @@
         <v>67</v>
       </c>
       <c r="M25">
-        <v>13.215041</v>
+        <v>13.789608</v>
       </c>
       <c r="N25">
-        <v>53.784959</v>
+        <v>53.210392</v>
       </c>
       <c r="O25">
-        <v>13.44623975</v>
+        <v>13.302598</v>
       </c>
       <c r="P25">
-        <v>40.33871925</v>
+        <v>39.907794</v>
       </c>
       <c r="Q25">
-        <v>68.73871925</v>
+        <v>68.307794</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1259697325413151</v>
+        <v>0.1268091475825825</v>
       </c>
       <c r="T25">
-        <v>1.562657307074941</v>
+        <v>1.579019068631638</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.069980486628834</v>
+        <v>4.858731299685966</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1063289521627627</v>
+        <v>0.1061219602687128</v>
       </c>
       <c r="C26">
-        <v>837.9847907819036</v>
+        <v>830.438588515992</v>
       </c>
       <c r="D26">
-        <v>828.7447907819037</v>
+        <v>831.588588515992</v>
       </c>
       <c r="E26">
-        <v>171.46</v>
+        <v>181.85</v>
       </c>
       <c r="F26">
-        <v>249.36</v>
+        <v>259.75</v>
       </c>
       <c r="G26">
         <v>258.6</v>
@@ -3419,28 +3419,28 @@
         <v>67</v>
       </c>
       <c r="M26">
-        <v>13.789608</v>
+        <v>14.364175</v>
       </c>
       <c r="N26">
-        <v>53.210392</v>
+        <v>52.635825</v>
       </c>
       <c r="O26">
-        <v>13.302598</v>
+        <v>13.15895625</v>
       </c>
       <c r="P26">
-        <v>39.907794</v>
+        <v>39.47686874999999</v>
       </c>
       <c r="Q26">
-        <v>68.307794</v>
+        <v>67.87686875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1268091475825825</v>
+        <v>0.1276709470249505</v>
       </c>
       <c r="T26">
-        <v>1.579019068631638</v>
+        <v>1.595817143829847</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.858731299685966</v>
+        <v>4.664382047698528</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1061219602687128</v>
+        <v>0.106402468374663</v>
       </c>
       <c r="C27">
-        <v>830.438588515992</v>
+        <v>816.1994492622538</v>
       </c>
       <c r="D27">
-        <v>831.588588515992</v>
+        <v>827.7394492622537</v>
       </c>
       <c r="E27">
-        <v>181.85</v>
+        <v>192.24</v>
       </c>
       <c r="F27">
-        <v>259.75</v>
+        <v>270.14</v>
       </c>
       <c r="G27">
         <v>258.6</v>
@@ -3501,45 +3501,45 @@
         <v>67</v>
       </c>
       <c r="M27">
-        <v>14.364175</v>
+        <v>15.614092</v>
       </c>
       <c r="N27">
-        <v>52.635825</v>
+        <v>51.385908</v>
       </c>
       <c r="O27">
-        <v>13.15895625</v>
+        <v>12.846477</v>
       </c>
       <c r="P27">
-        <v>39.47686874999999</v>
+        <v>38.539431</v>
       </c>
       <c r="Q27">
-        <v>67.87686875</v>
+        <v>66.93943100000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1276709470249505</v>
+        <v>0.1285560383441391</v>
       </c>
       <c r="T27">
-        <v>1.595817143829847</v>
+        <v>1.61306922106044</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.664382047698528</v>
+        <v>4.290995595517177</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.106402468374663</v>
+        <v>0.1062142264806131</v>
       </c>
       <c r="C28">
-        <v>816.1994492622538</v>
+        <v>808.3885643281224</v>
       </c>
       <c r="D28">
-        <v>827.7394492622537</v>
+        <v>830.3185643281223</v>
       </c>
       <c r="E28">
-        <v>192.24</v>
+        <v>202.63</v>
       </c>
       <c r="F28">
-        <v>270.14</v>
+        <v>280.53</v>
       </c>
       <c r="G28">
         <v>258.6</v>
@@ -3583,28 +3583,28 @@
         <v>67</v>
       </c>
       <c r="M28">
-        <v>15.614092</v>
+        <v>16.214634</v>
       </c>
       <c r="N28">
-        <v>51.385908</v>
+        <v>50.785366</v>
       </c>
       <c r="O28">
-        <v>12.846477</v>
+        <v>12.6963415</v>
       </c>
       <c r="P28">
-        <v>38.539431</v>
+        <v>38.08902449999999</v>
       </c>
       <c r="Q28">
-        <v>66.93943100000001</v>
+        <v>66.4890245</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1285560383441391</v>
+        <v>0.1294653787405658</v>
       </c>
       <c r="T28">
-        <v>1.61306922106044</v>
+        <v>1.630793957941186</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.290995595517177</v>
+        <v>4.132069832720244</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1062142264806131</v>
+        <v>0.1067609845865631</v>
       </c>
       <c r="C29">
-        <v>808.3885643281224</v>
+        <v>790.5514502658061</v>
       </c>
       <c r="D29">
-        <v>830.3185643281223</v>
+        <v>822.8714502658063</v>
       </c>
       <c r="E29">
-        <v>202.63</v>
+        <v>213.02</v>
       </c>
       <c r="F29">
-        <v>280.53</v>
+        <v>290.92</v>
       </c>
       <c r="G29">
         <v>258.6</v>
@@ -3665,45 +3665,45 @@
         <v>67</v>
       </c>
       <c r="M29">
-        <v>16.214634</v>
+        <v>17.833396</v>
       </c>
       <c r="N29">
-        <v>50.785366</v>
+        <v>49.166604</v>
       </c>
       <c r="O29">
-        <v>12.6963415</v>
+        <v>12.291651</v>
       </c>
       <c r="P29">
-        <v>38.08902449999999</v>
+        <v>36.874953</v>
       </c>
       <c r="Q29">
-        <v>66.4890245</v>
+        <v>65.27495300000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1294653787405658</v>
+        <v>0.1303999785924488</v>
       </c>
       <c r="T29">
-        <v>1.630793957941186</v>
+        <v>1.649011048624175</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.132069832720244</v>
+        <v>3.756996143639719</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1067609845865631</v>
+        <v>0.1065989926925132</v>
       </c>
       <c r="C30">
-        <v>790.5514502658061</v>
+        <v>782.353896207506</v>
       </c>
       <c r="D30">
-        <v>822.8714502658063</v>
+        <v>825.063896207506</v>
       </c>
       <c r="E30">
-        <v>213.02</v>
+        <v>223.4100000000001</v>
       </c>
       <c r="F30">
-        <v>290.92</v>
+        <v>301.3100000000001</v>
       </c>
       <c r="G30">
         <v>258.6</v>
@@ -3747,28 +3747,28 @@
         <v>67</v>
       </c>
       <c r="M30">
-        <v>17.833396</v>
+        <v>18.470303</v>
       </c>
       <c r="N30">
-        <v>49.166604</v>
+        <v>48.529697</v>
       </c>
       <c r="O30">
-        <v>12.291651</v>
+        <v>12.13242425</v>
       </c>
       <c r="P30">
-        <v>36.874953</v>
+        <v>36.39727275</v>
       </c>
       <c r="Q30">
-        <v>65.27495300000001</v>
+        <v>64.79727275</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1303999785924488</v>
+        <v>0.1313609052007229</v>
       </c>
       <c r="T30">
-        <v>1.649011048624175</v>
+        <v>1.667741296791192</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.756996143639719</v>
+        <v>3.627444552479728</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1065989926925132</v>
+        <v>0.1064370007984633</v>
       </c>
       <c r="C31">
-        <v>782.3538962075061</v>
+        <v>774.1680563984607</v>
       </c>
       <c r="D31">
-        <v>825.063896207506</v>
+        <v>827.2680563984607</v>
       </c>
       <c r="E31">
-        <v>223.41</v>
+        <v>233.8</v>
       </c>
       <c r="F31">
-        <v>301.31</v>
+        <v>311.7</v>
       </c>
       <c r="G31">
         <v>258.6</v>
@@ -3829,28 +3829,28 @@
         <v>67</v>
       </c>
       <c r="M31">
-        <v>18.470303</v>
+        <v>19.10721</v>
       </c>
       <c r="N31">
-        <v>48.529697</v>
+        <v>47.89279000000001</v>
       </c>
       <c r="O31">
-        <v>12.13242425</v>
+        <v>11.9731975</v>
       </c>
       <c r="P31">
-        <v>36.39727275</v>
+        <v>35.91959250000001</v>
       </c>
       <c r="Q31">
-        <v>64.79727275</v>
+        <v>64.31959250000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1313609052007229</v>
+        <v>0.1323492868549476</v>
       </c>
       <c r="T31">
-        <v>1.667741296791192</v>
+        <v>1.687006694905838</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.627444552479729</v>
+        <v>3.506529734063739</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1064370007984633</v>
+        <v>0.1069260089044134</v>
       </c>
       <c r="C32">
-        <v>774.1680563984607</v>
+        <v>757.1599114774492</v>
       </c>
       <c r="D32">
-        <v>827.2680563984607</v>
+        <v>820.6499114774492</v>
       </c>
       <c r="E32">
-        <v>233.8</v>
+        <v>244.19</v>
       </c>
       <c r="F32">
-        <v>311.7</v>
+        <v>322.09</v>
       </c>
       <c r="G32">
         <v>258.6</v>
@@ -3911,45 +3911,45 @@
         <v>67</v>
       </c>
       <c r="M32">
-        <v>19.10721</v>
+        <v>20.645969</v>
       </c>
       <c r="N32">
-        <v>47.89279000000001</v>
+        <v>46.354031</v>
       </c>
       <c r="O32">
-        <v>11.9731975</v>
+        <v>11.58850775</v>
       </c>
       <c r="P32">
-        <v>35.91959250000001</v>
+        <v>34.76552325</v>
       </c>
       <c r="Q32">
-        <v>64.31959250000001</v>
+        <v>63.16552325000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1323492868549476</v>
+        <v>0.1333663172527731</v>
       </c>
       <c r="T32">
-        <v>1.687006694905838</v>
+        <v>1.70683051035714</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.506529734063739</v>
+        <v>3.24518553718646</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1069260089044134</v>
+        <v>0.1067850170103636</v>
       </c>
       <c r="C33">
-        <v>757.1599114774492</v>
+        <v>748.6671805288202</v>
       </c>
       <c r="D33">
-        <v>820.6499114774492</v>
+        <v>822.54718052882</v>
       </c>
       <c r="E33">
-        <v>244.19</v>
+        <v>254.58</v>
       </c>
       <c r="F33">
-        <v>322.09</v>
+        <v>332.48</v>
       </c>
       <c r="G33">
         <v>258.6</v>
@@ -3993,28 +3993,28 @@
         <v>67</v>
       </c>
       <c r="M33">
-        <v>20.645969</v>
+        <v>21.311968</v>
       </c>
       <c r="N33">
-        <v>46.354031</v>
+        <v>45.68803199999999</v>
       </c>
       <c r="O33">
-        <v>11.58850775</v>
+        <v>11.422008</v>
       </c>
       <c r="P33">
-        <v>34.76552325</v>
+        <v>34.26602399999999</v>
       </c>
       <c r="Q33">
-        <v>63.16552325000001</v>
+        <v>62.666024</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1333663172527731</v>
+        <v>0.1344132603093582</v>
       </c>
       <c r="T33">
-        <v>1.70683051035714</v>
+        <v>1.727237379204069</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.24518553718646</v>
+        <v>3.143773489149382</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1067850170103636</v>
+        <v>0.1066440251163136</v>
       </c>
       <c r="C34">
-        <v>748.6671805288202</v>
+        <v>740.1832425407673</v>
       </c>
       <c r="D34">
-        <v>822.54718052882</v>
+        <v>824.4532425407674</v>
       </c>
       <c r="E34">
-        <v>254.58</v>
+        <v>264.97</v>
       </c>
       <c r="F34">
-        <v>332.48</v>
+        <v>342.87</v>
       </c>
       <c r="G34">
         <v>258.6</v>
@@ -4075,28 +4075,28 @@
         <v>67</v>
       </c>
       <c r="M34">
-        <v>21.311968</v>
+        <v>21.977967</v>
       </c>
       <c r="N34">
-        <v>45.68803199999999</v>
+        <v>45.02203299999999</v>
       </c>
       <c r="O34">
-        <v>11.422008</v>
+        <v>11.25550825</v>
       </c>
       <c r="P34">
-        <v>34.26602399999999</v>
+        <v>33.76652474999999</v>
       </c>
       <c r="Q34">
-        <v>62.666024</v>
+        <v>62.16652475</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1344132603093582</v>
+        <v>0.1354914553974831</v>
       </c>
       <c r="T34">
-        <v>1.727237379204069</v>
+        <v>1.748253408315086</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.143773489149382</v>
+        <v>3.048507625841825</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1066440251163136</v>
+        <v>0.1084920332222637</v>
       </c>
       <c r="C35">
-        <v>740.1832425407673</v>
+        <v>705.4903734698196</v>
       </c>
       <c r="D35">
-        <v>824.4532425407674</v>
+        <v>800.1503734698196</v>
       </c>
       <c r="E35">
-        <v>264.97</v>
+        <v>275.36</v>
       </c>
       <c r="F35">
-        <v>342.87</v>
+        <v>353.26</v>
       </c>
       <c r="G35">
         <v>258.6</v>
@@ -4157,45 +4157,45 @@
         <v>67</v>
       </c>
       <c r="M35">
-        <v>21.977967</v>
+        <v>25.399394</v>
       </c>
       <c r="N35">
-        <v>45.02203299999999</v>
+        <v>41.600606</v>
       </c>
       <c r="O35">
-        <v>11.25550825</v>
+        <v>10.4001515</v>
       </c>
       <c r="P35">
-        <v>33.76652474999999</v>
+        <v>31.2004545</v>
       </c>
       <c r="Q35">
-        <v>62.16652475</v>
+        <v>59.6004545</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1354914553974831</v>
+        <v>0.136602323064036</v>
       </c>
       <c r="T35">
-        <v>1.748253408315086</v>
+        <v>1.769906286793103</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.048507625841825</v>
+        <v>2.637858210317931</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1084920332222637</v>
+        <v>0.1084095413282138</v>
       </c>
       <c r="C36">
-        <v>705.4903734698196</v>
+        <v>696.1546204493056</v>
       </c>
       <c r="D36">
-        <v>800.1503734698196</v>
+        <v>801.2046204493057</v>
       </c>
       <c r="E36">
-        <v>275.36</v>
+        <v>285.75</v>
       </c>
       <c r="F36">
-        <v>353.26</v>
+        <v>363.65</v>
       </c>
       <c r="G36">
         <v>258.6</v>
@@ -4239,28 +4239,28 @@
         <v>67</v>
       </c>
       <c r="M36">
-        <v>25.399394</v>
+        <v>26.146435</v>
       </c>
       <c r="N36">
-        <v>41.600606</v>
+        <v>40.853565</v>
       </c>
       <c r="O36">
-        <v>10.4001515</v>
+        <v>10.21339125</v>
       </c>
       <c r="P36">
-        <v>31.2004545</v>
+        <v>30.64017375</v>
       </c>
       <c r="Q36">
-        <v>59.6004545</v>
+        <v>59.04017375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.136602323064036</v>
+        <v>0.1377473712741751</v>
       </c>
       <c r="T36">
-        <v>1.769906286793103</v>
+        <v>1.792225407685828</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.637858210317931</v>
+        <v>2.562490832880275</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1084095413282138</v>
+        <v>0.1093800494341639</v>
       </c>
       <c r="C37">
-        <v>696.1546204493056</v>
+        <v>673.5347529737244</v>
       </c>
       <c r="D37">
-        <v>801.2046204493057</v>
+        <v>788.9747529737243</v>
       </c>
       <c r="E37">
-        <v>285.75</v>
+        <v>296.14</v>
       </c>
       <c r="F37">
-        <v>363.65</v>
+        <v>374.04</v>
       </c>
       <c r="G37">
         <v>258.6</v>
@@ -4321,45 +4321,45 @@
         <v>67</v>
       </c>
       <c r="M37">
-        <v>26.146435</v>
+        <v>28.352232</v>
       </c>
       <c r="N37">
-        <v>40.853565</v>
+        <v>38.647768</v>
       </c>
       <c r="O37">
-        <v>10.21339125</v>
+        <v>9.661942</v>
       </c>
       <c r="P37">
-        <v>30.64017375</v>
+        <v>28.985826</v>
       </c>
       <c r="Q37">
-        <v>59.04017375</v>
+        <v>57.38582600000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1377473712741751</v>
+        <v>0.1389282022408811</v>
       </c>
       <c r="T37">
-        <v>1.792225407685828</v>
+        <v>1.815242001106451</v>
       </c>
       <c r="U37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.562490832880275</v>
+        <v>2.363129647076815</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1093800494341639</v>
+        <v>0.109326807540114</v>
       </c>
       <c r="C38">
-        <v>673.5347529737244</v>
+        <v>663.8059936661571</v>
       </c>
       <c r="D38">
-        <v>788.9747529737243</v>
+        <v>789.6359936661571</v>
       </c>
       <c r="E38">
-        <v>296.14</v>
+        <v>306.53</v>
       </c>
       <c r="F38">
-        <v>374.04</v>
+        <v>384.43</v>
       </c>
       <c r="G38">
         <v>258.6</v>
@@ -4403,28 +4403,28 @@
         <v>67</v>
       </c>
       <c r="M38">
-        <v>28.352232</v>
+        <v>29.139794</v>
       </c>
       <c r="N38">
-        <v>38.647768</v>
+        <v>37.860206</v>
       </c>
       <c r="O38">
-        <v>9.661942</v>
+        <v>9.4650515</v>
       </c>
       <c r="P38">
-        <v>28.985826</v>
+        <v>28.3951545</v>
       </c>
       <c r="Q38">
-        <v>57.38582600000001</v>
+        <v>56.7951545</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1389282022408811</v>
+        <v>0.1401465199049429</v>
       </c>
       <c r="T38">
-        <v>1.815242001106451</v>
+        <v>1.83898928003249</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.363129647076816</v>
+        <v>2.299261278236902</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.109326807540114</v>
+        <v>0.1092735656460641</v>
       </c>
       <c r="C39">
-        <v>663.8059936661571</v>
+        <v>654.0783436615427</v>
       </c>
       <c r="D39">
-        <v>789.6359936661571</v>
+        <v>790.2983436615426</v>
       </c>
       <c r="E39">
-        <v>306.53</v>
+        <v>316.92</v>
       </c>
       <c r="F39">
-        <v>384.43</v>
+        <v>394.82</v>
       </c>
       <c r="G39">
         <v>258.6</v>
@@ -4485,28 +4485,28 @@
         <v>67</v>
       </c>
       <c r="M39">
-        <v>29.139794</v>
+        <v>29.927356</v>
       </c>
       <c r="N39">
-        <v>37.860206</v>
+        <v>37.072644</v>
       </c>
       <c r="O39">
-        <v>9.4650515</v>
+        <v>9.268160999999999</v>
       </c>
       <c r="P39">
-        <v>28.3951545</v>
+        <v>27.804483</v>
       </c>
       <c r="Q39">
-        <v>56.7951545</v>
+        <v>56.204483</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1401465199049429</v>
+        <v>0.1414041381388131</v>
       </c>
       <c r="T39">
-        <v>1.83898928003249</v>
+        <v>1.863502600214208</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.299261278236902</v>
+        <v>2.238754402493825</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1092735656460641</v>
+        <v>0.1092203237520142</v>
       </c>
       <c r="C40">
-        <v>654.0783436615427</v>
+        <v>644.3518057536876</v>
       </c>
       <c r="D40">
-        <v>790.2983436615426</v>
+        <v>790.9618057536877</v>
       </c>
       <c r="E40">
-        <v>316.92</v>
+        <v>327.3100000000001</v>
       </c>
       <c r="F40">
-        <v>394.82</v>
+        <v>405.21</v>
       </c>
       <c r="G40">
         <v>258.6</v>
@@ -4567,28 +4567,28 @@
         <v>67</v>
       </c>
       <c r="M40">
-        <v>29.927356</v>
+        <v>30.714918</v>
       </c>
       <c r="N40">
-        <v>37.072644</v>
+        <v>36.285082</v>
       </c>
       <c r="O40">
-        <v>9.268160999999999</v>
+        <v>9.071270499999999</v>
       </c>
       <c r="P40">
-        <v>27.804483</v>
+        <v>27.2138115</v>
       </c>
       <c r="Q40">
-        <v>56.204483</v>
+        <v>55.6138115</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1414041381388131</v>
+        <v>0.1427029897574004</v>
       </c>
       <c r="T40">
-        <v>1.863502600214208</v>
+        <v>1.88881963581172</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.238754402493825</v>
+        <v>2.181350443455522</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1092203237520142</v>
+        <v>0.1091670818579643</v>
       </c>
       <c r="C41">
-        <v>644.3518057536876</v>
+        <v>634.6263827457898</v>
       </c>
       <c r="D41">
-        <v>790.9618057536877</v>
+        <v>791.6263827457898</v>
       </c>
       <c r="E41">
-        <v>327.3100000000001</v>
+        <v>337.7</v>
       </c>
       <c r="F41">
-        <v>405.21</v>
+        <v>415.6</v>
       </c>
       <c r="G41">
         <v>258.6</v>
@@ -4649,28 +4649,28 @@
         <v>67</v>
       </c>
       <c r="M41">
-        <v>30.714918</v>
+        <v>31.50248000000001</v>
       </c>
       <c r="N41">
-        <v>36.285082</v>
+        <v>35.49751999999999</v>
       </c>
       <c r="O41">
-        <v>9.071270499999999</v>
+        <v>8.874379999999999</v>
       </c>
       <c r="P41">
-        <v>27.2138115</v>
+        <v>26.62314</v>
       </c>
       <c r="Q41">
-        <v>55.6138115</v>
+        <v>55.02314</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1427029897574004</v>
+        <v>0.1440451364299405</v>
       </c>
       <c r="T41">
-        <v>1.88881963581172</v>
+        <v>1.914980572595816</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.181350443455522</v>
+        <v>2.126816682369133</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1091670818579643</v>
+        <v>0.1091138399639144</v>
       </c>
       <c r="C42">
-        <v>634.6263827457898</v>
+        <v>624.902077450475</v>
       </c>
       <c r="D42">
-        <v>791.6263827457898</v>
+        <v>792.2920774504748</v>
       </c>
       <c r="E42">
-        <v>337.7</v>
+        <v>348.09</v>
       </c>
       <c r="F42">
-        <v>415.6</v>
+        <v>425.99</v>
       </c>
       <c r="G42">
         <v>258.6</v>
@@ -4731,28 +4731,28 @@
         <v>67</v>
       </c>
       <c r="M42">
-        <v>31.50248000000001</v>
+        <v>32.29004200000001</v>
       </c>
       <c r="N42">
-        <v>35.49751999999999</v>
+        <v>34.70995799999999</v>
       </c>
       <c r="O42">
-        <v>8.874379999999999</v>
+        <v>8.677489499999998</v>
       </c>
       <c r="P42">
-        <v>26.62314</v>
+        <v>26.03246849999999</v>
       </c>
       <c r="Q42">
-        <v>55.02314</v>
+        <v>54.4324685</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1440451364299405</v>
+        <v>0.145432779599855</v>
       </c>
       <c r="T42">
-        <v>1.914980572595816</v>
+        <v>1.942028320796322</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.126816682369133</v>
+        <v>2.074943104750374</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1091138399639144</v>
+        <v>0.1090605980698645</v>
       </c>
       <c r="C43">
-        <v>624.902077450475</v>
+        <v>615.1788926898375</v>
       </c>
       <c r="D43">
-        <v>792.2920774504748</v>
+        <v>792.9588926898376</v>
       </c>
       <c r="E43">
-        <v>348.09</v>
+        <v>358.48</v>
       </c>
       <c r="F43">
-        <v>425.99</v>
+        <v>436.3800000000001</v>
       </c>
       <c r="G43">
         <v>258.6</v>
@@ -4813,28 +4813,28 @@
         <v>67</v>
       </c>
       <c r="M43">
-        <v>32.29004200000001</v>
+        <v>33.07760400000001</v>
       </c>
       <c r="N43">
-        <v>34.70995799999999</v>
+        <v>33.92239599999999</v>
       </c>
       <c r="O43">
-        <v>8.677489499999998</v>
+        <v>8.480598999999998</v>
       </c>
       <c r="P43">
-        <v>26.03246849999999</v>
+        <v>25.44179699999999</v>
       </c>
       <c r="Q43">
-        <v>54.4324685</v>
+        <v>53.841797</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.145432779599855</v>
+        <v>0.1468682725342492</v>
       </c>
       <c r="T43">
-        <v>1.942028320796322</v>
+        <v>1.970008749969259</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.074943104750374</v>
+        <v>2.025539697494413</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1090605980698645</v>
+        <v>0.1135868561758146</v>
       </c>
       <c r="C44">
-        <v>615.1788926898377</v>
+        <v>551.8415099934982</v>
       </c>
       <c r="D44">
-        <v>792.9588926898376</v>
+        <v>740.0115099934982</v>
       </c>
       <c r="E44">
-        <v>358.48</v>
+        <v>368.87</v>
       </c>
       <c r="F44">
-        <v>436.38</v>
+        <v>446.77</v>
       </c>
       <c r="G44">
         <v>258.6</v>
@@ -4895,45 +4895,45 @@
         <v>67</v>
       </c>
       <c r="M44">
-        <v>33.077604</v>
+        <v>40.2093</v>
       </c>
       <c r="N44">
-        <v>33.922396</v>
+        <v>26.7907</v>
       </c>
       <c r="O44">
-        <v>8.480599</v>
+        <v>6.697675</v>
       </c>
       <c r="P44">
-        <v>25.441797</v>
+        <v>20.093025</v>
       </c>
       <c r="Q44">
-        <v>53.84179700000001</v>
+        <v>48.493025</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1468682725342492</v>
+        <v>0.14835413364178</v>
       </c>
       <c r="T44">
-        <v>1.970008749969259</v>
+        <v>1.99897094858686</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.025539697494414</v>
+        <v>1.666281183706257</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1135868561758146</v>
+        <v>0.1136401142817647</v>
       </c>
       <c r="C45">
-        <v>551.8415099934982</v>
+        <v>540.8705615116037</v>
       </c>
       <c r="D45">
-        <v>740.0115099934982</v>
+        <v>739.4305615116037</v>
       </c>
       <c r="E45">
-        <v>368.87</v>
+        <v>379.26</v>
       </c>
       <c r="F45">
-        <v>446.77</v>
+        <v>457.16</v>
       </c>
       <c r="G45">
         <v>258.6</v>
@@ -4977,28 +4977,28 @@
         <v>67</v>
       </c>
       <c r="M45">
-        <v>40.2093</v>
+        <v>41.1444</v>
       </c>
       <c r="N45">
-        <v>26.7907</v>
+        <v>25.8556</v>
       </c>
       <c r="O45">
-        <v>6.697675</v>
+        <v>6.463900000000001</v>
       </c>
       <c r="P45">
-        <v>20.093025</v>
+        <v>19.3917</v>
       </c>
       <c r="Q45">
-        <v>48.493025</v>
+        <v>47.79170000000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.14835413364178</v>
+        <v>0.149893061217437</v>
       </c>
       <c r="T45">
-        <v>1.99897094858686</v>
+        <v>2.028967511440805</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.666281183706257</v>
+        <v>1.628411156803842</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1136401142817647</v>
+        <v>0.1136933723877148</v>
       </c>
       <c r="C46">
-        <v>540.8705615116037</v>
+        <v>529.900524465236</v>
       </c>
       <c r="D46">
-        <v>739.4305615116037</v>
+        <v>738.8505244652359</v>
       </c>
       <c r="E46">
-        <v>379.26</v>
+        <v>389.65</v>
       </c>
       <c r="F46">
-        <v>457.16</v>
+        <v>467.55</v>
       </c>
       <c r="G46">
         <v>258.6</v>
@@ -5059,28 +5059,28 @@
         <v>67</v>
       </c>
       <c r="M46">
-        <v>41.1444</v>
+        <v>42.0795</v>
       </c>
       <c r="N46">
-        <v>25.8556</v>
+        <v>24.9205</v>
       </c>
       <c r="O46">
-        <v>6.463900000000001</v>
+        <v>6.230124999999999</v>
       </c>
       <c r="P46">
-        <v>19.3917</v>
+        <v>18.690375</v>
       </c>
       <c r="Q46">
-        <v>47.79170000000001</v>
+        <v>47.090375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.149893061217437</v>
+        <v>0.1514879497958452</v>
       </c>
       <c r="T46">
-        <v>2.028967511440805</v>
+        <v>2.060054858398529</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.628411156803842</v>
+        <v>1.592224242208201</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1136933723877148</v>
+        <v>0.1137466304936649</v>
       </c>
       <c r="C47">
-        <v>529.900524465236</v>
+        <v>518.931396711183</v>
       </c>
       <c r="D47">
-        <v>738.8505244652359</v>
+        <v>738.2713967111829</v>
       </c>
       <c r="E47">
-        <v>389.65</v>
+        <v>400.04</v>
       </c>
       <c r="F47">
-        <v>467.55</v>
+        <v>477.94</v>
       </c>
       <c r="G47">
         <v>258.6</v>
@@ -5141,28 +5141,28 @@
         <v>67</v>
       </c>
       <c r="M47">
-        <v>42.0795</v>
+        <v>43.0146</v>
       </c>
       <c r="N47">
-        <v>24.9205</v>
+        <v>23.9854</v>
       </c>
       <c r="O47">
-        <v>6.230124999999999</v>
+        <v>5.99635</v>
       </c>
       <c r="P47">
-        <v>18.690375</v>
+        <v>17.98905</v>
       </c>
       <c r="Q47">
-        <v>47.090375</v>
+        <v>46.38905</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1514879497958452</v>
+        <v>0.1531419083216017</v>
       </c>
       <c r="T47">
-        <v>2.060054858398529</v>
+        <v>2.09229358857691</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.592224242208201</v>
+        <v>1.557610671725414</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1137466304936649</v>
+        <v>0.113799888599615</v>
       </c>
       <c r="C48">
-        <v>518.931396711183</v>
+        <v>507.9631761129482</v>
       </c>
       <c r="D48">
-        <v>738.2713967111829</v>
+        <v>737.6931761129482</v>
       </c>
       <c r="E48">
-        <v>400.04</v>
+        <v>410.4300000000001</v>
       </c>
       <c r="F48">
-        <v>477.94</v>
+        <v>488.33</v>
       </c>
       <c r="G48">
         <v>258.6</v>
@@ -5223,28 +5223,28 @@
         <v>67</v>
       </c>
       <c r="M48">
-        <v>43.0146</v>
+        <v>43.9497</v>
       </c>
       <c r="N48">
-        <v>23.9854</v>
+        <v>23.0503</v>
       </c>
       <c r="O48">
-        <v>5.99635</v>
+        <v>5.762575</v>
       </c>
       <c r="P48">
-        <v>17.98905</v>
+        <v>17.287725</v>
       </c>
       <c r="Q48">
-        <v>46.38905</v>
+        <v>45.68772500000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1531419083216017</v>
+        <v>0.1548582803766321</v>
       </c>
       <c r="T48">
-        <v>2.09229358857691</v>
+        <v>2.125748874611078</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.557610671725414</v>
+        <v>1.524470019135512</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.113799888599615</v>
+        <v>0.1364627695698917</v>
       </c>
       <c r="C49">
-        <v>507.9631761129482</v>
+        <v>313.1727577036578</v>
       </c>
       <c r="D49">
-        <v>737.6931761129482</v>
+        <v>553.2927577036578</v>
       </c>
       <c r="E49">
-        <v>410.4300000000001</v>
+        <v>420.8200000000001</v>
       </c>
       <c r="F49">
-        <v>488.33</v>
+        <v>498.72</v>
       </c>
       <c r="G49">
         <v>258.6</v>
@@ -5305,45 +5305,45 @@
         <v>67</v>
       </c>
       <c r="M49">
-        <v>43.9497</v>
+        <v>73.21209600000002</v>
       </c>
       <c r="N49">
-        <v>23.0503</v>
+        <v>-6.212096000000017</v>
       </c>
       <c r="O49">
-        <v>5.762575</v>
+        <v>-1.553024000000004</v>
       </c>
       <c r="P49">
-        <v>17.287725</v>
+        <v>-4.659072000000013</v>
       </c>
       <c r="Q49">
-        <v>45.68772500000001</v>
+        <v>23.74092799999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1548582803766321</v>
+        <v>0.1579231538889418</v>
       </c>
       <c r="T49">
-        <v>2.125748874611078</v>
+        <v>2.185488964012062</v>
       </c>
       <c r="U49">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.25</v>
+        <v>0.228787330443319</v>
       </c>
       <c r="W49">
-        <v>0.0675</v>
+        <v>0.1132140198909208</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.524470019135512</v>
+        <v>0.9151493217732761</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1364627695698917</v>
+        <v>0.1374727695698917</v>
       </c>
       <c r="C50">
-        <v>313.1727577036582</v>
+        <v>296.6868833463917</v>
       </c>
       <c r="D50">
-        <v>553.2927577036581</v>
+        <v>547.1968833463917</v>
       </c>
       <c r="E50">
-        <v>420.8199999999999</v>
+        <v>431.21</v>
       </c>
       <c r="F50">
-        <v>498.72</v>
+        <v>509.11</v>
       </c>
       <c r="G50">
         <v>258.6</v>
@@ -5387,37 +5387,37 @@
         <v>67</v>
       </c>
       <c r="M50">
-        <v>73.212096</v>
+        <v>74.73734800000001</v>
       </c>
       <c r="N50">
-        <v>-6.212096000000003</v>
+        <v>-7.737348000000011</v>
       </c>
       <c r="O50">
-        <v>-1.553024000000001</v>
+        <v>-1.934337000000003</v>
       </c>
       <c r="P50">
-        <v>-4.659072000000002</v>
+        <v>-5.803011000000009</v>
       </c>
       <c r="Q50">
-        <v>23.740928</v>
+        <v>22.596989</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1579231538889418</v>
+        <v>0.1601216471024504</v>
       </c>
       <c r="T50">
-        <v>2.185488964012062</v>
+        <v>2.228341688796613</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2287873304433191</v>
+        <v>0.2241182012505983</v>
       </c>
       <c r="W50">
-        <v>0.1132140198909208</v>
+        <v>0.1138994480564122</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9151493217732763</v>
+        <v>0.896472805002393</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1374727695698917</v>
+        <v>0.1384827695698917</v>
       </c>
       <c r="C51">
-        <v>296.6868833463917</v>
+        <v>280.3338671919911</v>
       </c>
       <c r="D51">
-        <v>547.1968833463917</v>
+        <v>541.2338671919911</v>
       </c>
       <c r="E51">
-        <v>431.21</v>
+        <v>441.6</v>
       </c>
       <c r="F51">
-        <v>509.11</v>
+        <v>519.5</v>
       </c>
       <c r="G51">
         <v>258.6</v>
@@ -5469,37 +5469,37 @@
         <v>67</v>
       </c>
       <c r="M51">
-        <v>74.73734800000001</v>
+        <v>76.26260000000001</v>
       </c>
       <c r="N51">
-        <v>-7.737348000000011</v>
+        <v>-9.262600000000006</v>
       </c>
       <c r="O51">
-        <v>-1.934337000000003</v>
+        <v>-2.315650000000002</v>
       </c>
       <c r="P51">
-        <v>-5.803011000000009</v>
+        <v>-6.946950000000005</v>
       </c>
       <c r="Q51">
-        <v>22.596989</v>
+        <v>21.45305</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1601216471024504</v>
+        <v>0.1624080800444994</v>
       </c>
       <c r="T51">
-        <v>2.228341688796613</v>
+        <v>2.272908522572544</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2241182012505983</v>
+        <v>0.2196358372255863</v>
       </c>
       <c r="W51">
-        <v>0.1138994480564122</v>
+        <v>0.1145574590952839</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.896472805002393</v>
+        <v>0.8785433489023452</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1384827695698917</v>
+        <v>0.1394927695698917</v>
       </c>
       <c r="C52">
-        <v>280.3338671919911</v>
+        <v>264.1094126404461</v>
       </c>
       <c r="D52">
-        <v>541.2338671919911</v>
+        <v>535.399412640446</v>
       </c>
       <c r="E52">
-        <v>441.6</v>
+        <v>451.99</v>
       </c>
       <c r="F52">
-        <v>519.5</v>
+        <v>529.89</v>
       </c>
       <c r="G52">
         <v>258.6</v>
@@ -5551,37 +5551,37 @@
         <v>67</v>
       </c>
       <c r="M52">
-        <v>76.26260000000001</v>
+        <v>77.787852</v>
       </c>
       <c r="N52">
-        <v>-9.262600000000006</v>
+        <v>-10.787852</v>
       </c>
       <c r="O52">
-        <v>-2.315650000000002</v>
+        <v>-2.696963</v>
       </c>
       <c r="P52">
-        <v>-6.946950000000005</v>
+        <v>-8.090889000000001</v>
       </c>
       <c r="Q52">
-        <v>21.45305</v>
+        <v>20.30911100000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1624080800444994</v>
+        <v>0.1647878367801015</v>
       </c>
       <c r="T52">
-        <v>2.272908522572544</v>
+        <v>2.319294410788311</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2196358372255863</v>
+        <v>0.2153292521819474</v>
       </c>
       <c r="W52">
-        <v>0.1145574590952839</v>
+        <v>0.1151896657796901</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8785433489023452</v>
+        <v>0.8613170087277895</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1394927695698917</v>
+        <v>0.1405027695698917</v>
       </c>
       <c r="C53">
-        <v>264.1094126404461</v>
+        <v>248.0094063837887</v>
       </c>
       <c r="D53">
-        <v>535.399412640446</v>
+        <v>529.6894063837887</v>
       </c>
       <c r="E53">
-        <v>451.99</v>
+        <v>462.38</v>
       </c>
       <c r="F53">
-        <v>529.89</v>
+        <v>540.28</v>
       </c>
       <c r="G53">
         <v>258.6</v>
@@ -5633,37 +5633,37 @@
         <v>67</v>
       </c>
       <c r="M53">
-        <v>77.787852</v>
+        <v>79.31310400000001</v>
       </c>
       <c r="N53">
-        <v>-10.787852</v>
+        <v>-12.31310400000001</v>
       </c>
       <c r="O53">
-        <v>-2.696963</v>
+        <v>-3.078276000000002</v>
       </c>
       <c r="P53">
-        <v>-8.090889000000001</v>
+        <v>-9.234828000000007</v>
       </c>
       <c r="Q53">
-        <v>20.30911100000001</v>
+        <v>19.165172</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1647878367801015</v>
+        <v>0.1672667500463536</v>
       </c>
       <c r="T53">
-        <v>2.319294410788311</v>
+        <v>2.367613044346401</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2153292521819474</v>
+        <v>0.2111883050246022</v>
       </c>
       <c r="W53">
-        <v>0.1151896657796901</v>
+        <v>0.1157975568223884</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8613170087277895</v>
+        <v>0.8447532200984089</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1405027695698917</v>
+        <v>0.1415127695698917</v>
       </c>
       <c r="C54">
-        <v>248.0094063837887</v>
+        <v>232.0299087352334</v>
       </c>
       <c r="D54">
-        <v>529.6894063837887</v>
+        <v>524.0999087352335</v>
       </c>
       <c r="E54">
-        <v>462.38</v>
+        <v>472.7700000000001</v>
       </c>
       <c r="F54">
-        <v>540.28</v>
+        <v>550.6700000000001</v>
       </c>
       <c r="G54">
         <v>258.6</v>
@@ -5715,37 +5715,37 @@
         <v>67</v>
       </c>
       <c r="M54">
-        <v>79.31310400000001</v>
+        <v>80.83835600000002</v>
       </c>
       <c r="N54">
-        <v>-12.31310400000001</v>
+        <v>-13.83835600000002</v>
       </c>
       <c r="O54">
-        <v>-3.078276000000002</v>
+        <v>-3.459589000000005</v>
       </c>
       <c r="P54">
-        <v>-9.234828000000007</v>
+        <v>-10.37876700000001</v>
       </c>
       <c r="Q54">
-        <v>19.165172</v>
+        <v>18.02123299999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1672667500463536</v>
+        <v>0.16985114898351</v>
       </c>
       <c r="T54">
-        <v>2.367613044346401</v>
+        <v>2.417987789970792</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2111883050246022</v>
+        <v>0.207203620024138</v>
       </c>
       <c r="W54">
-        <v>0.1157975568223884</v>
+        <v>0.1163825085804565</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8447532200984089</v>
+        <v>0.828814480096552</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1415127695698917</v>
+        <v>0.1425227695698917</v>
       </c>
       <c r="C55">
-        <v>232.0299087352334</v>
+        <v>216.1671445642271</v>
       </c>
       <c r="D55">
-        <v>524.0999087352335</v>
+        <v>518.6271445642271</v>
       </c>
       <c r="E55">
-        <v>472.7700000000001</v>
+        <v>483.1600000000001</v>
       </c>
       <c r="F55">
-        <v>550.6700000000001</v>
+        <v>561.0600000000001</v>
       </c>
       <c r="G55">
         <v>258.6</v>
@@ -5797,37 +5797,37 @@
         <v>67</v>
       </c>
       <c r="M55">
-        <v>80.83835600000002</v>
+        <v>82.36360800000001</v>
       </c>
       <c r="N55">
-        <v>-13.83835600000002</v>
+        <v>-15.36360800000001</v>
       </c>
       <c r="O55">
-        <v>-3.459589000000005</v>
+        <v>-3.840902000000003</v>
       </c>
       <c r="P55">
-        <v>-10.37876700000001</v>
+        <v>-11.52270600000001</v>
       </c>
       <c r="Q55">
-        <v>18.02123299999999</v>
+        <v>16.877294</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.16985114898351</v>
+        <v>0.1725479130918472</v>
       </c>
       <c r="T55">
-        <v>2.417987789970792</v>
+        <v>2.470552741926679</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.207203620024138</v>
+        <v>0.2033665159496169</v>
       </c>
       <c r="W55">
-        <v>0.1163825085804565</v>
+        <v>0.1169457954585962</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.828814480096552</v>
+        <v>0.8134660637984678</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1425227695698917</v>
+        <v>0.1751670661350131</v>
       </c>
       <c r="C56">
-        <v>216.1671445642271</v>
+        <v>74.90752821065234</v>
       </c>
       <c r="D56">
-        <v>518.6271445642271</v>
+        <v>387.7575282106523</v>
       </c>
       <c r="E56">
-        <v>483.1600000000001</v>
+        <v>493.5500000000001</v>
       </c>
       <c r="F56">
-        <v>561.0600000000001</v>
+        <v>571.45</v>
       </c>
       <c r="G56">
         <v>258.6</v>
@@ -5879,45 +5879,45 @@
         <v>67</v>
       </c>
       <c r="M56">
-        <v>82.36360800000001</v>
+        <v>114.74716</v>
       </c>
       <c r="N56">
-        <v>-15.36360800000001</v>
+        <v>-47.74716000000001</v>
       </c>
       <c r="O56">
-        <v>-3.840902000000003</v>
+        <v>-11.93679</v>
       </c>
       <c r="P56">
-        <v>-11.52270600000001</v>
+        <v>-35.81037000000001</v>
       </c>
       <c r="Q56">
-        <v>16.877294</v>
+        <v>-7.41037</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1725479130918472</v>
+        <v>0.1796629701941581</v>
       </c>
       <c r="T56">
-        <v>2.470552741926679</v>
+        <v>2.609238448099537</v>
       </c>
       <c r="U56">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.2033665159496169</v>
+        <v>0.1459731116656831</v>
       </c>
       <c r="W56">
-        <v>0.1169457954585962</v>
+        <v>0.1714885991775308</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8134660637984678</v>
+        <v>0.5838924466627322</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1751670661350131</v>
+        <v>0.1767170661350131</v>
       </c>
       <c r="C57">
-        <v>74.90752821065234</v>
+        <v>59.92665105101082</v>
       </c>
       <c r="D57">
-        <v>387.7575282106523</v>
+        <v>383.1666510510108</v>
       </c>
       <c r="E57">
-        <v>493.5500000000001</v>
+        <v>503.9400000000001</v>
       </c>
       <c r="F57">
-        <v>571.45</v>
+        <v>581.84</v>
       </c>
       <c r="G57">
         <v>258.6</v>
@@ -5961,37 +5961,37 @@
         <v>67</v>
       </c>
       <c r="M57">
-        <v>114.74716</v>
+        <v>116.833472</v>
       </c>
       <c r="N57">
-        <v>-47.74716000000001</v>
+        <v>-49.83347200000001</v>
       </c>
       <c r="O57">
-        <v>-11.93679</v>
+        <v>-12.458368</v>
       </c>
       <c r="P57">
-        <v>-35.81037000000001</v>
+        <v>-37.37510400000001</v>
       </c>
       <c r="Q57">
-        <v>-7.41037</v>
+        <v>-8.975104000000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1796629701941581</v>
+        <v>0.1827053104258435</v>
       </c>
       <c r="T57">
-        <v>2.609238448099537</v>
+        <v>2.668539321919981</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1459731116656831</v>
+        <v>0.1433664489573673</v>
       </c>
       <c r="W57">
-        <v>0.1714885991775308</v>
+        <v>0.1720120170493606</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5838924466627322</v>
+        <v>0.5734657958294691</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1767170661350131</v>
+        <v>0.1782670661350131</v>
       </c>
       <c r="C58">
-        <v>59.92665105101082</v>
+        <v>45.05320979683711</v>
       </c>
       <c r="D58">
-        <v>383.1666510510108</v>
+        <v>378.6832097968371</v>
       </c>
       <c r="E58">
-        <v>503.9400000000001</v>
+        <v>514.33</v>
       </c>
       <c r="F58">
-        <v>581.84</v>
+        <v>592.23</v>
       </c>
       <c r="G58">
         <v>258.6</v>
@@ -6043,37 +6043,37 @@
         <v>67</v>
       </c>
       <c r="M58">
-        <v>116.833472</v>
+        <v>118.919784</v>
       </c>
       <c r="N58">
-        <v>-49.83347200000001</v>
+        <v>-51.91978400000001</v>
       </c>
       <c r="O58">
-        <v>-12.458368</v>
+        <v>-12.979946</v>
       </c>
       <c r="P58">
-        <v>-37.37510400000001</v>
+        <v>-38.93983800000001</v>
       </c>
       <c r="Q58">
-        <v>-8.975104000000002</v>
+        <v>-10.539838</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1827053104258435</v>
+        <v>0.1858891548543515</v>
       </c>
       <c r="T58">
-        <v>2.668539321919981</v>
+        <v>2.730598375918121</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1433664489573673</v>
+        <v>0.1408512480984661</v>
       </c>
       <c r="W58">
-        <v>0.1720120170493606</v>
+        <v>0.172517069381828</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5734657958294691</v>
+        <v>0.5634049923938644</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1782670661350131</v>
+        <v>0.1798170661350131</v>
       </c>
       <c r="C59">
-        <v>45.05320979683711</v>
+        <v>30.28347673661779</v>
       </c>
       <c r="D59">
-        <v>378.6832097968371</v>
+        <v>374.3034767366179</v>
       </c>
       <c r="E59">
-        <v>514.33</v>
+        <v>524.7200000000001</v>
       </c>
       <c r="F59">
-        <v>592.23</v>
+        <v>602.6200000000001</v>
       </c>
       <c r="G59">
         <v>258.6</v>
@@ -6125,37 +6125,37 @@
         <v>67</v>
       </c>
       <c r="M59">
-        <v>118.919784</v>
+        <v>121.006096</v>
       </c>
       <c r="N59">
-        <v>-51.91978400000001</v>
+        <v>-54.00609600000003</v>
       </c>
       <c r="O59">
-        <v>-12.979946</v>
+        <v>-13.50152400000001</v>
       </c>
       <c r="P59">
-        <v>-38.93983800000001</v>
+        <v>-40.50457200000002</v>
       </c>
       <c r="Q59">
-        <v>-10.539838</v>
+        <v>-12.10457200000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1858891548543515</v>
+        <v>0.1892246109223122</v>
       </c>
       <c r="T59">
-        <v>2.730598375918121</v>
+        <v>2.79561262296379</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1408512480984661</v>
+        <v>0.1384227783036649</v>
       </c>
       <c r="W59">
-        <v>0.172517069381828</v>
+        <v>0.1730047061166241</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5634049923938644</v>
+        <v>0.5536911132146598</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1798170661350131</v>
+        <v>0.1813670661350131</v>
       </c>
       <c r="C60">
-        <v>30.28347673661801</v>
+        <v>15.61389464133276</v>
       </c>
       <c r="D60">
-        <v>374.303476736618</v>
+        <v>370.0238946413327</v>
       </c>
       <c r="E60">
-        <v>524.72</v>
+        <v>535.11</v>
       </c>
       <c r="F60">
-        <v>602.62</v>
+        <v>613.01</v>
       </c>
       <c r="G60">
         <v>258.6</v>
@@ -6207,37 +6207,37 @@
         <v>67</v>
       </c>
       <c r="M60">
-        <v>121.006096</v>
+        <v>123.092408</v>
       </c>
       <c r="N60">
-        <v>-54.006096</v>
+        <v>-56.09240800000001</v>
       </c>
       <c r="O60">
-        <v>-13.501524</v>
+        <v>-14.023102</v>
       </c>
       <c r="P60">
-        <v>-40.504572</v>
+        <v>-42.069306</v>
       </c>
       <c r="Q60">
-        <v>-12.10457199999999</v>
+        <v>-13.669306</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1892246109223122</v>
+        <v>0.1927227721643198</v>
       </c>
       <c r="T60">
-        <v>2.795612622963789</v>
+        <v>2.863798296694613</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.138422778303665</v>
+        <v>0.1360766295188571</v>
       </c>
       <c r="W60">
-        <v>0.1730047061166241</v>
+        <v>0.1734758127926135</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5536911132146598</v>
+        <v>0.5443065180754283</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1813670661350131</v>
+        <v>0.1829170661350131</v>
       </c>
       <c r="C61">
-        <v>15.61389464133276</v>
+        <v>1.041067128604823</v>
       </c>
       <c r="D61">
-        <v>370.0238946413327</v>
+        <v>365.8410671286048</v>
       </c>
       <c r="E61">
-        <v>535.11</v>
+        <v>545.5</v>
       </c>
       <c r="F61">
-        <v>613.01</v>
+        <v>623.4</v>
       </c>
       <c r="G61">
         <v>258.6</v>
@@ -6289,37 +6289,37 @@
         <v>67</v>
       </c>
       <c r="M61">
-        <v>123.092408</v>
+        <v>125.17872</v>
       </c>
       <c r="N61">
-        <v>-56.09240800000001</v>
+        <v>-58.17872</v>
       </c>
       <c r="O61">
-        <v>-14.023102</v>
+        <v>-14.54468</v>
       </c>
       <c r="P61">
-        <v>-42.069306</v>
+        <v>-43.63404</v>
       </c>
       <c r="Q61">
-        <v>-13.669306</v>
+        <v>-15.23403999999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1927227721643198</v>
+        <v>0.1963958414684278</v>
       </c>
       <c r="T61">
-        <v>2.863798296694613</v>
+        <v>2.935393254111978</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1360766295188571</v>
+        <v>0.1338086856935428</v>
       </c>
       <c r="W61">
-        <v>0.1734758127926135</v>
+        <v>0.1739312159127366</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5443065180754283</v>
+        <v>0.5352347427741713</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1829170661350131</v>
+        <v>0.1844670661350131</v>
       </c>
       <c r="C62">
-        <v>1.041067128604823</v>
+        <v>-13.43825032689847</v>
       </c>
       <c r="D62">
-        <v>365.8410671286048</v>
+        <v>361.7517496731015</v>
       </c>
       <c r="E62">
-        <v>545.5</v>
+        <v>555.89</v>
       </c>
       <c r="F62">
-        <v>623.4</v>
+        <v>633.79</v>
       </c>
       <c r="G62">
         <v>258.6</v>
@@ -6371,37 +6371,37 @@
         <v>67</v>
       </c>
       <c r="M62">
-        <v>125.17872</v>
+        <v>127.265032</v>
       </c>
       <c r="N62">
-        <v>-58.17872</v>
+        <v>-60.26503199999999</v>
       </c>
       <c r="O62">
-        <v>-14.54468</v>
+        <v>-15.066258</v>
       </c>
       <c r="P62">
-        <v>-43.63404</v>
+        <v>-45.19877399999999</v>
       </c>
       <c r="Q62">
-        <v>-15.23403999999999</v>
+        <v>-16.79877399999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1963958414684278</v>
+        <v>0.2002572733009516</v>
       </c>
       <c r="T62">
-        <v>2.935393254111978</v>
+        <v>3.010659747807158</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1338086856935428</v>
+        <v>0.1316151006821732</v>
       </c>
       <c r="W62">
-        <v>0.1739312159127366</v>
+        <v>0.1743716877830196</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5352347427741713</v>
+        <v>0.526460402728693</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1844670661350131</v>
+        <v>0.1860170661350131</v>
       </c>
       <c r="C63">
-        <v>-13.43825032689847</v>
+        <v>-27.82715878682427</v>
       </c>
       <c r="D63">
-        <v>361.7517496731015</v>
+        <v>357.7528412131756</v>
       </c>
       <c r="E63">
-        <v>555.89</v>
+        <v>566.28</v>
       </c>
       <c r="F63">
-        <v>633.79</v>
+        <v>644.1799999999999</v>
       </c>
       <c r="G63">
         <v>258.6</v>
@@ -6453,37 +6453,37 @@
         <v>67</v>
       </c>
       <c r="M63">
-        <v>127.265032</v>
+        <v>129.351344</v>
       </c>
       <c r="N63">
-        <v>-60.26503199999999</v>
+        <v>-62.35134399999998</v>
       </c>
       <c r="O63">
-        <v>-15.066258</v>
+        <v>-15.587836</v>
       </c>
       <c r="P63">
-        <v>-45.19877399999999</v>
+        <v>-46.76350799999999</v>
       </c>
       <c r="Q63">
-        <v>-16.79877399999999</v>
+        <v>-18.36350799999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2002572733009516</v>
+        <v>0.2043219383878187</v>
       </c>
       <c r="T63">
-        <v>3.010659747807158</v>
+        <v>3.089887635907346</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1316151006821732</v>
+        <v>0.1294922764776221</v>
       </c>
       <c r="W63">
-        <v>0.1743716877830196</v>
+        <v>0.1747979508832935</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.526460402728693</v>
+        <v>0.5179691059104883</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1860170661350131</v>
+        <v>0.1875670661350131</v>
       </c>
       <c r="C64">
-        <v>-27.82715878682427</v>
+        <v>-42.1286236918844</v>
       </c>
       <c r="D64">
-        <v>357.7528412131756</v>
+        <v>353.8413763081156</v>
       </c>
       <c r="E64">
-        <v>566.28</v>
+        <v>576.6700000000001</v>
       </c>
       <c r="F64">
-        <v>644.1799999999999</v>
+        <v>654.5700000000001</v>
       </c>
       <c r="G64">
         <v>258.6</v>
@@ -6535,37 +6535,37 @@
         <v>67</v>
       </c>
       <c r="M64">
-        <v>129.351344</v>
+        <v>131.437656</v>
       </c>
       <c r="N64">
-        <v>-62.35134399999998</v>
+        <v>-64.437656</v>
       </c>
       <c r="O64">
-        <v>-15.587836</v>
+        <v>-16.109414</v>
       </c>
       <c r="P64">
-        <v>-46.76350799999999</v>
+        <v>-48.328242</v>
       </c>
       <c r="Q64">
-        <v>-18.36350799999998</v>
+        <v>-19.928242</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2043219383878187</v>
+        <v>0.208606315101003</v>
       </c>
       <c r="T64">
-        <v>3.089887635907346</v>
+        <v>3.17339811255349</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1294922764776221</v>
+        <v>0.1274368435176598</v>
       </c>
       <c r="W64">
-        <v>0.1747979508832935</v>
+        <v>0.1752106818216539</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5179691059104883</v>
+        <v>0.5097473740706393</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1875670661350131</v>
+        <v>0.1891170661350131</v>
       </c>
       <c r="C65">
-        <v>-42.1286236918844</v>
+        <v>-56.34548219567841</v>
       </c>
       <c r="D65">
-        <v>353.8413763081156</v>
+        <v>350.0145178043215</v>
       </c>
       <c r="E65">
-        <v>576.6700000000001</v>
+        <v>587.0600000000001</v>
       </c>
       <c r="F65">
-        <v>654.5700000000001</v>
+        <v>664.96</v>
       </c>
       <c r="G65">
         <v>258.6</v>
@@ -6617,37 +6617,37 @@
         <v>67</v>
       </c>
       <c r="M65">
-        <v>131.437656</v>
+        <v>133.523968</v>
       </c>
       <c r="N65">
-        <v>-64.437656</v>
+        <v>-66.52396800000002</v>
       </c>
       <c r="O65">
-        <v>-16.109414</v>
+        <v>-16.63099200000001</v>
       </c>
       <c r="P65">
-        <v>-48.328242</v>
+        <v>-49.89297600000002</v>
       </c>
       <c r="Q65">
-        <v>-19.928242</v>
+        <v>-21.49297600000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.208606315101003</v>
+        <v>0.2131287127426976</v>
       </c>
       <c r="T65">
-        <v>3.17339811255349</v>
+        <v>3.261548060124422</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1274368435176598</v>
+        <v>0.1254456428376964</v>
       </c>
       <c r="W65">
-        <v>0.1752106818216539</v>
+        <v>0.1756105149181906</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5097473740706393</v>
+        <v>0.5017825713507854</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1891170661350131</v>
+        <v>0.2141975781627511</v>
       </c>
       <c r="C66">
-        <v>-56.34548219567841</v>
+        <v>-118.8653490230388</v>
       </c>
       <c r="D66">
-        <v>350.0145178043215</v>
+        <v>297.8846509769612</v>
       </c>
       <c r="E66">
-        <v>587.0600000000001</v>
+        <v>597.45</v>
       </c>
       <c r="F66">
-        <v>664.96</v>
+        <v>675.35</v>
       </c>
       <c r="G66">
         <v>258.6</v>
@@ -6699,45 +6699,45 @@
         <v>67</v>
       </c>
       <c r="M66">
-        <v>133.523968</v>
+        <v>159.24753</v>
       </c>
       <c r="N66">
-        <v>-66.52396800000002</v>
+        <v>-92.24753000000001</v>
       </c>
       <c r="O66">
-        <v>-16.63099200000001</v>
+        <v>-23.0618825</v>
       </c>
       <c r="P66">
-        <v>-49.89297600000002</v>
+        <v>-69.18564750000002</v>
       </c>
       <c r="Q66">
-        <v>-21.49297600000001</v>
+        <v>-40.78564750000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2131287127426976</v>
+        <v>0.2201395674717404</v>
       </c>
       <c r="T66">
-        <v>3.261548060124422</v>
+        <v>3.398202668090511</v>
       </c>
       <c r="U66">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1254456428376964</v>
+        <v>0.1051821651488095</v>
       </c>
       <c r="W66">
-        <v>0.1756105149181906</v>
+        <v>0.2109980454579107</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5017825713507854</v>
+        <v>0.4207286605952381</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2141975781627511</v>
+        <v>0.2160975781627511</v>
       </c>
       <c r="C67">
-        <v>-118.8653490230388</v>
+        <v>-132.5788304428115</v>
       </c>
       <c r="D67">
-        <v>297.8846509769612</v>
+        <v>294.5611695571884</v>
       </c>
       <c r="E67">
-        <v>597.45</v>
+        <v>607.84</v>
       </c>
       <c r="F67">
-        <v>675.35</v>
+        <v>685.74</v>
       </c>
       <c r="G67">
         <v>258.6</v>
@@ -6781,37 +6781,37 @@
         <v>67</v>
       </c>
       <c r="M67">
-        <v>159.24753</v>
+        <v>161.697492</v>
       </c>
       <c r="N67">
-        <v>-92.24753000000001</v>
+        <v>-94.69749200000001</v>
       </c>
       <c r="O67">
-        <v>-23.0618825</v>
+        <v>-23.674373</v>
       </c>
       <c r="P67">
-        <v>-69.18564750000002</v>
+        <v>-71.02311900000001</v>
       </c>
       <c r="Q67">
-        <v>-40.78564750000001</v>
+        <v>-42.623119</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2201395674717404</v>
+        <v>0.2252672018091445</v>
       </c>
       <c r="T67">
-        <v>3.398202668090511</v>
+        <v>3.49814980538729</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1051821651488095</v>
+        <v>0.1035884959798882</v>
       </c>
       <c r="W67">
-        <v>0.2109980454579107</v>
+        <v>0.2113738326479424</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4207286605952381</v>
+        <v>0.4143539839195527</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2160975781627511</v>
+        <v>0.2179975781627511</v>
       </c>
       <c r="C68">
-        <v>-132.5788304428115</v>
+        <v>-146.2189703584247</v>
       </c>
       <c r="D68">
-        <v>294.5611695571884</v>
+        <v>291.3110296415753</v>
       </c>
       <c r="E68">
-        <v>607.84</v>
+        <v>618.23</v>
       </c>
       <c r="F68">
-        <v>685.74</v>
+        <v>696.13</v>
       </c>
       <c r="G68">
         <v>258.6</v>
@@ -6863,37 +6863,37 @@
         <v>67</v>
       </c>
       <c r="M68">
-        <v>161.697492</v>
+        <v>164.147454</v>
       </c>
       <c r="N68">
-        <v>-94.69749200000001</v>
+        <v>-97.14745400000001</v>
       </c>
       <c r="O68">
-        <v>-23.674373</v>
+        <v>-24.2868635</v>
       </c>
       <c r="P68">
-        <v>-71.02311900000001</v>
+        <v>-72.8605905</v>
       </c>
       <c r="Q68">
-        <v>-42.623119</v>
+        <v>-44.4605905</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2252672018091445</v>
+        <v>0.230705601863967</v>
       </c>
       <c r="T68">
-        <v>3.49814980538729</v>
+        <v>3.604154344944481</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1035884959798882</v>
+        <v>0.1020423990249645</v>
       </c>
       <c r="W68">
-        <v>0.2113738326479424</v>
+        <v>0.2117384023099134</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4143539839195527</v>
+        <v>0.4081695960998578</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2179975781627511</v>
+        <v>0.2198975781627511</v>
       </c>
       <c r="C69">
-        <v>-146.2189703584247</v>
+        <v>-159.7881699898038</v>
       </c>
       <c r="D69">
-        <v>291.3110296415753</v>
+        <v>288.1318300101963</v>
       </c>
       <c r="E69">
-        <v>618.23</v>
+        <v>628.6200000000001</v>
       </c>
       <c r="F69">
-        <v>696.13</v>
+        <v>706.5200000000001</v>
       </c>
       <c r="G69">
         <v>258.6</v>
@@ -6945,37 +6945,37 @@
         <v>67</v>
       </c>
       <c r="M69">
-        <v>164.147454</v>
+        <v>166.597416</v>
       </c>
       <c r="N69">
-        <v>-97.14745400000001</v>
+        <v>-99.59741600000004</v>
       </c>
       <c r="O69">
-        <v>-24.2868635</v>
+        <v>-24.89935400000001</v>
       </c>
       <c r="P69">
-        <v>-72.8605905</v>
+        <v>-74.69806200000002</v>
       </c>
       <c r="Q69">
-        <v>-44.4605905</v>
+        <v>-46.29806200000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.230705601863967</v>
+        <v>0.236483901922216</v>
       </c>
       <c r="T69">
-        <v>3.604154344944481</v>
+        <v>3.716784168223997</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1020423990249645</v>
+        <v>0.1005417755098914</v>
       </c>
       <c r="W69">
-        <v>0.2117384023099134</v>
+        <v>0.2120922493347676</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4081695960998578</v>
+        <v>0.4021671020395657</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2198975781627511</v>
+        <v>0.2217975781627511</v>
       </c>
       <c r="C70">
-        <v>-159.7881699898038</v>
+        <v>-173.2887268664053</v>
       </c>
       <c r="D70">
-        <v>288.1318300101963</v>
+        <v>285.0212731335947</v>
       </c>
       <c r="E70">
-        <v>628.6200000000001</v>
+        <v>639.0100000000001</v>
       </c>
       <c r="F70">
-        <v>706.5200000000001</v>
+        <v>716.9100000000001</v>
       </c>
       <c r="G70">
         <v>258.6</v>
@@ -7027,37 +7027,37 @@
         <v>67</v>
       </c>
       <c r="M70">
-        <v>166.597416</v>
+        <v>169.047378</v>
       </c>
       <c r="N70">
-        <v>-99.59741600000004</v>
+        <v>-102.047378</v>
       </c>
       <c r="O70">
-        <v>-24.89935400000001</v>
+        <v>-25.51184450000001</v>
       </c>
       <c r="P70">
-        <v>-74.69806200000002</v>
+        <v>-76.53553350000003</v>
       </c>
       <c r="Q70">
-        <v>-46.29806200000002</v>
+        <v>-48.13553350000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.236483901922216</v>
+        <v>0.2426349955326101</v>
       </c>
       <c r="T70">
-        <v>3.716784168223997</v>
+        <v>3.836680431715094</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1005417755098914</v>
+        <v>0.09908464832858867</v>
       </c>
       <c r="W70">
-        <v>0.2120922493347676</v>
+        <v>0.2124358399241188</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4021671020395657</v>
+        <v>0.3963385933143546</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2217975781627511</v>
+        <v>0.2236975781627511</v>
       </c>
       <c r="C71">
-        <v>-173.2887268664053</v>
+        <v>-186.7228403644452</v>
       </c>
       <c r="D71">
-        <v>285.0212731335947</v>
+        <v>281.9771596355548</v>
       </c>
       <c r="E71">
-        <v>639.0100000000001</v>
+        <v>649.4000000000001</v>
       </c>
       <c r="F71">
-        <v>716.9100000000001</v>
+        <v>727.3000000000001</v>
       </c>
       <c r="G71">
         <v>258.6</v>
@@ -7109,37 +7109,37 @@
         <v>67</v>
       </c>
       <c r="M71">
-        <v>169.047378</v>
+        <v>171.49734</v>
       </c>
       <c r="N71">
-        <v>-102.047378</v>
+        <v>-104.49734</v>
       </c>
       <c r="O71">
-        <v>-25.51184450000001</v>
+        <v>-26.12433500000001</v>
       </c>
       <c r="P71">
-        <v>-76.53553350000003</v>
+        <v>-78.37300500000003</v>
       </c>
       <c r="Q71">
-        <v>-48.13553350000002</v>
+        <v>-49.97300500000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2426349955326101</v>
+        <v>0.2491961620503638</v>
       </c>
       <c r="T71">
-        <v>3.836680431715094</v>
+        <v>3.96456977943893</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09908464832858867</v>
+        <v>0.09766915335246597</v>
       </c>
       <c r="W71">
-        <v>0.2124358399241188</v>
+        <v>0.2127696136394885</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3963385933143546</v>
+        <v>0.3906766134098639</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2236975781627511</v>
+        <v>0.2255975781627511</v>
       </c>
       <c r="C72">
-        <v>-186.7228403644452</v>
+        <v>-200.09261689304</v>
       </c>
       <c r="D72">
-        <v>281.9771596355548</v>
+        <v>278.9973831069601</v>
       </c>
       <c r="E72">
-        <v>649.4000000000001</v>
+        <v>659.7900000000001</v>
       </c>
       <c r="F72">
-        <v>727.3000000000001</v>
+        <v>737.6900000000001</v>
       </c>
       <c r="G72">
         <v>258.6</v>
@@ -7191,37 +7191,37 @@
         <v>67</v>
       </c>
       <c r="M72">
-        <v>171.49734</v>
+        <v>173.947302</v>
       </c>
       <c r="N72">
-        <v>-104.49734</v>
+        <v>-106.947302</v>
       </c>
       <c r="O72">
-        <v>-26.12433500000001</v>
+        <v>-26.7368255</v>
       </c>
       <c r="P72">
-        <v>-78.37300500000003</v>
+        <v>-80.2104765</v>
       </c>
       <c r="Q72">
-        <v>-49.97300500000003</v>
+        <v>-51.81047649999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2491961620503638</v>
+        <v>0.2562098228107212</v>
       </c>
       <c r="T72">
-        <v>3.96456977943893</v>
+        <v>4.101279082178205</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09766915335246597</v>
+        <v>0.09629353147426224</v>
       </c>
       <c r="W72">
-        <v>0.2127696136394885</v>
+        <v>0.213093985278369</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3906766134098639</v>
+        <v>0.3851741258970489</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2255975781627511</v>
+        <v>0.2274975781627511</v>
       </c>
       <c r="C73">
-        <v>-200.0926168930399</v>
+        <v>-213.4000747549624</v>
       </c>
       <c r="D73">
-        <v>278.9973831069601</v>
+        <v>276.0799252450375</v>
       </c>
       <c r="E73">
-        <v>659.79</v>
+        <v>670.1799999999999</v>
       </c>
       <c r="F73">
-        <v>737.6899999999999</v>
+        <v>748.0799999999999</v>
       </c>
       <c r="G73">
         <v>258.6</v>
@@ -7273,37 +7273,37 @@
         <v>67</v>
       </c>
       <c r="M73">
-        <v>173.947302</v>
+        <v>176.397264</v>
       </c>
       <c r="N73">
-        <v>-106.947302</v>
+        <v>-109.397264</v>
       </c>
       <c r="O73">
-        <v>-26.73682549999999</v>
+        <v>-27.34931599999999</v>
       </c>
       <c r="P73">
-        <v>-80.21047649999998</v>
+        <v>-82.04794799999999</v>
       </c>
       <c r="Q73">
-        <v>-51.81047649999998</v>
+        <v>-53.64794799999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2562098228107211</v>
+        <v>0.2637244593396754</v>
       </c>
       <c r="T73">
-        <v>4.101279082178203</v>
+        <v>4.247753335113138</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09629353147426226</v>
+        <v>0.0949561213148975</v>
       </c>
       <c r="W73">
-        <v>0.213093985278369</v>
+        <v>0.2134093465939472</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.385174125897049</v>
+        <v>0.37982448525959</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2274975781627511</v>
+        <v>0.2293975781627511</v>
       </c>
       <c r="C74">
-        <v>-213.4000747549624</v>
+        <v>-226.6471487055819</v>
       </c>
       <c r="D74">
-        <v>276.0799252450375</v>
+        <v>273.2228512944181</v>
       </c>
       <c r="E74">
-        <v>670.1799999999999</v>
+        <v>680.5700000000001</v>
       </c>
       <c r="F74">
-        <v>748.0799999999999</v>
+        <v>758.47</v>
       </c>
       <c r="G74">
         <v>258.6</v>
@@ -7355,37 +7355,37 @@
         <v>67</v>
       </c>
       <c r="M74">
-        <v>176.397264</v>
+        <v>178.847226</v>
       </c>
       <c r="N74">
-        <v>-109.397264</v>
+        <v>-111.847226</v>
       </c>
       <c r="O74">
-        <v>-27.34931599999999</v>
+        <v>-27.9618065</v>
       </c>
       <c r="P74">
-        <v>-82.04794799999999</v>
+        <v>-83.88541950000001</v>
       </c>
       <c r="Q74">
-        <v>-53.64794799999999</v>
+        <v>-55.48541950000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2637244593396754</v>
+        <v>0.2717957356115153</v>
       </c>
       <c r="T74">
-        <v>4.247753335113138</v>
+        <v>4.405077532709921</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0949561213148975</v>
+        <v>0.09365535252976191</v>
       </c>
       <c r="W74">
-        <v>0.2134093465939472</v>
+        <v>0.2137160678734822</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.37982448525959</v>
+        <v>0.3746214101190476</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2293975781627511</v>
+        <v>0.2312975781627511</v>
       </c>
       <c r="C75">
-        <v>-226.6471487055819</v>
+        <v>-239.835694231626</v>
       </c>
       <c r="D75">
-        <v>273.2228512944181</v>
+        <v>270.424305768374</v>
       </c>
       <c r="E75">
-        <v>680.5700000000001</v>
+        <v>690.96</v>
       </c>
       <c r="F75">
-        <v>758.47</v>
+        <v>768.86</v>
       </c>
       <c r="G75">
         <v>258.6</v>
@@ -7437,37 +7437,37 @@
         <v>67</v>
       </c>
       <c r="M75">
-        <v>178.847226</v>
+        <v>181.297188</v>
       </c>
       <c r="N75">
-        <v>-111.847226</v>
+        <v>-114.297188</v>
       </c>
       <c r="O75">
-        <v>-27.9618065</v>
+        <v>-28.574297</v>
       </c>
       <c r="P75">
-        <v>-83.88541950000001</v>
+        <v>-85.722891</v>
       </c>
       <c r="Q75">
-        <v>-55.48541950000001</v>
+        <v>-57.322891</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2717957356115153</v>
+        <v>0.2804878792888812</v>
       </c>
       <c r="T75">
-        <v>4.405077532709921</v>
+        <v>4.574503591660302</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09365535252976191</v>
+        <v>0.0923897396577381</v>
       </c>
       <c r="W75">
-        <v>0.2137160678734822</v>
+        <v>0.2140144993887054</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3746214101190476</v>
+        <v>0.3695589586309523</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2312975781627511</v>
+        <v>0.2331975781627511</v>
       </c>
       <c r="C76">
-        <v>-239.835694231626</v>
+        <v>-252.967491569656</v>
       </c>
       <c r="D76">
-        <v>270.424305768374</v>
+        <v>267.6825084303439</v>
       </c>
       <c r="E76">
-        <v>690.96</v>
+        <v>701.35</v>
       </c>
       <c r="F76">
-        <v>768.86</v>
+        <v>779.25</v>
       </c>
       <c r="G76">
         <v>258.6</v>
@@ -7519,37 +7519,37 @@
         <v>67</v>
       </c>
       <c r="M76">
-        <v>181.297188</v>
+        <v>183.74715</v>
       </c>
       <c r="N76">
-        <v>-114.297188</v>
+        <v>-116.74715</v>
       </c>
       <c r="O76">
-        <v>-28.574297</v>
+        <v>-29.1867875</v>
       </c>
       <c r="P76">
-        <v>-85.722891</v>
+        <v>-87.5603625</v>
       </c>
       <c r="Q76">
-        <v>-57.322891</v>
+        <v>-59.16036249999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2804878792888812</v>
+        <v>0.2898753944604365</v>
       </c>
       <c r="T76">
-        <v>4.574503591660302</v>
+        <v>4.757483735326716</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0923897396577381</v>
+        <v>0.09115787646230158</v>
       </c>
       <c r="W76">
-        <v>0.2140144993887054</v>
+        <v>0.2143049727301893</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3695589586309523</v>
+        <v>0.3646315058492063</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2331975781627511</v>
+        <v>0.2350975781627511</v>
       </c>
       <c r="C77">
-        <v>-252.967491569656</v>
+        <v>-266.0442494825353</v>
       </c>
       <c r="D77">
-        <v>267.6825084303439</v>
+        <v>264.9957505174647</v>
       </c>
       <c r="E77">
-        <v>701.35</v>
+        <v>711.74</v>
       </c>
       <c r="F77">
-        <v>779.25</v>
+        <v>789.64</v>
       </c>
       <c r="G77">
         <v>258.6</v>
@@ -7601,37 +7601,37 @@
         <v>67</v>
       </c>
       <c r="M77">
-        <v>183.74715</v>
+        <v>186.197112</v>
       </c>
       <c r="N77">
-        <v>-116.74715</v>
+        <v>-119.197112</v>
       </c>
       <c r="O77">
-        <v>-29.1867875</v>
+        <v>-29.799278</v>
       </c>
       <c r="P77">
-        <v>-87.5603625</v>
+        <v>-89.397834</v>
       </c>
       <c r="Q77">
-        <v>-59.16036249999999</v>
+        <v>-60.997834</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2898753944604365</v>
+        <v>0.3000452025629547</v>
       </c>
       <c r="T77">
-        <v>4.757483735326716</v>
+        <v>4.955712224298662</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09115787646230158</v>
+        <v>0.08995843071937656</v>
       </c>
       <c r="W77">
-        <v>0.2143049727301893</v>
+        <v>0.214587802036371</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3646315058492063</v>
+        <v>0.3598337228775063</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2350975781627511</v>
+        <v>0.2369975781627511</v>
       </c>
       <c r="C78">
-        <v>-266.0442494825353</v>
+        <v>-279.0676088107302</v>
       </c>
       <c r="D78">
-        <v>264.9957505174647</v>
+        <v>262.3623911892697</v>
       </c>
       <c r="E78">
-        <v>711.74</v>
+        <v>722.13</v>
       </c>
       <c r="F78">
-        <v>789.64</v>
+        <v>800.03</v>
       </c>
       <c r="G78">
         <v>258.6</v>
@@ -7683,37 +7683,37 @@
         <v>67</v>
       </c>
       <c r="M78">
-        <v>186.197112</v>
+        <v>188.647074</v>
       </c>
       <c r="N78">
-        <v>-119.197112</v>
+        <v>-121.647074</v>
       </c>
       <c r="O78">
-        <v>-29.799278</v>
+        <v>-30.4117685</v>
       </c>
       <c r="P78">
-        <v>-89.397834</v>
+        <v>-91.23530550000001</v>
       </c>
       <c r="Q78">
-        <v>-60.997834</v>
+        <v>-62.8353055</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3000452025629547</v>
+        <v>0.3110993418048223</v>
       </c>
       <c r="T78">
-        <v>4.955712224298662</v>
+        <v>5.171177973181212</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08995843071937656</v>
+        <v>0.08879013941133272</v>
       </c>
       <c r="W78">
-        <v>0.214587802036371</v>
+        <v>0.2148632851268077</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3598337228775063</v>
+        <v>0.3551605576453308</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2369975781627511</v>
+        <v>0.2388975781627511</v>
       </c>
       <c r="C79">
-        <v>-279.0676088107302</v>
+        <v>-292.039145813952</v>
       </c>
       <c r="D79">
-        <v>262.3623911892697</v>
+        <v>259.7808541860481</v>
       </c>
       <c r="E79">
-        <v>722.13</v>
+        <v>732.5200000000001</v>
       </c>
       <c r="F79">
-        <v>800.03</v>
+        <v>810.4200000000001</v>
       </c>
       <c r="G79">
         <v>258.6</v>
@@ -7765,37 +7765,37 @@
         <v>67</v>
       </c>
       <c r="M79">
-        <v>188.647074</v>
+        <v>191.097036</v>
       </c>
       <c r="N79">
-        <v>-121.647074</v>
+        <v>-124.097036</v>
       </c>
       <c r="O79">
-        <v>-30.4117685</v>
+        <v>-31.02425900000001</v>
       </c>
       <c r="P79">
-        <v>-91.23530550000001</v>
+        <v>-93.07277700000003</v>
       </c>
       <c r="Q79">
-        <v>-62.8353055</v>
+        <v>-64.67277700000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3110993418048223</v>
+        <v>0.3231584027959506</v>
       </c>
       <c r="T79">
-        <v>5.171177973181212</v>
+        <v>5.406231517416722</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08879013941133272</v>
+        <v>0.0876518042906746</v>
       </c>
       <c r="W79">
-        <v>0.2148632851268077</v>
+        <v>0.2151317045482589</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3551605576453308</v>
+        <v>0.3506072171626984</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2388975781627511</v>
+        <v>0.2407975781627511</v>
       </c>
       <c r="C80">
-        <v>-292.039145813952</v>
+        <v>-304.960375317436</v>
       </c>
       <c r="D80">
-        <v>259.7808541860481</v>
+        <v>257.249624682564</v>
       </c>
       <c r="E80">
-        <v>732.5200000000001</v>
+        <v>742.9100000000001</v>
       </c>
       <c r="F80">
-        <v>810.4200000000001</v>
+        <v>820.8100000000001</v>
       </c>
       <c r="G80">
         <v>258.6</v>
@@ -7847,37 +7847,37 @@
         <v>67</v>
       </c>
       <c r="M80">
-        <v>191.097036</v>
+        <v>193.546998</v>
       </c>
       <c r="N80">
-        <v>-124.097036</v>
+        <v>-126.546998</v>
       </c>
       <c r="O80">
-        <v>-31.02425900000001</v>
+        <v>-31.63674950000001</v>
       </c>
       <c r="P80">
-        <v>-93.07277700000003</v>
+        <v>-94.91024850000002</v>
       </c>
       <c r="Q80">
-        <v>-64.67277700000002</v>
+        <v>-66.51024850000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3231584027959506</v>
+        <v>0.336365945786234</v>
       </c>
       <c r="T80">
-        <v>5.406231517416722</v>
+        <v>5.663671113484186</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0876518042906746</v>
+        <v>0.08654228778066606</v>
       </c>
       <c r="W80">
-        <v>0.2151317045482589</v>
+        <v>0.215393328541319</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3506072171626984</v>
+        <v>0.3461691511226642</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2407975781627511</v>
+        <v>0.2426975781627511</v>
       </c>
       <c r="C81">
-        <v>-304.960375317436</v>
+        <v>-317.832753676061</v>
       </c>
       <c r="D81">
-        <v>257.249624682564</v>
+        <v>254.7672463239391</v>
       </c>
       <c r="E81">
-        <v>742.9100000000001</v>
+        <v>753.3000000000001</v>
       </c>
       <c r="F81">
-        <v>820.8100000000001</v>
+        <v>831.2</v>
       </c>
       <c r="G81">
         <v>258.6</v>
@@ -7929,37 +7929,37 @@
         <v>67</v>
       </c>
       <c r="M81">
-        <v>193.546998</v>
+        <v>195.99696</v>
       </c>
       <c r="N81">
-        <v>-126.546998</v>
+        <v>-128.99696</v>
       </c>
       <c r="O81">
-        <v>-31.63674950000001</v>
+        <v>-32.24924000000001</v>
       </c>
       <c r="P81">
-        <v>-94.91024850000002</v>
+        <v>-96.74772000000002</v>
       </c>
       <c r="Q81">
-        <v>-66.51024850000002</v>
+        <v>-68.34772000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.336365945786234</v>
+        <v>0.3508942430755457</v>
       </c>
       <c r="T81">
-        <v>5.663671113484186</v>
+        <v>5.946854669158395</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08654228778066606</v>
+        <v>0.08546050918340772</v>
       </c>
       <c r="W81">
-        <v>0.215393328541319</v>
+        <v>0.2156484119345524</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3461691511226642</v>
+        <v>0.3418420367336309</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2426975781627511</v>
+        <v>0.2445975781627511</v>
       </c>
       <c r="C82">
-        <v>-317.832753676061</v>
+        <v>-330.6576815684882</v>
       </c>
       <c r="D82">
-        <v>254.7672463239391</v>
+        <v>252.3323184315119</v>
       </c>
       <c r="E82">
-        <v>753.3000000000001</v>
+        <v>763.6900000000001</v>
       </c>
       <c r="F82">
-        <v>831.2</v>
+        <v>841.59</v>
       </c>
       <c r="G82">
         <v>258.6</v>
@@ -8011,37 +8011,37 @@
         <v>67</v>
       </c>
       <c r="M82">
-        <v>195.99696</v>
+        <v>198.446922</v>
       </c>
       <c r="N82">
-        <v>-128.99696</v>
+        <v>-131.446922</v>
       </c>
       <c r="O82">
-        <v>-32.24924000000001</v>
+        <v>-32.86173050000001</v>
       </c>
       <c r="P82">
-        <v>-96.74772000000002</v>
+        <v>-98.58519150000002</v>
       </c>
       <c r="Q82">
-        <v>-68.34772000000001</v>
+        <v>-70.18519150000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3508942430755457</v>
+        <v>0.3669518348163639</v>
       </c>
       <c r="T82">
-        <v>5.946854669158395</v>
+        <v>6.259847020166732</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08546050918340772</v>
+        <v>0.08440544116879775</v>
       </c>
       <c r="W82">
-        <v>0.2156484119345524</v>
+        <v>0.2158971969723975</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3418420367336309</v>
+        <v>0.337621764675191</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2445975781627511</v>
+        <v>0.2464975781627511</v>
       </c>
       <c r="C83">
-        <v>-330.6576815684882</v>
+        <v>-343.4365066325909</v>
       </c>
       <c r="D83">
-        <v>252.3323184315119</v>
+        <v>249.9434933674092</v>
       </c>
       <c r="E83">
-        <v>763.6900000000001</v>
+        <v>774.08</v>
       </c>
       <c r="F83">
-        <v>841.59</v>
+        <v>851.98</v>
       </c>
       <c r="G83">
         <v>258.6</v>
@@ -8093,37 +8093,37 @@
         <v>67</v>
       </c>
       <c r="M83">
-        <v>198.446922</v>
+        <v>200.896884</v>
       </c>
       <c r="N83">
-        <v>-131.446922</v>
+        <v>-133.896884</v>
       </c>
       <c r="O83">
-        <v>-32.86173050000001</v>
+        <v>-33.474221</v>
       </c>
       <c r="P83">
-        <v>-98.58519150000002</v>
+        <v>-100.422663</v>
       </c>
       <c r="Q83">
-        <v>-70.18519150000002</v>
+        <v>-72.02266299999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3669518348163639</v>
+        <v>0.384793603417273</v>
       </c>
       <c r="T83">
-        <v>6.259847020166732</v>
+        <v>6.607616299064884</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08440544116879775</v>
+        <v>0.0833761065203978</v>
       </c>
       <c r="W83">
-        <v>0.2158971969723975</v>
+        <v>0.2161399140824902</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.337621764675191</v>
+        <v>0.3335044260815911</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2464975781627511</v>
+        <v>0.2483975781627511</v>
       </c>
       <c r="C84">
-        <v>-343.4365066325909</v>
+        <v>-356.1705259525879</v>
       </c>
       <c r="D84">
-        <v>249.9434933674092</v>
+        <v>247.5994740474122</v>
       </c>
       <c r="E84">
-        <v>774.08</v>
+        <v>784.4700000000001</v>
       </c>
       <c r="F84">
-        <v>851.98</v>
+        <v>862.3700000000001</v>
       </c>
       <c r="G84">
         <v>258.6</v>
@@ -8175,37 +8175,37 @@
         <v>67</v>
       </c>
       <c r="M84">
-        <v>200.896884</v>
+        <v>203.346846</v>
       </c>
       <c r="N84">
-        <v>-133.896884</v>
+        <v>-136.346846</v>
       </c>
       <c r="O84">
-        <v>-33.474221</v>
+        <v>-34.08671150000001</v>
       </c>
       <c r="P84">
-        <v>-100.422663</v>
+        <v>-102.2601345</v>
       </c>
       <c r="Q84">
-        <v>-72.02266299999999</v>
+        <v>-73.86013450000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.384793603417273</v>
+        <v>0.4047344036182892</v>
       </c>
       <c r="T84">
-        <v>6.607616299064884</v>
+        <v>6.996299610774584</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0833761065203978</v>
+        <v>0.08237157511653757</v>
       </c>
       <c r="W84">
-        <v>0.2161399140824902</v>
+        <v>0.2163767825875204</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3335044260815911</v>
+        <v>0.3294863004661502</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2483975781627511</v>
+        <v>0.2502975781627511</v>
       </c>
       <c r="C85">
-        <v>-356.1705259525879</v>
+        <v>-368.8609884075304</v>
       </c>
       <c r="D85">
-        <v>247.5994740474122</v>
+        <v>245.2990115924697</v>
       </c>
       <c r="E85">
-        <v>784.4700000000001</v>
+        <v>794.8600000000001</v>
       </c>
       <c r="F85">
-        <v>862.3700000000001</v>
+        <v>872.7600000000001</v>
       </c>
       <c r="G85">
         <v>258.6</v>
@@ -8257,37 +8257,37 @@
         <v>67</v>
       </c>
       <c r="M85">
-        <v>203.346846</v>
+        <v>205.796808</v>
       </c>
       <c r="N85">
-        <v>-136.346846</v>
+        <v>-138.796808</v>
       </c>
       <c r="O85">
-        <v>-34.08671150000001</v>
+        <v>-34.69920200000001</v>
       </c>
       <c r="P85">
-        <v>-102.2601345</v>
+        <v>-104.097606</v>
       </c>
       <c r="Q85">
-        <v>-73.86013450000002</v>
+        <v>-75.69760600000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4047344036182892</v>
+        <v>0.4271678038444323</v>
       </c>
       <c r="T85">
-        <v>6.996299610774584</v>
+        <v>7.433568336447997</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08237157511653757</v>
+        <v>0.08139096112705498</v>
       </c>
       <c r="W85">
-        <v>0.2163767825875204</v>
+        <v>0.2166080113662404</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3294863004661502</v>
+        <v>0.32556384450822</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2502975781627511</v>
+        <v>0.2521975781627511</v>
       </c>
       <c r="C86">
-        <v>-368.8609884075303</v>
+        <v>-381.5090968900736</v>
       </c>
       <c r="D86">
-        <v>245.2990115924697</v>
+        <v>243.0409031099264</v>
       </c>
       <c r="E86">
-        <v>794.86</v>
+        <v>805.25</v>
       </c>
       <c r="F86">
-        <v>872.76</v>
+        <v>883.15</v>
       </c>
       <c r="G86">
         <v>258.6</v>
@@ -8339,37 +8339,37 @@
         <v>67</v>
       </c>
       <c r="M86">
-        <v>205.796808</v>
+        <v>208.24677</v>
       </c>
       <c r="N86">
-        <v>-138.796808</v>
+        <v>-141.24677</v>
       </c>
       <c r="O86">
-        <v>-34.699202</v>
+        <v>-35.3116925</v>
       </c>
       <c r="P86">
-        <v>-104.097606</v>
+        <v>-105.9350775</v>
       </c>
       <c r="Q86">
-        <v>-75.69760599999999</v>
+        <v>-77.5350775</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.427167803844432</v>
+        <v>0.4525923241007275</v>
       </c>
       <c r="T86">
-        <v>7.433568336447991</v>
+        <v>7.929139558877858</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08139096112705499</v>
+        <v>0.08043342040791317</v>
       </c>
       <c r="W86">
-        <v>0.2166080113662404</v>
+        <v>0.2168337994678141</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.32556384450822</v>
+        <v>0.3217336816316527</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2521975781627511</v>
+        <v>0.2540975781627511</v>
       </c>
       <c r="C87">
-        <v>-381.5090968900736</v>
+        <v>-394.1160104038161</v>
       </c>
       <c r="D87">
-        <v>243.0409031099264</v>
+        <v>240.8239895961839</v>
       </c>
       <c r="E87">
-        <v>805.25</v>
+        <v>815.64</v>
       </c>
       <c r="F87">
-        <v>883.15</v>
+        <v>893.54</v>
       </c>
       <c r="G87">
         <v>258.6</v>
@@ -8421,37 +8421,37 @@
         <v>67</v>
       </c>
       <c r="M87">
-        <v>208.24677</v>
+        <v>210.696732</v>
       </c>
       <c r="N87">
-        <v>-141.24677</v>
+        <v>-143.696732</v>
       </c>
       <c r="O87">
-        <v>-35.3116925</v>
+        <v>-35.924183</v>
       </c>
       <c r="P87">
-        <v>-105.9350775</v>
+        <v>-107.772549</v>
       </c>
       <c r="Q87">
-        <v>-77.5350775</v>
+        <v>-79.37254899999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4525923241007275</v>
+        <v>0.4816489186793509</v>
       </c>
       <c r="T87">
-        <v>7.929139558877858</v>
+        <v>8.495506670226277</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08043342040791317</v>
+        <v>0.07949814807758859</v>
       </c>
       <c r="W87">
-        <v>0.2168337994678141</v>
+        <v>0.2170543366833046</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3217336816316527</v>
+        <v>0.3179925923103544</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2540975781627511</v>
+        <v>0.2559975781627511</v>
       </c>
       <c r="C88">
-        <v>-394.1160104038161</v>
+        <v>-406.6828460468912</v>
       </c>
       <c r="D88">
-        <v>240.8239895961839</v>
+        <v>238.6471539531087</v>
       </c>
       <c r="E88">
-        <v>815.64</v>
+        <v>826.03</v>
       </c>
       <c r="F88">
-        <v>893.54</v>
+        <v>903.9299999999999</v>
       </c>
       <c r="G88">
         <v>258.6</v>
@@ -8503,37 +8503,37 @@
         <v>67</v>
       </c>
       <c r="M88">
-        <v>210.696732</v>
+        <v>213.146694</v>
       </c>
       <c r="N88">
-        <v>-143.696732</v>
+        <v>-146.146694</v>
       </c>
       <c r="O88">
-        <v>-35.924183</v>
+        <v>-36.5366735</v>
       </c>
       <c r="P88">
-        <v>-107.772549</v>
+        <v>-109.6100205</v>
       </c>
       <c r="Q88">
-        <v>-79.37254899999999</v>
+        <v>-81.21002049999998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4816489186793509</v>
+        <v>0.5151757585777624</v>
       </c>
       <c r="T88">
-        <v>8.495506670226277</v>
+        <v>9.149007183320604</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07949814807758859</v>
+        <v>0.07858437626060483</v>
       </c>
       <c r="W88">
-        <v>0.2170543366833046</v>
+        <v>0.2172698040777494</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3179925923103544</v>
+        <v>0.3143375050424193</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2559975781627511</v>
+        <v>0.2578975781627511</v>
       </c>
       <c r="C89">
-        <v>-406.6828460468912</v>
+        <v>-419.210680888942</v>
       </c>
       <c r="D89">
-        <v>238.6471539531087</v>
+        <v>236.509319111058</v>
       </c>
       <c r="E89">
-        <v>826.03</v>
+        <v>836.4200000000001</v>
       </c>
       <c r="F89">
-        <v>903.9299999999999</v>
+        <v>914.3200000000001</v>
       </c>
       <c r="G89">
         <v>258.6</v>
@@ -8585,37 +8585,37 @@
         <v>67</v>
       </c>
       <c r="M89">
-        <v>213.146694</v>
+        <v>215.596656</v>
       </c>
       <c r="N89">
-        <v>-146.146694</v>
+        <v>-148.596656</v>
       </c>
       <c r="O89">
-        <v>-36.5366735</v>
+        <v>-37.14916400000001</v>
       </c>
       <c r="P89">
-        <v>-109.6100205</v>
+        <v>-111.447492</v>
       </c>
       <c r="Q89">
-        <v>-81.21002049999998</v>
+        <v>-83.04749200000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5151757585777624</v>
+        <v>0.5542904051259093</v>
       </c>
       <c r="T89">
-        <v>9.149007183320604</v>
+        <v>9.911424448597323</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07858437626060483</v>
+        <v>0.07769137198491612</v>
       </c>
       <c r="W89">
-        <v>0.2172698040777494</v>
+        <v>0.2174803744859568</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3143375050424193</v>
+        <v>0.3107654879396645</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2578975781627511</v>
+        <v>0.2597975781627511</v>
       </c>
       <c r="C90">
-        <v>-419.210680888942</v>
+        <v>-431.700553748107</v>
       </c>
       <c r="D90">
-        <v>236.509319111058</v>
+        <v>234.409446251893</v>
       </c>
       <c r="E90">
-        <v>836.4200000000001</v>
+        <v>846.8100000000001</v>
       </c>
       <c r="F90">
-        <v>914.3200000000001</v>
+        <v>924.71</v>
       </c>
       <c r="G90">
         <v>258.6</v>
@@ -8667,37 +8667,37 @@
         <v>67</v>
       </c>
       <c r="M90">
-        <v>215.596656</v>
+        <v>218.046618</v>
       </c>
       <c r="N90">
-        <v>-148.596656</v>
+        <v>-151.046618</v>
       </c>
       <c r="O90">
-        <v>-37.14916400000001</v>
+        <v>-37.76165450000001</v>
       </c>
       <c r="P90">
-        <v>-111.447492</v>
+        <v>-113.2849635</v>
       </c>
       <c r="Q90">
-        <v>-83.04749200000001</v>
+        <v>-84.88496350000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5542904051259093</v>
+        <v>0.6005168055919011</v>
       </c>
       <c r="T90">
-        <v>9.911424448597323</v>
+        <v>10.81246303483344</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07769137198491612</v>
+        <v>0.07681843522104066</v>
       </c>
       <c r="W90">
-        <v>0.2174803744859568</v>
+        <v>0.2176862129748786</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3107654879396645</v>
+        <v>0.3072737408841626</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2597975781627511</v>
+        <v>0.2616975781627511</v>
       </c>
       <c r="C91">
-        <v>-431.700553748107</v>
+        <v>-444.1534668741767</v>
       </c>
       <c r="D91">
-        <v>234.409446251893</v>
+        <v>232.3465331258232</v>
       </c>
       <c r="E91">
-        <v>846.8100000000001</v>
+        <v>857.2</v>
       </c>
       <c r="F91">
-        <v>924.71</v>
+        <v>935.1</v>
       </c>
       <c r="G91">
         <v>258.6</v>
@@ -8749,37 +8749,37 @@
         <v>67</v>
       </c>
       <c r="M91">
-        <v>218.046618</v>
+        <v>220.49658</v>
       </c>
       <c r="N91">
-        <v>-151.046618</v>
+        <v>-153.49658</v>
       </c>
       <c r="O91">
-        <v>-37.76165450000001</v>
+        <v>-38.37414500000001</v>
       </c>
       <c r="P91">
-        <v>-113.2849635</v>
+        <v>-115.122435</v>
       </c>
       <c r="Q91">
-        <v>-84.88496350000001</v>
+        <v>-86.72243500000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6005168055919011</v>
+        <v>0.6559884861510914</v>
       </c>
       <c r="T91">
-        <v>10.81246303483344</v>
+        <v>11.89370933831679</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07681843522104066</v>
+        <v>0.07596489705191799</v>
       </c>
       <c r="W91">
-        <v>0.2176862129748786</v>
+        <v>0.2178874772751578</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3072737408841626</v>
+        <v>0.3038595882076719</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2616975781627511</v>
+        <v>0.2635975781627511</v>
       </c>
       <c r="C92">
-        <v>-444.1534668741767</v>
+        <v>-456.570387543649</v>
       </c>
       <c r="D92">
-        <v>232.3465331258232</v>
+        <v>230.319612456351</v>
       </c>
       <c r="E92">
-        <v>857.2</v>
+        <v>867.59</v>
       </c>
       <c r="F92">
-        <v>935.1</v>
+        <v>945.49</v>
       </c>
       <c r="G92">
         <v>258.6</v>
@@ -8831,37 +8831,37 @@
         <v>67</v>
       </c>
       <c r="M92">
-        <v>220.49658</v>
+        <v>222.946542</v>
       </c>
       <c r="N92">
-        <v>-153.49658</v>
+        <v>-155.946542</v>
       </c>
       <c r="O92">
-        <v>-38.37414500000001</v>
+        <v>-38.98663550000001</v>
       </c>
       <c r="P92">
-        <v>-115.122435</v>
+        <v>-116.9599065</v>
       </c>
       <c r="Q92">
-        <v>-86.72243500000002</v>
+        <v>-88.55990650000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6559884861510914</v>
+        <v>0.723787206834546</v>
       </c>
       <c r="T92">
-        <v>11.89370933831679</v>
+        <v>13.21523259812977</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07596489705191799</v>
+        <v>0.07513011796343537</v>
       </c>
       <c r="W92">
-        <v>0.2178874772751578</v>
+        <v>0.2180843181842219</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3038595882076719</v>
+        <v>0.3005204718537415</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2635975781627511</v>
+        <v>0.2654975781627511</v>
       </c>
       <c r="C93">
-        <v>-456.570387543649</v>
+        <v>-468.9522495720182</v>
       </c>
       <c r="D93">
-        <v>230.319612456351</v>
+        <v>228.3277504279818</v>
       </c>
       <c r="E93">
-        <v>867.59</v>
+        <v>877.98</v>
       </c>
       <c r="F93">
-        <v>945.49</v>
+        <v>955.88</v>
       </c>
       <c r="G93">
         <v>258.6</v>
@@ -8913,37 +8913,37 @@
         <v>67</v>
       </c>
       <c r="M93">
-        <v>222.946542</v>
+        <v>225.396504</v>
       </c>
       <c r="N93">
-        <v>-155.946542</v>
+        <v>-158.396504</v>
       </c>
       <c r="O93">
-        <v>-38.98663550000001</v>
+        <v>-39.59912600000001</v>
       </c>
       <c r="P93">
-        <v>-116.9599065</v>
+        <v>-118.797378</v>
       </c>
       <c r="Q93">
-        <v>-88.55990650000001</v>
+        <v>-90.397378</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.723787206834546</v>
+        <v>0.8085356076888645</v>
       </c>
       <c r="T93">
-        <v>13.21523259812977</v>
+        <v>14.86713667289599</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07513011796343537</v>
+        <v>0.0743134862464415</v>
       </c>
       <c r="W93">
-        <v>0.2180843181842219</v>
+        <v>0.2182768799430891</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3005204718537415</v>
+        <v>0.2972539449857661</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2654975781627511</v>
+        <v>0.2673975781627511</v>
       </c>
       <c r="C94">
-        <v>-468.9522495720182</v>
+        <v>-481.299954748266</v>
       </c>
       <c r="D94">
-        <v>228.3277504279818</v>
+        <v>226.3700452517341</v>
       </c>
       <c r="E94">
-        <v>877.98</v>
+        <v>888.3700000000001</v>
       </c>
       <c r="F94">
-        <v>955.88</v>
+        <v>966.2700000000001</v>
       </c>
       <c r="G94">
         <v>258.6</v>
@@ -8995,37 +8995,37 @@
         <v>67</v>
       </c>
       <c r="M94">
-        <v>225.396504</v>
+        <v>227.846466</v>
       </c>
       <c r="N94">
-        <v>-158.396504</v>
+        <v>-160.846466</v>
       </c>
       <c r="O94">
-        <v>-39.59912600000001</v>
+        <v>-40.21161650000001</v>
       </c>
       <c r="P94">
-        <v>-118.797378</v>
+        <v>-120.6348495</v>
       </c>
       <c r="Q94">
-        <v>-90.397378</v>
+        <v>-92.23484950000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8085356076888645</v>
+        <v>0.9174978373587025</v>
       </c>
       <c r="T94">
-        <v>14.86713667289599</v>
+        <v>16.99101334045257</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0743134862464415</v>
+        <v>0.07351441650185611</v>
       </c>
       <c r="W94">
-        <v>0.2182768799430891</v>
+        <v>0.2184653005888623</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2972539449857661</v>
+        <v>0.2940576660074244</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2673975781627511</v>
+        <v>0.2692975781627511</v>
       </c>
       <c r="C95">
-        <v>-481.299954748266</v>
+        <v>-493.6143741961808</v>
       </c>
       <c r="D95">
-        <v>226.3700452517341</v>
+        <v>224.4456258038192</v>
       </c>
       <c r="E95">
-        <v>888.3700000000001</v>
+        <v>898.7600000000001</v>
       </c>
       <c r="F95">
-        <v>966.2700000000001</v>
+        <v>976.6600000000001</v>
       </c>
       <c r="G95">
         <v>258.6</v>
@@ -9077,37 +9077,37 @@
         <v>67</v>
       </c>
       <c r="M95">
-        <v>227.846466</v>
+        <v>230.296428</v>
       </c>
       <c r="N95">
-        <v>-160.846466</v>
+        <v>-163.296428</v>
       </c>
       <c r="O95">
-        <v>-40.21161650000001</v>
+        <v>-40.82410700000001</v>
       </c>
       <c r="P95">
-        <v>-120.6348495</v>
+        <v>-122.472321</v>
       </c>
       <c r="Q95">
-        <v>-92.23484950000001</v>
+        <v>-94.07232100000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9174978373587025</v>
+        <v>1.06278081025182</v>
       </c>
       <c r="T95">
-        <v>16.99101334045257</v>
+        <v>19.82284889719466</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07351441650185611</v>
+        <v>0.07273234824119808</v>
       </c>
       <c r="W95">
-        <v>0.2184653005888623</v>
+        <v>0.2186497122847255</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2940576660074244</v>
+        <v>0.2909293929647923</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2692975781627511</v>
+        <v>0.2711975781627511</v>
       </c>
       <c r="C96">
-        <v>-493.6143741961808</v>
+        <v>-505.8963496668283</v>
       </c>
       <c r="D96">
-        <v>224.4456258038192</v>
+        <v>222.5536503331717</v>
       </c>
       <c r="E96">
-        <v>898.7600000000001</v>
+        <v>909.1500000000001</v>
       </c>
       <c r="F96">
-        <v>976.6600000000001</v>
+        <v>987.0500000000001</v>
       </c>
       <c r="G96">
         <v>258.6</v>
@@ -9159,37 +9159,37 @@
         <v>67</v>
       </c>
       <c r="M96">
-        <v>230.296428</v>
+        <v>232.74639</v>
       </c>
       <c r="N96">
-        <v>-163.296428</v>
+        <v>-165.74639</v>
       </c>
       <c r="O96">
-        <v>-40.82410700000001</v>
+        <v>-41.4365975</v>
       </c>
       <c r="P96">
-        <v>-122.472321</v>
+        <v>-124.3097925</v>
       </c>
       <c r="Q96">
-        <v>-94.07232100000002</v>
+        <v>-95.90979250000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.06278081025182</v>
+        <v>1.266176972302184</v>
       </c>
       <c r="T96">
-        <v>19.82284889719466</v>
+        <v>23.78741867663361</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07273234824119808</v>
+        <v>0.07196674457550126</v>
       </c>
       <c r="W96">
-        <v>0.2186497122847255</v>
+        <v>0.2188302416290968</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2909293929647923</v>
+        <v>0.287866978302005</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2711975781627511</v>
+        <v>0.2730975781627511</v>
       </c>
       <c r="C97">
-        <v>-505.8963496668283</v>
+        <v>-518.1466947661951</v>
       </c>
       <c r="D97">
-        <v>222.5536503331717</v>
+        <v>220.6933052338049</v>
       </c>
       <c r="E97">
-        <v>909.1500000000001</v>
+        <v>919.5400000000001</v>
       </c>
       <c r="F97">
-        <v>987.0500000000001</v>
+        <v>997.4400000000001</v>
       </c>
       <c r="G97">
         <v>258.6</v>
@@ -9241,37 +9241,37 @@
         <v>67</v>
       </c>
       <c r="M97">
-        <v>232.74639</v>
+        <v>235.196352</v>
       </c>
       <c r="N97">
-        <v>-165.74639</v>
+        <v>-168.196352</v>
       </c>
       <c r="O97">
-        <v>-41.4365975</v>
+        <v>-42.049088</v>
       </c>
       <c r="P97">
-        <v>-124.3097925</v>
+        <v>-126.147264</v>
       </c>
       <c r="Q97">
-        <v>-95.90979250000001</v>
+        <v>-97.747264</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.266176972302184</v>
+        <v>1.571271215377731</v>
       </c>
       <c r="T97">
-        <v>23.78741867663361</v>
+        <v>29.73427334579202</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07196674457550126</v>
+        <v>0.07121709098617311</v>
       </c>
       <c r="W97">
-        <v>0.2188302416290968</v>
+        <v>0.2190070099454604</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.287866978302005</v>
+        <v>0.2848683639446925</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.273097578162751</v>
+        <v>0.2749975781627511</v>
       </c>
       <c r="C98">
-        <v>-518.146694766195</v>
+        <v>-530.3661961217742</v>
       </c>
       <c r="D98">
-        <v>220.693305233805</v>
+        <v>218.8638038782257</v>
       </c>
       <c r="E98">
-        <v>919.54</v>
+        <v>929.9299999999999</v>
       </c>
       <c r="F98">
-        <v>997.4399999999999</v>
+        <v>1007.83</v>
       </c>
       <c r="G98">
         <v>258.6</v>
@@ -9323,37 +9323,37 @@
         <v>67</v>
       </c>
       <c r="M98">
-        <v>235.196352</v>
+        <v>237.646314</v>
       </c>
       <c r="N98">
-        <v>-168.196352</v>
+        <v>-170.646314</v>
       </c>
       <c r="O98">
-        <v>-42.049088</v>
+        <v>-42.6615785</v>
       </c>
       <c r="P98">
-        <v>-126.147264</v>
+        <v>-127.9847355</v>
       </c>
       <c r="Q98">
-        <v>-97.74726399999999</v>
+        <v>-99.58473549999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.571271215377727</v>
+        <v>2.079761620503636</v>
       </c>
       <c r="T98">
-        <v>29.73427334579194</v>
+        <v>39.64569779438926</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07121709098617313</v>
+        <v>0.07048289417188268</v>
       </c>
       <c r="W98">
-        <v>0.2190070099454604</v>
+        <v>0.2191801335542701</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2848683639446925</v>
+        <v>0.2819315766875307</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2749975781627511</v>
+        <v>0.2768975781627511</v>
       </c>
       <c r="C99">
-        <v>-530.3661961217742</v>
+        <v>-542.5556144916015</v>
       </c>
       <c r="D99">
-        <v>218.8638038782257</v>
+        <v>217.0643855083985</v>
       </c>
       <c r="E99">
-        <v>929.9299999999999</v>
+        <v>940.3200000000001</v>
       </c>
       <c r="F99">
-        <v>1007.83</v>
+        <v>1018.22</v>
       </c>
       <c r="G99">
         <v>258.6</v>
@@ -9405,37 +9405,37 @@
         <v>67</v>
       </c>
       <c r="M99">
-        <v>237.646314</v>
+        <v>240.096276</v>
       </c>
       <c r="N99">
-        <v>-170.646314</v>
+        <v>-173.096276</v>
       </c>
       <c r="O99">
-        <v>-42.6615785</v>
+        <v>-43.274069</v>
       </c>
       <c r="P99">
-        <v>-127.9847355</v>
+        <v>-129.822207</v>
       </c>
       <c r="Q99">
-        <v>-99.58473549999999</v>
+        <v>-101.422207</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.079761620503636</v>
+        <v>3.096742430755454</v>
       </c>
       <c r="T99">
-        <v>39.64569779438926</v>
+        <v>59.4685466915839</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07048289417188268</v>
+        <v>0.06976368096604713</v>
       </c>
       <c r="W99">
-        <v>0.2191801335542701</v>
+        <v>0.2193497240282061</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2819315766875307</v>
+        <v>0.2790547238641885</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2768975781627511</v>
+        <v>0.2787975781627511</v>
       </c>
       <c r="C100">
-        <v>-542.5556144916015</v>
+        <v>-554.715685819029</v>
       </c>
       <c r="D100">
-        <v>217.0643855083985</v>
+        <v>215.294314180971</v>
       </c>
       <c r="E100">
-        <v>940.3200000000001</v>
+        <v>950.7099999999999</v>
       </c>
       <c r="F100">
-        <v>1018.22</v>
+        <v>1028.61</v>
       </c>
       <c r="G100">
         <v>258.6</v>
@@ -9487,37 +9487,37 @@
         <v>67</v>
       </c>
       <c r="M100">
-        <v>240.096276</v>
+        <v>242.546238</v>
       </c>
       <c r="N100">
-        <v>-173.096276</v>
+        <v>-175.546238</v>
       </c>
       <c r="O100">
-        <v>-43.274069</v>
+        <v>-43.8865595</v>
       </c>
       <c r="P100">
-        <v>-129.822207</v>
+        <v>-131.6596785</v>
       </c>
       <c r="Q100">
-        <v>-101.422207</v>
+        <v>-103.2596785</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.096742430755454</v>
+        <v>6.147684861510906</v>
       </c>
       <c r="T100">
-        <v>59.4685466915839</v>
+        <v>118.9370933831678</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06976368096604713</v>
+        <v>0.06905899731992546</v>
       </c>
       <c r="W100">
-        <v>0.2193497240282061</v>
+        <v>0.2195158884319616</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2790547238641885</v>
+        <v>0.2762359892797018</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2787975781627511</v>
-      </c>
-      <c r="C101">
-        <v>-554.715685819029</v>
-      </c>
-      <c r="D101">
-        <v>215.294314180971</v>
-      </c>
-      <c r="E101">
-        <v>950.7099999999999</v>
-      </c>
-      <c r="F101">
-        <v>1028.61</v>
-      </c>
-      <c r="G101">
-        <v>258.6</v>
-      </c>
-      <c r="H101">
-        <v>961.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="K101">
-        <v>28.40000000000001</v>
-      </c>
-      <c r="L101">
-        <v>67</v>
-      </c>
-      <c r="M101">
-        <v>242.546238</v>
-      </c>
-      <c r="N101">
-        <v>-175.546238</v>
-      </c>
-      <c r="O101">
-        <v>-43.8865595</v>
-      </c>
-      <c r="P101">
-        <v>-131.6596785</v>
-      </c>
-      <c r="Q101">
-        <v>-103.2596785</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.147684861510906</v>
-      </c>
-      <c r="T101">
-        <v>118.9370933831678</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06905899731992546</v>
-      </c>
-      <c r="W101">
-        <v>0.2195158884319616</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2762359892797018</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
